--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -18,23 +18,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля навесного" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Модули'!$A$1:$E$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Поля модуля'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Модули'!$A$1:$E$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Самоходные машины'!$A$1:$E$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля самоходной машины'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Навесное и сменное'!$A$1:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Вопросы'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Источники'!$A$1:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Решения'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Источники'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,199 +529,216 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Спецоборудование, смонтированное на шасси, — модуль. Модуль записывается отдельно от базы всегда, в том числе когда его не переставляют (самосвальный кузов, бортовая платформа, пожарная надстройка).</t>
+          <t>Спецоборудование, смонтированное на шасси, — модуль. Модуль записывается отдельно от базы всегда, в том числе когда его не переставляют (самосвальный кузов, бортовая платформа, пожарная надстройка): на ту же базу могли поставить другой модуль. Штатный кузов цельнометаллического фургона без переоборудования — «Базовый модуль». Шасси без надстройки или с демонтированной надстройкой — «модуль отсутствует».</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2а</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Основной модуль</t>
+          <t>Где модульность</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>На базе может стоять несколько модулей. Ровно один — основной: он даёт машине название («автокран», «пожарная автоцистерна», «вахтовый автобус»). Остальные — дополнительные (гидроборт, лебёдка, снегоотвал).</t>
+          <t>Модульность — только когда машина построена на серийном продукте (серийное шасси, серийный прицеп, серийный трактор). Изделие, созданное целиком, а не на базе серийного, — цельное, без деления на базу и модуль: например трал (длинный прицеп собственной конструкции).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Отдельный модуль или параметр</t>
+          <t>Несколько модулей</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Отдельный модуль — у оборудования есть свой изготовитель и заводской номер (или свой учёт в надзоре) и его можно снять, не разрушив основной модуль. Иначе это параметр модуля: секции цистерны, насос бензовоза, тент бортовой платформы.</t>
+          <t>На базе может стоять несколько модулей, каждый записывается отдельно: КамАЗ + бортовая платформа + кран-манипулятор — база и два модуля. Название машины складывается из модулей.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина</t>
+          <t>Отдельный модуль или параметр</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись, параметры рабочего органа — поля машины.</t>
+          <t>Отдельный модуль — у оборудования есть свой изготовитель и заводской номер (или свой учёт в надзоре) и его можно снять, не разрушив соседний модуль. Иначе это параметр модуля: секции цистерны, насос бензовоза, тент бортовой платформы.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Трактор как база</t>
+          <t>Самоходная машина</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Оборудование на тракторе, который сам по себе работает как трактор, — модуль на базе «Трактор»: навесной экскаватор на МТЗ, бульдозерный отвал на ДТ-75, погрузчик ПКУ-0,8.</t>
+          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись, параметры рабочего органа — поля машины.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Прицеп или навесное</t>
+          <t>Трактор как база</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Орудие со своей транспортной осью, которое едет на своих колёсах, — прицеп (подвид «прицепная машина»): прицепная сеялка, пресс-подборщик. Без колёс — навесное оборудование: навесной плуг, отвал, ковш.</t>
+          <t>Оборудование на тракторе, который сам по себе работает как трактор, — модуль на базе «Трактор»: навесной экскаватор на МТЗ, бульдозерный отвал на ДТ-75, погрузчик ПКУ-0,8.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Сменное навесное</t>
+          <t>Прицеп или навесное</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Оборудование, которое ставится штатно и поочерёдно (быстросъём, трёхточечная навеска), — отдельная запись со связью «установлено на». Оценивается и в составе машины, и отдельно. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
+          <t>Есть свои колёса — прицеп (подвид «прицепная машина»): прицепная сеялка, пресс-подборщик, плуг на колёсах. Без колёс — навесное оборудование: навесной плуг, отвал, ковш.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Кран на шасси</t>
+          <t>Сменное навесное</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Автокран на автомобильном шасси: база «Тяжёлый грузовик» + модуль «Автокран». Кран на собственном крановом спецшасси: база «Специальное многоосное шасси» + тот же модуль — это другой класс. Гусеничный и пневмоколёсный кран — самоходные машины.</t>
+          <t>Оборудование, которое ставится штатно и поочерёдно (быстросъём, трёхточечная навеска), — отдельная запись со связью «установлено на». Оценивается и в составе машины, и отдельно. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Тягач и полуприцеп</t>
+          <t>Кран на шасси</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Седельный тягач и полуприцеп — две записи. Седельно-сцепное устройство — часть базы тягача. Полуприцеп несёт свой модуль (цистерна, рефрижератор, самосвальный кузов).</t>
+          <t>Автокран на автомобильном шасси: база «Тяжёлый грузовик» + модуль «Автокран». Кран на собственном крановом спецшасси: база «Специальное многоосное шасси» + тот же модуль — это другой класс. Гусеничный и пневмоколёсный кран — самоходные машины.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Контейнеры и адаптеры</t>
+          <t>Тягач и полуприцеп</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Сменные контейнеры мультилифта, бункеры бункеровоза, жатки комбайна — сменное оборудование, отдельные записи, а не модуль ТС.</t>
+          <t>Седельный тягач и полуприцеп — две записи. Седельно-сцепное устройство — часть базы тягача. Полуприцеп несёт свой модуль (цистерна, рефрижератор, самосвальный кузов).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Полный привод</t>
+          <t>Контейнеры и адаптеры</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Полный привод — признак базы («повышенной проходимости», колёсная формула), а не отдельная категория: Урал-4320 — тяжёлый грузовик с признаком полного привода.</t>
+          <t>Сменные контейнеры мультилифта, бункеры бункеровоза, жатки комбайна — сменное оборудование, отдельные записи, а не модуль ТС.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Полный привод</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Полный привод — признак базы («повышенной проходимости», колёсная формула), а не отдельная категория: Урал-4320 — тяжёлый грузовик с признаком полного привода.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Масса</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Полная масса базы — по документу шасси, полная масса машины целиком — по СТС. Категория базы определяется по массе, а не по модели: Sprinter на 5 т — среднетоннажный.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -881,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1041,7 +1060,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Модули: кран-манипулятор (основной) + бортовая платформа</t>
+          <t>Модули: бортовая платформа + кран-манипулятор</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -1049,17 +1068,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Урал-4320 вахтовка</t>
+          <t>Sprinter Van без переоборудования</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>База: тяжёлый грузовик, повышенной проходимости</t>
+          <t>База: лёгкий коммерческий, цельнометаллический фургон</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Модуль: вахтовый автобус</t>
+          <t>Модуль: базовый модуль</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -1067,35 +1086,39 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Тягач Volvo FH + полуприцеп-цистерна</t>
+          <t>Полуприцеп-трал ЧМЗАП</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Две записи: седельный тягач; полуприцеп</t>
+          <t>Прицеп: полуприцеп</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Модуль полуприцепа: бензовоз</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Цельный: не построен на серийном продукте</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>МТЗ-82 с экскаватором ЭО-2621</t>
+          <t>Урал-4320 вахтовка</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>База: трактор</t>
+          <t>База: тяжёлый грузовик, повышенной проходимости</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Модули: экскаваторное (основной) + погрузочное</t>
+          <t>Модуль: вахтовый автобус</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -1103,56 +1126,48 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>JCB 3CX</t>
+          <t>Тягач Volvo FH + полуприцеп-цистерна</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина: экскаватор-погрузчик</t>
+          <t>Две записи: седельный тягач; полуприцеп</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Одна запись</t>
-        </is>
-      </c>
+          <t>Модуль полуприцепа: бензовоз</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Bobcat S530 с вилами и гидромолотом</t>
+          <t>МТЗ-82 с экскаватором ЭО-2621</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина: мини-погрузчик</t>
+          <t>База: трактор</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Сменное: вилы паллетные; гидромолот</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Отдельные записи со связью</t>
-        </is>
-      </c>
+          <t>Модули: экскаваторное + погрузочное</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Навесной плуг ПЛН-3-35</t>
+          <t>JCB 3CX</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Сменное навесное: плуг навесной</t>
+          <t>Самоходная машина: экскаватор-погрузчик</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1162,74 +1177,118 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Колёс нет</t>
+          <t>Одна запись</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Сеялка СЗ-3,6</t>
+          <t>Bobcat S530 с вилами и гидромолотом</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Прицеп: прицепная машина</t>
+          <t>Самоходная машина: мини-погрузчик</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Сменное: вилы паллетные; гидромолот</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Своя транспортная ось</t>
+          <t>Отдельные записи со связью</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>МТ-ЛБ, переделанный во вездеход с кунгом</t>
+          <t>Навесной плуг ПЛН-3-35</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина: гусеничный транспортёр (переоборудован)</t>
+          <t>Сменное навесное: плуг навесной</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Модуль: передвижной офис (кунг)</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Колёс нет</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Сеялка СЗ-3,6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Прицеп: прицепная машина</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Свои колёса</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>МТ-ЛБ, переделанный во вездеход с кунгом</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Самоходная машина: гусеничный транспортёр (переоборудован)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Модуль: передвижной офис (кунг)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Комбайн Акрос с жаткой</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Самоходная машина: комбайн</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Сменное: жатка зерновая</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Тележка жатки — прицеп</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D17"/>
+  <autoFilter ref="A1:D19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1244,14 +1303,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Вопрос</t>
+          <t>Случай</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1261,7 +1320,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Что решить</t>
+          <t>Как записывать</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1332,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sprinter Van без переоборудования: кузов принадлежит базе, внутри ничего нет.</t>
+          <t>Sprinter Van без переоборудования</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>База без модуля, или модуль «Грузовой отсек (штатный)», чтобы модуль был всегда?</t>
+          <t>База + «Базовый модуль»</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1349,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ-шасси на хранении или грузовик, с которого сняли кран.</t>
+          <t>КамАЗ-шасси на хранении, грузовик со снятым краном</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Допускать базу без модуля с пометкой «модуль отсутствует», или обязательный модуль «Без надстройки»?</t>
+          <t>База без модуля, пометка «модуль отсутствует»</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1366,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Урал-4320: тяжёлый грузовик 6×6.</t>
+          <t>Урал-4320 6×6</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Признак базы (как в правиле 12), или отдельная категория «Полноприводный» для подбора аналогов-вездеходов?</t>
+          <t>Признак базы, не категория</t>
         </is>
       </c>
     </row>
@@ -1324,63 +1383,63 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Фургон Lamberet с установкой Thermo King: установка стоит 20–30 % и меняется отдельно.</t>
+          <t>Фургон с установкой Thermo King</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Один модуль «Рефрижератор» с блоком «холодильная установка», или изотермический фургон + дополнительный модуль «Холодильная установка»?</t>
+          <t>Один модуль «Рефрижератор», устанавливается на базу</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Основной модуль в паре «борт + КМУ»</t>
+          <t>Борт и КМУ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ с бортом и КМУ за кабиной: на рынке это «манипулятор», цену даёт КМУ.</t>
+          <t>КамАЗ с бортом и краном-манипулятором</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Основной — КМУ, борт — дополнительный?</t>
+          <t>База + два модуля: бортовая платформа и кран-манипулятор</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Орудие с опорными колёсами</t>
+          <t>Орудие с колёсами</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Навесной культиватор с колёсами, которые только держат глубину, и полунавесной плуг на транспортной оси.</t>
+          <t>Плуг или культиватор на своих колёсах</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Опорные колёса — навесное; транспортная ось — прицеп. Так?</t>
+          <t>Есть свои колёса — прицеп</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Трал (низкорамная платформа)</t>
+          <t>Трал</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Полуприцеп-трал ЧМЗАП для перевозки техники.</t>
+          <t>Полуприцеп-трал ЧМЗАП</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Это тип полуприцепа (база) без модуля, или база «Полуприцеп» + модуль «Трал»?</t>
+          <t>Прицеп (полуприцеп) целиком. Не построен на серийном продукте — модульности нет</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1451,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Liebherr LTM: шасси и кран — одного изготовителя, шасси отдельно не существует.</t>
+          <t>Liebherr LTM</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Всё равно база + модуль (по правилу «всегда разделять»), с пометкой «шасси собственного изготовления»?</t>
+          <t>База + модуль: на ту же базу могли поставить другой модуль</t>
         </is>
       </c>
     </row>
@@ -1408,6 +1467,61 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Что</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Пояснение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Регистрация техники в КР</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Точный текст ПП КР №407 о регистрации тракторов и самоходных машин не проверен</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Надзор за подъёмными сооружениями в КР</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Какой орган ведёт учёт кранов, подъёмников и КМУ — нужно для поля «учёт в надзоре»</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2087,7 +2201,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Цистерна, трал, рефрижератор, самосвальный, контейнеровоз</t>
+          <t>Цистерна, рефрижератор, самосвальный, контейнеровоз. Трал — цельный полуприцеп собственной конструкции, без модуля</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3086,25 +3200,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Грузовые кузова</t>
+          <t>Базовый</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Бортовая платформа</t>
+          <t>Базовый модуль</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК (цельнометаллический фургон)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Длина платформы, мм; ширина, мм; высота бортов, мм; материал бортов; откидных бортов; гидроборт</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>Объём грузового отсека, м³; высота крыши; перегородка кабины</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Штатный кузов без переоборудования</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3114,7 +3232,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Тентованная платформа</t>
+          <t>Бортовая платформа</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -3124,7 +3242,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Длина, ширина, высота; объём, м³; европаллет; способ загрузки (задняя, боковая, верхняя, шторная)</t>
+          <t>Длина платформы, мм; ширина, мм; высота бортов, мм; материал бортов; откидных бортов; гидроборт</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -3137,24 +3255,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Самосвальный кузов</t>
+          <t>Тентованная платформа</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; разгрузка (назад, на три стороны, вбок); материал днища; толщина днища, мм; подогрев выхлопом; полог</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Карьерный самосвал — самоходная машина, не модуль</t>
-        </is>
-      </c>
+          <t>Длина, ширина, высота; объём, м³; европаллет; способ загрузки (задняя, боковая, верхняя, шторная)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3164,20 +3278,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Промтоварный фургон</t>
+          <t>Самосвальный кузов</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Внутренние длина, ширина, высота; объём, м³; материал стенок; дверей; гидроборт</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>Объём, м³; разгрузка (назад, на три стороны, вбок); материал днища; толщина днища, мм; подогрев выхлопом; полог</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Карьерный самосвал — самоходная машина, не модуль</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3187,7 +3305,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Изотермический фургон</t>
+          <t>Промтоварный фургон</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3197,14 +3315,10 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; толщина стенок, мм; класс изотермии (IN, IR)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Сам не охлаждает</t>
-        </is>
-      </c>
+          <t>Внутренние длина, ширина, высота; объём, м³; материал стенок; дверей; гидроборт</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3214,7 +3328,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Рефрижератор</t>
+          <t>Изотермический фургон</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3224,12 +3338,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; класс ATP (A–F); диапазон температур; холодильная установка: марка, модель, заводской номер, моточасы; многотемпературный; питание от сети на стоянке</t>
+          <t>Объём, м³; толщина стенок, мм; класс изотермии (IN, IR)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Охлаждает — этим отличается от изотермического</t>
+          <t>Сам не охлаждает</t>
         </is>
       </c>
     </row>
@@ -3241,20 +3355,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Рефрижератор</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>ЛК, СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Контейнеры (20, 40, 45 футов); фитинговых замков</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>Объём, м³; класс ATP (A–F); диапазон температур; холодильная установка: марка, модель, заводской номер, моточасы; многотемпературный; питание от сети на стоянке</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Один модуль, устанавливаемый на базу; охлаждает — этим отличается от изотермического</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3264,24 +3382,20 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Мультилифт (крюковой погрузчик)</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ, полуприцеп</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Тяговое усилие, т; длина контейнеров, мм; высота крюка, мм</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Контейнеры — сменное оборудование</t>
-        </is>
-      </c>
+          <t>Контейнеры (20, 40, 45 футов); фитинговых замков</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3291,7 +3405,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Бункеровоз (портальный погрузчик)</t>
+          <t>Мультилифт (крюковой погрузчик)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3301,12 +3415,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность подъёма, т; объём бункера, м³</t>
+          <t>Тяговое усилие, т; длина контейнеров, мм; высота крюка, мм</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Бункеры — сменное оборудование</t>
+          <t>Контейнеры — сменное оборудование</t>
         </is>
       </c>
     </row>
@@ -3318,20 +3432,24 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Лесовоз</t>
+          <t>Бункеровоз (портальный погрузчик)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ТТ + роспуск</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Коников; длина хлыста, м</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность подъёма, т; объём бункера, м³</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Бункеры — сменное оборудование</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3341,24 +3459,20 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Сортиментовоз</t>
+          <t>Лесовоз</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>ТТ + роспуск</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Коников; стоек; длина сортимента, м</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Лесной манипулятор — дополнительный модуль</t>
-        </is>
-      </c>
+          <t>Коников; длина хлыста, м</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3368,20 +3482,24 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Панелевоз</t>
+          <t>Сортиментовоз</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>полуприцеп</t>
+          <t>ТТ, полуприцеп</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; высота кассеты, мм</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>Коников; стоек; длина сортимента, м</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Лесной манипулятор — дополнительный модуль</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3391,17 +3509,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Автовоз</t>
+          <t>Панелевоз</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>полуприцеп</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Мест; ярусов</t>
+          <t>Грузоподъёмность, т; высота кассеты, мм</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -3414,17 +3532,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Автовоз</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ, полуприцеп</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; разгрузка; надставные борта</t>
+          <t>Мест; ярусов</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -3437,7 +3555,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Скотовоз</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3447,7 +3565,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ярусов; голов по видам; поение; вентиляция</t>
+          <t>Объём, м³; разгрузка; надставные борта</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -3455,29 +3573,25 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Цистерны</t>
+          <t>Грузовые кузова</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Бензовоз (светлые нефтепродукты)</t>
+          <t>Скотовоз</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>ТТ, прицеп</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
-        </is>
-      </c>
+          <t>Ярусов; голов по видам; поение; вентиляция</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3487,22 +3601,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Топливозаправщик</t>
+          <t>Бензовоз (светлые нефтепродукты)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
+          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Заправляет технику на месте</t>
+          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3628,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Масловоз, маслозаправщик</t>
+          <t>Топливозаправщик</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3524,10 +3638,14 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; продуктов</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Заправляет технику на месте</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3537,17 +3655,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Нефтевоз, мазутовоз</t>
+          <t>Масловоз, маслозаправщик</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; подогрев</t>
+          <t>Общие для цистерн; продуктов</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -3560,7 +3678,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Битумовоз</t>
+          <t>Нефтевоз, мазутовоз</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3570,7 +3688,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; горелка; температура удержания, °C</t>
+          <t>Общие для цистерн; подогрев</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -3583,7 +3701,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Газовоз (пропан-бутан)</t>
+          <t>Битумовоз</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3593,7 +3711,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; рабочее давление, МПа</t>
+          <t>Общие для цистерн; горелка; температура удержания, °C</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -3606,17 +3724,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Водовоз технический</t>
+          <t>Газовоз (пропан-бутан)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ТТ, прицеп</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн</t>
+          <t>Общие для цистерн; рабочее давление, МПа</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -3629,7 +3747,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Водовоз питьевой</t>
+          <t>Водовоз технический</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3639,7 +3757,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
+          <t>Общие для цистерн</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -3652,17 +3770,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Молоковоз</t>
+          <t>Водовоз питьевой</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн</t>
+          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -3675,7 +3793,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Пищевая цистерна</t>
+          <t>Молоковоз</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3685,7 +3803,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
+          <t>Общие для цистерн</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -3698,17 +3816,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Цементовоз, муковоз (сыпучие)</t>
+          <t>Пищевая цистерна</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
+          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -3721,7 +3839,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Химическая цистерна</t>
+          <t>Цементовоз, муковоз (сыпучие)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3731,7 +3849,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; футеровка</t>
+          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -3744,17 +3862,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Ассенизаторская (вакуумная)</t>
+          <t>Химическая цистерна</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ, прицеп</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
+          <t>Общие для цистерн; футеровка</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -3767,17 +3885,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Илососная</t>
+          <t>Ассенизаторская (вакуумная)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
+          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3785,29 +3903,25 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Цистерны</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Автокран</t>
+          <t>Илососная</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Класс различает база</t>
-        </is>
-      </c>
+          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3817,20 +3931,24 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Кран-манипулятор (КМУ)</t>
+          <t>Автокран</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>ТТ, спецшасси</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Класс различает база</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3840,17 +3958,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Лесной гидроманипулятор</t>
+          <t>Кран-манипулятор (КМУ)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
+          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3863,34 +3981,30 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Автовышка</t>
+          <t>Лесной гидроманипулятор</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
+          <t>ТТ, прицеп</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Автогидроподъёмник (АГП) — синоним</t>
-        </is>
-      </c>
+          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Эвакуаторы</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с платформой</t>
+          <t>Автовышка</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3900,10 +4014,14 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Автогидроподъёмник (АГП) — синоним</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3913,17 +4031,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с частичной погрузкой</t>
+          <t>Эвакуатор с платформой</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
+          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3936,17 +4054,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор-ротатор</t>
+          <t>Эвакуатор с частичной погрузкой</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
+          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3954,22 +4072,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Строительные и дорожные</t>
+          <t>Эвакуаторы</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Автобетоносмеситель (миксер)</t>
+          <t>Эвакуатор-ротатор</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
+          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3982,17 +4100,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Автобетононасос</t>
+          <t>Автобетоносмеситель (миксер)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
+          <t>ТТ, полуприцеп</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
+          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -4005,17 +4123,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Буровая установка</t>
+          <t>Автобетононасос</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси, вездеход</t>
+          <t>ТТ, спецшасси</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
+          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -4028,17 +4146,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Ямобур (бурильно-крановая машина)</t>
+          <t>Буровая установка</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ, спецшасси, вездеход</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
+          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -4051,7 +4169,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Автогудронатор</t>
+          <t>Ямобур (бурильно-крановая машина)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4061,7 +4179,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
+          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4074,17 +4192,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Асфальтовоз-термос</t>
+          <t>Автогудронатор</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Объём кузова, м³; подогрев</t>
+          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4097,7 +4215,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Распределитель щебня</t>
+          <t>Асфальтовоз-термос</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4107,14 +4225,10 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Ширина распределения, м</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Обычно дополнительный модуль на самосвале</t>
-        </is>
-      </c>
+          <t>Объём кузова, м³; подогрев</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4124,30 +4238,34 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Дорожный ремонтёр (ямочный ремонт)</t>
+          <t>Распределитель щебня</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Термобункер, м³; ёмкость эмульсии, л</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
+          <t>Ширина распределения, м</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Обычно дополнительный модуль на самосвале</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с задней загрузкой</t>
+          <t>Дорожный ремонтёр (ямочный ремонт)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4157,7 +4275,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
+          <t>Термобункер, м³; ёмкость эмульсии, л</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4170,7 +4288,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с боковой загрузкой</t>
+          <t>Мусоровоз с задней загрузкой</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4180,7 +4298,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; манипулятор, грузоподъёмность</t>
+          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4193,17 +4311,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с фронтальной загрузкой</t>
+          <t>Мусоровоз с боковой загрузкой</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; грузоподъёмность вил, т</t>
+          <t>Объём, м³; манипулятор, грузоподъёмность</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4216,24 +4334,20 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Комбинированная дорожная машина (КДМ)</t>
+          <t>Мусоровоз с фронтальной загрузкой</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Оборудование (передний отвал, боковой отвал, щётка, пескоразбрасыватель, поливомоечное); объём бункера, м³; объём цистерны, м³; ширина обработки, м</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Один модуль со списком оборудования</t>
-        </is>
-      </c>
+          <t>Объём, м³; грузоподъёмность вил, т</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4243,7 +4357,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Поливомоечная машина</t>
+          <t>Комбинированная дорожная машина (КДМ)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4253,10 +4367,14 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>Оборудование (передний отвал, боковой отвал, щётка, пескоразбрасыватель, поливомоечное); объём бункера, м³; объём цистерны, м³; ширина обработки, м</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Один модуль со списком оборудования</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4266,7 +4384,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Подметально-уборочная машина</t>
+          <t>Поливомоечная машина</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4276,7 +4394,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
+          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -4289,7 +4407,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Пескоразбрасыватель</t>
+          <t>Подметально-уборочная машина</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4299,7 +4417,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³; ширина распределения, м</t>
+          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -4312,17 +4430,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Шнекороторный снегоочиститель</t>
+          <t>Пескоразбрасыватель</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Производительность, т/ч; ширина захвата, м</t>
+          <t>Объём бункера, м³; ширина распределения, м</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -4335,17 +4453,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочная машина</t>
+          <t>Шнекороторный снегоочиститель</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ, спецшасси</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
+          <t>Производительность, т/ч; ширина захвата, м</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -4358,49 +4476,45 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочно-илососная машина</t>
+          <t>Каналопромывочная машина</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Поля каналопромывочной и илососной</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Один модуль</t>
-        </is>
-      </c>
+          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автоцистерна (АЦ)</t>
+          <t>Каналопромывочно-илососная машина</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
+          <t>Поля каналопромывочной и илососной</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
+          <t>Один модуль</t>
         </is>
       </c>
     </row>
@@ -4412,20 +4526,24 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автолестница (АЛ)</t>
+          <t>Пожарная автоцистерна (АЦ)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4435,7 +4553,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Пожарный подъёмник (АКП, АТП)</t>
+          <t>Пожарная автолестница (АЛ)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4445,7 +4563,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
+          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -4458,17 +4576,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Пожарная насосная станция (ПНС)</t>
+          <t>Пожарный подъёмник (АКП, АТП)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>ТТ, спецшасси</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с</t>
+          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -4481,17 +4599,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Насосно-рукавный пожарный (АНР)</t>
+          <t>Пожарная насосная станция (ПНС)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с; запас рукавов, м</t>
+          <t>Подача насоса, л/с</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -4504,17 +4622,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Пожарный первой помощи (АПП)</t>
+          <t>Насосно-рукавный пожарный (АНР)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с; запас воды, л</t>
+          <t>Подача насоса, л/с; запас рукавов, м</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -4527,17 +4645,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Пожарный пенного, порошкового или газового тушения</t>
+          <t>Пожарный первой помощи (АПП)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>ЛК, СТ</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Огнетушащее вещество; масса или объём</t>
+          <t>Подача насоса, л/с; запас воды, л</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -4550,17 +4668,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Аэродромный пожарный</t>
+          <t>Пожарный пенного, порошкового или газового тушения</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>спецшасси</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
+          <t>Огнетушащее вещество; масса или объём</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -4573,17 +4691,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
+          <t>Аэродромный пожарный</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
+          <t>спецшасси</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Вид; класс по массе (L, M, S); комплектность</t>
+          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -4591,29 +4709,25 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса A (санитарная)</t>
+          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ЛК</t>
+          <t>ЛК, СТ</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>По ГОСТ 33665-2015</t>
-        </is>
-      </c>
+          <t>Вид; класс по массе (L, M, S); комплектность</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4623,7 +4737,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса B (экстренная)</t>
+          <t>Скорая помощь класса A (санитарная)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4633,10 +4747,14 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>По ГОСТ 33665-2015</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4646,17 +4764,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Реанимобиль (класс C)</t>
+          <t>Скорая помощь класса B (экстренная)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
+          <t>ЛК</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Реанимационный комплект (перечень); автономное электропитание</t>
+          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -4669,17 +4787,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Передвижной медицинский кабинет</t>
+          <t>Реанимобиль (класс C)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп, автобус</t>
+          <t>ЛК, СТ</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
+          <t>Реанимационный комплект (перечень); автономное электропитание</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -4687,22 +4805,22 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Передвижная лаборатория</t>
+          <t>Передвижной медицинский кабинет</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
+          <t>СТ, ТТ, прицеп, автобус</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Профиль; приборы (перечень)</t>
+          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -4715,17 +4833,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Передвижная автомастерская</t>
+          <t>Передвижная лаборатория</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
+          <t>Профиль; приборы (перечень)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4738,17 +4856,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Аварийная газовой службы</t>
+          <t>Передвижная автомастерская</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Генератор, кВт; газоанализаторы</t>
+          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4761,17 +4879,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Аварийно-ремонтная (электросети, водоканал)</t>
+          <t>Аварийная газовой службы</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
+          <t>ЛК, СТ</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
+          <t>Генератор, кВт; газоанализаторы</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4784,17 +4902,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Инкассаторский автомобиль</t>
+          <t>Аварийно-ремонтная (электросети, водоканал)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ЛК</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Класс защиты (Бр1–Бр5); сейф</t>
+          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4807,17 +4925,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Оперативный (патрульный)</t>
+          <t>Инкассаторский автомобиль</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>легковой, ЛК</t>
+          <t>ЛК</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Спецсигналы; отсек для задержанных; связь</t>
+          <t>Класс защиты (Бр1–Бр5); сейф</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4830,17 +4948,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Штабной автомобиль</t>
+          <t>Оперативный (патрульный)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
+          <t>легковой, ЛК</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Рабочих мест; средства связи</t>
+          <t>Спецсигналы; отсек для задержанных; связь</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4853,17 +4971,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Передвижной офис (бытовка)</t>
+          <t>Штабной автомобиль</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Мест; отопление; санузел</t>
+          <t>Рабочих мест; средства связи</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4876,24 +4994,20 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Вахтовый автобус</t>
+          <t>Передвижной офис (бытовка)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>СТ, ТТ, прицеп</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
-        </is>
-      </c>
+          <t>Мест; отопление; санузел</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4903,20 +5017,24 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Автодом</t>
+          <t>Вахтовый автобус</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
+          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4926,17 +5044,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Автолавка (торговый фургон)</t>
+          <t>Автодом</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, прицеп</t>
+          <t>ЛК, СТ</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Торговое окно; холодильные витрины; весы</t>
+          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4949,17 +5067,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Хлебный фургон</t>
+          <t>Автолавка (торговый фургон)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
+          <t>ЛК, СТ, прицеп</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Лотков; стеллажи</t>
+          <t>Торговое окно; холодильные витрины; весы</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -4972,17 +5090,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Катафалк</t>
+          <t>Хлебный фургон</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>легковой, ЛК</t>
+          <t>ЛК, СТ</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Мест для гроба; сидячих мест</t>
+          <t>Лотков; стеллажи</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -4995,17 +5113,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Спецоборудование салона автобуса</t>
+          <t>Катафалк</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>автобус</t>
+          <t>легковой, ЛК</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Профиль; оборудование (перечень)</t>
+          <t>Мест для гроба; сидячих мест</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -5013,22 +5131,22 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Цементировочный агрегат (ЦА)</t>
+          <t>Спецоборудование салона автобуса</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>ТТ повышенной проходимости</t>
+          <t>автобус</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
+          <t>Профиль; оборудование (перечень)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -5041,17 +5159,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Насосный агрегат</t>
+          <t>Цементировочный агрегат (ЦА)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>ТТ повышенной проходимости</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Давление, МПа; подача, л/с</t>
+          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -5064,17 +5182,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Паропередвижная установка (ППУ)</t>
+          <t>Насосный агрегат</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ТТ, вездеход</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
+          <t>Давление, МПа; подача, л/с</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -5087,17 +5205,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Агрегат депарафинизации (АДПМ)</t>
+          <t>Паропередвижная установка (ППУ)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>ТТ, вездеход</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
+          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -5110,17 +5228,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Подъёмник ремонта скважин</t>
+          <t>Агрегат депарафинизации (АДПМ)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
+          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -5133,17 +5251,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Смесительная установка</t>
+          <t>Подъёмник ремонта скважин</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>ТТ, спецшасси</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³</t>
+          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -5156,7 +5274,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Каротажный подъёмник (лаборатория)</t>
+          <t>Смесительная установка</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5166,7 +5284,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Глубина, м; кабель, м</t>
+          <t>Объём бункера, м³</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -5174,22 +5292,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Кормовоз</t>
+          <t>Каротажный подъёмник (лаборатория)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
+          <t>Глубина, м; кабель, м</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -5202,7 +5320,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Кормораздатчик на шасси</t>
+          <t>Кормовоз</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5212,7 +5330,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; взвешивание</t>
+          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -5220,29 +5338,25 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Сельскохозяйственные</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Экскаваторное оборудование</t>
+          <t>Кормораздатчик на шасси</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>трактор</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Объём ковша, м³; глубина копания, м; заводской номер</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
-        </is>
-      </c>
+          <t>Объём, м³; взвешивание</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5252,7 +5366,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Погрузочное оборудование</t>
+          <t>Экскаваторное оборудование</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5262,12 +5376,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём ковша, м³</t>
+          <t>Объём ковша, м³; глубина копания, м; заводской номер</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>ПКУ-0,8</t>
+          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5393,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Бульдозерное оборудование</t>
+          <t>Погрузочное оборудование</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5289,12 +5403,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Ширина отвала, мм; высота, мм; поворотный</t>
+          <t>Грузоподъёмность, т; объём ковша, м³</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>ДЗ-42 на ДТ-75</t>
+          <t>ПКУ-0,8</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5420,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Траншеекопатель</t>
+          <t>Бульдозерное оборудование</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5316,12 +5430,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Глубина траншеи, м; ширина, мм</t>
+          <t>Ширина отвала, мм; высота, мм; поворотный</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>ЭТЦ на МТЗ</t>
+          <t>ДЗ-42 на ДТ-75</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5447,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Коммунальное оборудование</t>
+          <t>Траншеекопатель</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5343,10 +5457,14 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Отвал; щётка; разбрасыватель — перечень</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
+          <t>Глубина траншеи, м; ширина, мм</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>ЭТЦ на МТЗ</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5356,27 +5474,50 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
+          <t>Коммунальное оборудование</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>трактор</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Отвал; щётка; разбрасыватель — перечень</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Навесное на тракторе</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>Трубоукладочное оборудование</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>трактор</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Грузоподъёмность, т; момент устойчивости, т·м</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>На Т-170</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E97"/>
+  <autoFilter ref="A1:E98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5387,7 +5528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5432,24 +5573,24 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Основной или дополнительный</t>
+          <t>Изготовитель модуля</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ровно один основной</t>
+          <t>отдельно от изготовителя базы; может быть неизвестен</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Изготовитель модуля</t>
+          <t>Модель (индекс) установки</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -5459,14 +5600,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>отдельно от изготовителя базы; может быть неизвестен</t>
+          <t>КС-45717, АЦ 3,0-40/4, КМУ Palfinger PK 23500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Модель (индекс) установки</t>
+          <t>Заводской номер</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -5474,21 +5615,17 @@
           <t>текст</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>КС-45717, АЦ 3,0-40/4, КМУ Palfinger PK 23500</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Заводской номер</t>
+          <t>Год выпуска модуля</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>год</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -5496,7 +5633,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Год выпуска модуля</t>
+          <t>Год монтажа на эту базу</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -5509,99 +5646,86 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Год монтажа на эту базу</t>
+          <t>Моточасы модуля</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>год</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>счётчик крана, насоса, КМУ, холодильной установки</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Моточасы модуля</t>
+          <t>Привод</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>список</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>счётчик крана, насоса, КМУ, холодильной установки</t>
+          <t>от КОМ базы, свой двигатель, электро</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Привод</t>
+          <t>Учёт в надзоре</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>да / нет + номер</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>от КОМ базы, свой двигатель, электро</t>
+          <t>краны, подъёмники, КМУ, сосуды под давлением</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Учёт в надзоре</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>да / нет + номер</t>
+          <t>список</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>краны, подъёмники, КМУ, сосуды под давлением</t>
+          <t>шкала осмотра</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Комплектность</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -16,27 +16,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля самоходной машины" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навесное и сменное" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля навесного" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы прицепов" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Модули'!$A$1:$E$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Самоходные машины'!$A$1:$E$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Самоходные машины'!$A$1:$E$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля самоходной машины'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Навесное и сменное'!$A$1:$E$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Решения'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Источники'!$A$1:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Типы прицепов'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Решения'!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Источники'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -512,7 +514,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Каждая единица относится ровно к одному виду: колёсное ТС (база + модули), прицеп или полуприцеп (база + модули), самоходная машина собственной конструкции, сменное навесное оборудование.</t>
+          <t>Каждая единица относится ровно к одному виду: колёсное ТС (база + модули), прицеп или полуприцеп (тип), самоходная машина собственной конструкции, сменное навесное оборудование.</t>
         </is>
       </c>
     </row>
@@ -536,214 +538,659 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2а</t>
+          <t>2б</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Где модульность</t>
+          <t>Прицепы — типом</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Модульность — только когда машина построена на серийном продукте (серийное шасси, серийный прицеп, серийный трактор). Изделие, созданное целиком, а не на базе серийного, — цельное, без деления на базу и модуль: например трал (длинный прицеп собственной конструкции).</t>
+          <t>Прицеп и полуприцеп описываются ТИПОМ (цистерна, рефрижератор, самосвальный, трал, прицепная машина), а не базой с модулем: рама сама по себе модульности не создаёт. Тот же агрегат, смонтированный на шасси, — модуль: передвижная АЗС, электростанция, компрессор бывают и типом прицепа, и модулем.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2в</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Несколько модулей</t>
+          <t>Навесное вместо полей</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>На базе может стоять несколько модулей, каждый записывается отдельно: КамАЗ + бортовая платформа + кран-манипулятор — база и два модуля. Название машины складывается из модулей.</t>
+          <t>Ковши, вилы, жатки, отвалы, щётки, бункеры — всегда навесное оборудование отдельной записью, даже когда пришли вместе с машиной. В поля машины они не выносятся.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2г</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Отдельный модуль или параметр</t>
+          <t>Что не входит</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Отдельный модуль — у оборудования есть свой изготовитель и заводской номер (или свой учёт в надзоре) и его можно снять, не разрушив соседний модуль. Иначе это параметр модуля: секции цистерны, насос бензовоза, тент бортовой платформы.</t>
+          <t>Малая механизация с оператором — виброплита, ручной виброкаток и подобное — инструмент, а не техника: в классификатор не входит. Самодельные и кустарные надстройки не учитываются.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2а</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина</t>
+          <t>Где модульность</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись, параметры рабочего органа — поля машины.</t>
+          <t>Модульность — только когда машина построена на серийном продукте (серийное шасси, серийный трактор). Изделие, созданное целиком, а не на базе серийного, — цельное, без деления на базу и модуль.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Трактор как база</t>
+          <t>Несколько модулей</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Оборудование на тракторе, который сам по себе работает как трактор, — модуль на базе «Трактор»: навесной экскаватор на МТЗ, бульдозерный отвал на ДТ-75, погрузчик ПКУ-0,8.</t>
+          <t>На базе может стоять несколько модулей, каждый записывается отдельно: КамАЗ + бортовая платформа + кран-манипулятор — база и два модуля. Название машины складывается из модулей.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Прицеп или навесное</t>
+          <t>Отдельный модуль или параметр</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Есть свои колёса — прицеп (подвид «прицепная машина»): прицепная сеялка, пресс-подборщик, плуг на колёсах. Без колёс — навесное оборудование: навесной плуг, отвал, ковш.</t>
+          <t>Отдельный модуль — у оборудования есть свой изготовитель и заводской номер (или свой учёт в надзоре) и его можно снять, не разрушив соседний модуль. Иначе это параметр модуля: секции цистерны, насос бензовоза, тент бортовой платформы.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Сменное навесное</t>
+          <t>Самоходная машина</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Оборудование, которое ставится штатно и поочерёдно (быстросъём, трёхточечная навеска), — отдельная запись со связью «установлено на». Оценивается и в составе машины, и отдельно. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
+          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись, параметры рабочего органа — поля машины.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Кран на шасси</t>
+          <t>Трактор как база</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Автокран на автомобильном шасси: база «Тяжёлый грузовик» + модуль «Автокран». Кран на собственном крановом спецшасси: база «Специальное многоосное шасси» + тот же модуль — это другой класс. Гусеничный и пневмоколёсный кран — самоходные машины.</t>
+          <t>Оборудование на тракторе, который сам по себе работает как трактор, — модуль на базе «Трактор»: навесной экскаватор на МТЗ, бульдозерный отвал на ДТ-75, погрузчик ПКУ-0,8. Отдельной записи «экскаватор» при этом не заводится — это трактор с модулем.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Тягач и полуприцеп</t>
+          <t>Прицеп или навесное</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Седельный тягач и полуприцеп — две записи. Седельно-сцепное устройство — часть базы тягача. Полуприцеп несёт свой модуль (цистерна, рефрижератор, самосвальный кузов).</t>
+          <t>Есть свои колёса — прицеп (тип «прицепная машина»): прицепная сеялка, пресс-подборщик, плуг на колёсах. Без колёс — навесное оборудование: навесной плуг, отвал, ковш.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Контейнеры и адаптеры</t>
+          <t>Сменное навесное</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Сменные контейнеры мультилифта, бункеры бункеровоза, жатки комбайна — сменное оборудование, отдельные записи, а не модуль ТС.</t>
+          <t>Оборудование, которое ставится штатно и поочерёдно (быстросъём, трёхточечная навеска), — отдельная запись со связью «установлено на». Оценивается и в составе машины, и отдельно. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Полный привод</t>
+          <t>Кран на шасси</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Полный привод — признак базы («повышенной проходимости», колёсная формула), а не отдельная категория: Урал-4320 — тяжёлый грузовик с признаком полного привода.</t>
+          <t>Автокран на автомобильном шасси: база «Тяжёлый грузовик» + модуль «Автокран». Кран на собственном крановом спецшасси: база «Специальное многоосное шасси» + тот же модуль — это другой класс. Гусеничный и пневмоколёсный кран — самоходные машины.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Тягач и полуприцеп</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Седельный тягач и полуприцеп — две записи. Седельно-сцепное устройство — часть базы тягача. У полуприцепа указывается тип (цистерна, рефрижератор, самосвальный).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Контейнеры и адаптеры</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Сменные контейнеры мультилифта, бункеры бункеровоза, жатки комбайна — сменное оборудование, отдельные записи, а не модуль ТС.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Полный привод</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Полный привод — признак базы («повышенной проходимости», колёсная формула), а не отдельная категория: Урал-4320 — тяжёлый грузовик с признаком полного привода.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Масса</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Полная масса базы — по документу шасси, полная масса машины целиком — по СТС. Категория базы определяется по массе, а не по модели: Sprinter на 5 т — среднетоннажный.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C15"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Назначение</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Поля сверх общих полей прицепа</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Бортовой</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Платформа с бортами</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Длина, ширина, высота бортов, мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Тентованный</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Платформа с каркасом и тентом</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; способ загрузки; европаллет</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Самосвальный</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Кузов с опрокидыванием</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; разгрузка (назад, на три стороны, вбок)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Цистерна</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Наливные и сыпучие грузы</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Продукт; объём, м³; секций; материал; насос; класс ДОПОГ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Изотермический</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Утеплённый фургон без охлаждения</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; класс изотермии</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Рефрижератор</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Фургон с холодильной установкой</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; класс ATP; установка: марка, номер, моточасы</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Фургон промтоварный</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Закрытый кузов</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Внутренние размеры; объём, м³; гидроборт</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Контейнеровоз</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Платформа под контейнеры</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Контейнеры (20, 40, 45 футов); фитинговых замков</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Трал (низкорамный)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Перевозка техники</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность, т; погрузочная высота, мм; аппарели; раздвижной</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Лесовоз, сортиментовоз</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Перевозка леса</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Коников; длина сортимента, м</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Автовоз</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Перевозка автомобилей</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Мест; ярусов</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Скотовоз</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Перевозка животных</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Ярусов; голов; поение; вентиляция</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Зерновоз</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Перевозка зерна</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; разгрузка</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Цементовоз (сыпучие)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Пневморазгрузка</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; компрессор, м³/мин</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Роспуск</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Для длинномеров</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность, т; раздвижной</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Передвижная АЗС</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Заправка техники на месте</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; секций; насос; счётчик; раздаточных пистолетов</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Электростанция</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Автономное питание</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Мощность, кВт; напряжение; топливный бак, л; моточасы</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Компрессорная установка</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Сжатый воздух</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Производительность, м³/мин; давление, бар; моточасы</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Мотопомпа</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Перекачка воды</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Подача, л/мин; напор, м</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка (вагончик)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Бытовые помещения</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Мест; отопление; санузел</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Прицепная машина</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Сельхозорудие на своих колёсах</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Вид (лист «Прицепные машины»); ширина захвата, м</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -894,13 +1341,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1091,7 +1538,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Прицеп: полуприцеп</t>
+          <t>Прицеп: полуприцеп, тип «трал»</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1101,117 +1548,121 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Цельный: не построен на серийном продукте</t>
+          <t>Описывается типом, модуля нет</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Урал-4320 вахтовка</t>
+          <t>Полуприцеп-цистерна безрамный</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>База: тяжёлый грузовик, повышенной проходимости</t>
+          <t>Прицеп: полуприцеп, тип «цистерна»</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Модуль: вахтовый автобус</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>«Безрамный» — свойство полуприцепа</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Тягач Volvo FH + полуприцеп-цистерна</t>
+          <t>Передвижная АЗС на прицепе</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Две записи: седельный тягач; полуприцеп</t>
+          <t>Прицеп, тип «передвижная АЗС»</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Модуль полуприцепа: бензовоз</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>На шасси та же АЗС была бы модулем</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>МТЗ-82 с экскаватором ЭО-2621</t>
+          <t>Думпер Wacker Neuson</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>База: трактор</t>
+          <t>Самоходная машина: думпер</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Модули: экскаваторное + погрузочное</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Мини-самосвал с поворотным ковшом</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>JCB 3CX</t>
+          <t>Multicar с щёткой и отвалом</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина: экскаватор-погрузчик</t>
+          <t>База: малое коммунальное шасси</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Одна запись</t>
-        </is>
-      </c>
+          <t>Навесное: щётка; отвал снежный</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Bobcat S530 с вилами и гидромолотом</t>
+          <t>Урал-4320 вахтовка</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина: мини-погрузчик</t>
+          <t>База: тяжёлый грузовик, повышенной проходимости</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Сменное: вилы паллетные; гидромолот</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Отдельные записи со связью</t>
-        </is>
-      </c>
+          <t>Модуль: вахтовый автобус</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Навесной плуг ПЛН-3-35</t>
+          <t>Тягач Volvo FH + полуприцеп-цистерна</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Сменное навесное: плуг навесной</t>
+          <t>Две записи: седельный тягач; полуприцеп типа «цистерна»</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1219,87 +1670,167 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Колёс нет</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Сеялка СЗ-3,6</t>
+          <t>МТЗ-82 с экскаватором ЭО-2621</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Прицеп: прицепная машина</t>
+          <t>База: трактор</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Свои колёса</t>
-        </is>
-      </c>
+          <t>Модули: экскаваторное + погрузочное</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>МТ-ЛБ, переделанный во вездеход с кунгом</t>
+          <t>JCB 3CX</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина: гусеничный транспортёр (переоборудован)</t>
+          <t>Самоходная машина: экскаватор-погрузчик</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Модуль: передвижной офис (кунг)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Одна запись</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>Bobcat S530 с вилами и гидромолотом</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Самоходная машина: мини-погрузчик</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Сменное: вилы паллетные; гидромолот</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Отдельные записи со связью</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Навесной плуг ПЛН-3-35</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Сменное навесное: плуг навесной</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Колёс нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Сеялка СЗ-3,6</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Прицеп: прицепная машина</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Свои колёса</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>МТ-ЛБ, переделанный во вездеход с кунгом</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Самоходная машина: гусеничный транспортёр (переоборудован)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Модуль: передвижной офис (кунг)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Комбайн Акрос с жаткой</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Самоходная машина: комбайн</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Сменное: жатка зерновая</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Тележка жатки — прицеп</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19"/>
+  <autoFilter ref="A1:D23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1439,7 +1970,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Прицеп (полуприцеп) целиком. Не построен на серийном продукте — модульности нет</t>
+          <t>Полуприцеп типа «трал»: прицеп описывается типом, модуля нет</t>
         </is>
       </c>
     </row>
@@ -1460,13 +1991,149 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Прицепы и полуприцепы</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Полуприцеп-цистерна, трал, прицеп-АЗС</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Описываются типом прицепа; рама модульности не создаёт. Тот же агрегат на шасси — модуль</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Безрамная цистерна</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Полуприцеп с несущей цистерной</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Полуприцеп типа «цистерна», «безрамный» — свойство</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Ковш, вилы, жатка</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Штатный ковш экскаватора, жатка комбайна</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Навесное оборудование отдельной записью, в поля машины не выносится</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Комбинированная дорожная машина</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>КДМ с отвалом, щёткой и разбрасывателем</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Модуль КДМ, а отвал, щётка и бункер — навесное оборудование</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Лестница пожарной автоцистерны</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>АЦЛ</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Параметр модуля, отдельным модулем не заводится</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Трактор с навесным экскаватором</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ-82 + ЭО-2621</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Трактор + модуль «экскаваторное оборудование»; отдельной записи «экскаватор» нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Малая механизация</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Виброплита с оператором, ручной виброкаток</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Инструмент, в классификатор не входит</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Самодельные надстройки</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Бочка на раме, гаражный кунг</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Не учитываются: переоборудование незаконно</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C9"/>
+  <autoFilter ref="A1:C17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1521,7 +2188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1786,7 +2453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1917,32 +2584,32 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Среднетоннажный грузовик (3,5–12 т)</t>
+          <t>Малое коммунальное шасси</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1, N2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Две оси, обычно 4×2, кабина капотная или бескапотная.</t>
+          <t>Компактный носитель сменного коммунального оборудования: отвал, щётка, бункер, поливалка. Не лёгкий коммерческий и не трактор.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ГАЗ-3307/3309, ГАЗон Next, ЗИЛ-130/5301/4331, МАЗ-4371, Isuzu NQR/NPR, Hyundai HD-65/78/120, Mitsubishi Canter, Hino 300, FAW, Foton</t>
+          <t>Multicar и китайские аналоги, коммунальные минишасси</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Монтажная длина рамы, мм; высота рамы, мм</t>
+          <t>Монтажная длина рамы, мм; передняя навеска; гидровыводы</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз, автовышка до 22 м, КДМ, цистерна до 6 м³, лёгкий автокран</t>
+          <t>Коммунальное сменное оборудование</t>
         </is>
       </c>
     </row>
@@ -1954,32 +2621,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Тяжёлый грузовик (свыше 12 т)</t>
+          <t>Среднетоннажный грузовик (3,5–12 т)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2–4 оси, 4×2, 6×4, 8×4; бескапотная кабина.</t>
+          <t>Две оси, обычно 4×2, кабина капотная или бескапотная.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ-5320/65115/6520, МАЗ-5516/6501, Howo, Shacman, FAW, Dongfeng, MAN TGS, Volvo FM, Scania, Mercedes Actros/Arocs</t>
+          <t>ГАЗ-3307/3309, ГАЗон Next, ЗИЛ-130/5301/4331, МАЗ-4371, Isuzu NQR/NPR, Hyundai HD-65/78/120, Mitsubishi Canter, Hino 300, FAW, Foton</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Нагрузка на заднюю тележку, кг; тип подвески тележки; число ведущих осей; подъёмная ось</t>
+          <t>Монтажная длина рамы, мм; высота рамы, мм</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Самосвал, миксер, автокран на автошасси, бетононасос, КМУ, топливозаправщик</t>
+          <t>Мусоровоз, автовышка до 22 м, КДМ, цистерна до 6 м³, лёгкий автокран</t>
         </is>
       </c>
     </row>
@@ -1991,32 +2658,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Седельный тягач</t>
+          <t>Тяжёлый грузовик (свыше 12 т)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>N2, N3</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Короткая рама, седельно-сцепное устройство, без грузовой платформы.</t>
+          <t>2–4 оси, 4×2, 6×4, 8×4; бескапотная кабина.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ-5410/5490/65116, МАЗ-5440/6430, Volvo FH, Scania R, MAN TGX, Howo T7H, Shacman X3000</t>
+          <t>КамАЗ-5320/65115/6520, МАЗ-5516/6501, Howo, Shacman, FAW, Dongfeng, MAN TGS, Volvo FM, Scania, Mercedes Actros/Arocs</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Высота седельного устройства, мм; нагрузка на седло, кг; полная масса автопоезда, кг; гидравлика для полуприцепа</t>
+          <t>Нагрузка на заднюю тележку, кг; тип подвески тележки; число ведущих осей; подъёмная ось</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Работает с полуприцепами — отдельными записями</t>
+          <t>Самосвал, миксер, автокран на автошасси, бетононасос, КМУ, топливозаправщик</t>
         </is>
       </c>
     </row>
@@ -2028,32 +2695,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Специальное многоосное шасси</t>
+          <t>Седельный тягач</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>N3, N3G</t>
+          <t>N2, N3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Шасси спроектировано под конкретную машину и отдельно не продаётся: 3–9 осей, многоосное рулевое, выносные опоры в раме, часто вторая кабина. Марка шасси и крана обычно совпадают.</t>
+          <t>Короткая рама, седельно-сцепное устройство, без грузовой платформы.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Liebherr LTM, Grove GMK, Tadano, XCMG QAY, Zoomlion, SANY; МЗКТ «Волат»; «Ивановец», «Галичанин» на собственных спецшасси</t>
+          <t>КамАЗ-5410/5490/65116, МАЗ-5440/6430, Volvo FH, Scania R, MAN TGX, Howo T7H, Shacman X3000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Число управляемых осей; тип подвески (гидропневматическая, рессорная); максимальная скорость, км/ч; нагрузка на ось, кг</t>
+          <t>Высота седельного устройства, мм; нагрузка на седло, кг; полная масса автопоезда, кг; гидравлика для полуприцепа</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Автокран тяжёлый, аэродромная пожарная, тяжёлая буровая</t>
+          <t>Работает с полуприцепами — отдельными записями</t>
         </is>
       </c>
     </row>
@@ -2065,32 +2732,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Автобус</t>
+          <t>Специальное многоосное шасси</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>M2, M3</t>
+          <t>N3, N3G</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Больше 8 пассажирских мест. Кузов-вагон или кузов стороннего завода на автобусном шасси — всё равно база целиком.</t>
+          <t>Шасси спроектировано под конкретную машину и отдельно не продаётся: 3–9 осей, многоосное рулевое, выносные опоры в раме, часто вторая кабина. Марка шасси и крана обычно совпадают.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ПАЗ, ЛиАЗ, МАЗ-103, Yutong, Higer, King Long, Hyundai County, Isuzu Novo</t>
+          <t>Liebherr LTM, Grove GMK, Tadano, XCMG QAY, Zoomlion, SANY; МЗКТ «Волат»; «Ивановец», «Галичанин» на собственных спецшасси</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Посадочных мест; общая вместимость; класс автобуса; расположение двигателя; высота пола; изготовитель кузова</t>
+          <t>Число управляемых осей; тип подвески (гидропневматическая, рессорная); максимальная скорость, км/ч; нагрузка на ось, кг</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Передвижной медпункт, штаб — через модуль «спецоборудование салона»</t>
+          <t>Автокран тяжёлый, аэродромная пожарная, тяжёлая буровая</t>
         </is>
       </c>
     </row>
@@ -2102,69 +2769,69 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Мототехника</t>
+          <t>Автобус</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>L1–L7</t>
+          <t>M2, M3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Мотоциклы, мотороллеры, квадрициклы.</t>
+          <t>Больше 8 пассажирских мест. Кузов-вагон или кузов стороннего завода на автобусном шасси — всё равно база целиком.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Грузовые мотороллеры, квадроциклы</t>
+          <t>ПАЗ, ЛиАЗ, МАЗ-103, Yutong, Higer, King Long, Hyundai County, Isuzu Novo</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Тип (мотоцикл, мотороллер, квадрицикл)</t>
+          <t>Посадочных мест; общая вместимость; класс автобуса; расположение двигателя; высота пола; изготовитель кузова</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Как база — редко</t>
+          <t>Передвижной медпункт, штаб — через модуль «спецоборудование салона»</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>Колёсное ТС</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>Мототехника</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>O1–O4</t>
+          <t>L1–L7</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Буксируется, своего двигателя нет; полный, центральноосный или роспуск.</t>
+          <t>Мотоциклы, мотороллеры, квадрициклы.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>СЗАП, МАЗ-8926, Нефаз, Тонар, ГКБ-8350, Krone, Schmitz, CIMC</t>
+          <t>Грузовые мотороллеры, квадроциклы</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Число осей; полная масса, кг; снаряжённая масса, кг; тормоза; подвеска; сцепное устройство; размерность шин</t>
+          <t>Тип (мотоцикл, мотороллер, квадрицикл)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Прицеп-цистерна, платформа под технику, передвижная электростанция</t>
+          <t>Как база — редко</t>
         </is>
       </c>
     </row>
@@ -2176,32 +2843,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>Прицеп</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>O3, O4</t>
+          <t>O1–O4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Опирается на седло тягача шкворнем, передней оси нет. Бывает безрамным — несущая цистерна.</t>
+          <t>Буксируется, своего двигателя нет; полный, центральноосный или роспуск.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>МАЗ-9397/9758, Нефаз-9334, Тонар, ЧМЗАП, Schmitz, Krone, Kögel, Wielton, CIMC</t>
+          <t>СЗАП, МАЗ-8926, Нефаз, Тонар, ГКБ-8350, Krone, Schmitz, CIMC</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Всё как у прицепа, плюс диаметр шкворня; нагрузка на седло, кг; подъёмные и управляемые оси; конструкция (рамный, безрамный)</t>
+          <t>Тип прицепа (лист «Типы прицепов»); число осей; полная масса, кг; снаряжённая масса, кг; тормоза; подвеска; сцепное устройство; размерность шин</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Цистерна, рефрижератор, самосвальный, контейнеровоз. Трал — цельный полуприцеп собственной конструкции, без модуля</t>
+          <t>Описывается типом, модуль не заводится</t>
         </is>
       </c>
     </row>
@@ -2213,32 +2880,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Тракторный прицеп</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>R1–R4</t>
+          <t>O3, O4</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Прицеп или полуприцеп к трактору.</t>
+          <t>Опирается на седло тягача шкворнем, передней оси нет. Бывает безрамным — несущая цистерна.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2ПТС-4/6, 1ПТС-9, ПСТ-6/9/12, ПСЕ-12,5, МЖТ</t>
+          <t>МАЗ-9397/9758, Нефаз-9334, Тонар, ЧМЗАП, Schmitz, Krone, Kögel, Wielton, CIMC</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; самосвальный или бортовой; объём кузова, м³; скоростной индекс (a, b)</t>
+          <t>Всё как у прицепа, плюс диаметр шкворня; нагрузка на седло, кг; подъёмные и управляемые оси; конструкция (рамный, безрамный — свойство, а не отдельный вид)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Цистерна для жидких удобрений, водовозка</t>
+          <t>Описывается типом: цистерна, рефрижератор, самосвальный, контейнеровоз, трал</t>
         </is>
       </c>
     </row>
@@ -2250,69 +2917,69 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Прицепная машина</t>
+          <t>Тракторный прицеп</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>S (по Регламенту ЕС 167/2013)</t>
+          <t>R1–R4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Рабочее орудие на своей транспортной оси (решение: со своими колёсами — прицеп).</t>
+          <t>Прицеп или полуприцеп к трактору.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Прицепная сеялка СЗ-3,6, опрыскиватель ОП-2000, пресс-подборщик ПРФ-180, косилка КДН, разбрасыватель РОУ, кормораздатчик КТУ-10, борона БДТ-7, прицепной скрепер ДЗ-111</t>
+          <t>2ПТС-4/6, 1ПТС-9, ПСТ-6/9/12, ПСЕ-12,5, МЖТ</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Вид машины; ширина захвата, м; ёмкость бака или бункера; привод от ВОМ</t>
+          <t>Тип прицепа; грузоподъёмность, т; объём кузова, м³; скоростной индекс (a, b)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Виды — на листе «Прицепные машины»</t>
+          <t>Цистерна для жидких удобрений, водовозка — типы</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина</t>
+          <t>Прицеп</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Трактор</t>
+          <t>Прицепная машина</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>T1–T5, C1–C5</t>
+          <t>S (по Регламенту ЕС 167/2013)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Работает сам по себе и несёт навесное оборудование — тогда он база.</t>
+          <t>Рабочее орудие на своей транспортной оси (решение: со своими колёсами — прицеп).</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>МТЗ «Беларус», ЮМЗ-6, Т-40, Т-150К, К-700, ДТ-75, Т-130/170, LOVOL, YTO</t>
+          <t>Прицепная сеялка СЗ-3,6, опрыскиватель ОП-2000, пресс-подборщик ПРФ-180, косилка КДН, разбрасыватель РОУ, кормораздатчик КТУ-10, борона БДТ-7, прицепной скрепер ДЗ-111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Тяговый класс; колёсная формула или гусеничный ход; ВОМ; передняя и задняя навеска; моточасы</t>
+          <t>Общие поля прицепа плюс: вид машины; ширина захвата, м; ёмкость бака или бункера; привод от ВОМ</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Навесной экскаватор, бульдозерный отвал, погрузчик ПКУ, траншеекопатель</t>
+          <t>Виды — на листе «Прицепные машины»</t>
         </is>
       </c>
     </row>
@@ -2324,37 +2991,74 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>Трактор</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>T1–T5, C1–C5</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Работает сам по себе и несёт навесное оборудование — тогда он база.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ «Беларус», ЮМЗ-6, Т-40, Т-150К, К-700, ДТ-75, Т-130/170, LOVOL, YTO</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Тяговый класс; колёсная формула или гусеничный ход; ВОМ; передняя и задняя навеска; моточасы</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Навесной экскаватор, бульдозерный отвал, погрузчик ПКУ, траншеекопатель</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Самоходная машина</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>Вездеходное шасси (транспортёр)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>AII, AIII, E</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Гусеничный или колёсный ход сверхвысокой проходимости, учёт как самоходной машины.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>ГАЗ-71/34039, МТ-ЛБ, ТМ-140, «Витязь», ТРЭКОЛ, Шерп</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Тип движителя; давление на грунт; плавающий; исходная модель и документ о переоборудовании</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Буровая, ППУ, кунг связи, медпункт, манипулятор</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3237,7 +3941,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3260,7 +3964,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3283,7 +3987,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3310,7 +4014,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3333,7 +4037,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -3360,7 +4064,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3387,7 +4091,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3487,7 +4191,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3514,7 +4218,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>полуприцеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3537,7 +4241,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3560,7 +4264,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3583,7 +4287,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3606,7 +4310,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3683,7 +4387,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3706,7 +4410,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3729,7 +4433,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3752,7 +4456,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3775,7 +4479,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ, прицеп</t>
+          <t>ЛК, СТ, ТТ</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3798,7 +4502,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3821,7 +4525,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3844,7 +4548,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3867,7 +4571,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3963,7 +4667,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3986,7 +4690,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ТТ, прицеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4105,7 +4809,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ТТ, полуприцеп</t>
+          <t>ТТ</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4367,12 +5071,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Оборудование (передний отвал, боковой отвал, щётка, пескоразбрасыватель, поливомоечное); объём бункера, м³; объём цистерны, м³; ширина обработки, м</t>
+          <t>Гидравлика для сменного оборудования; места навески (переднее, среднее, заднее)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Один модуль со списком оборудования</t>
+          <t>Отвалы, щётка, пескоразбрасыватель, поливомоечная цистерна — навесное оборудование отдельными записями, а не поля модуля</t>
         </is>
       </c>
     </row>
@@ -4815,7 +5519,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп, автобус</t>
+          <t>СТ, ТТ, автобус</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4999,7 +5703,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, прицеп</t>
+          <t>СТ, ТТ</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5072,7 +5776,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, прицеп</t>
+          <t>ЛК, СТ</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5736,7 +6440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5791,7 +6495,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Объём основного ковша, м³; глубина копания, м; радиус копания, м; тип стрелы; ширина башмака, мм; быстросъём</t>
+          <t>Глубина копания, м; радиус копания, м; тип стрелы; ширина башмака, мм; быстросъём</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5872,7 +6576,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Объём ковша погрузчика, м³; объём ковша экскаватора, м³; глубина копания, м; грузоподъёмность погрузчика, т; телескопическая рукоять; привод 2WD/4WD</t>
+          <t>Глубина копания, м; грузоподъёмность погрузчика, т; телескопическая рукоять; привод 2WD/4WD (ковши — навесное оборудование)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5916,20 +6620,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Скрепер самоходный</t>
+          <t>Думпер (мини-самосвал)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Объём ковша, м³; ширина резания, м; глубина резания, мм</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; объём ковша, м³; опрокидывание (вперёд, поворотное); самозагрузка</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Wacker Neuson, Ausa, Thwaites, китайские аналоги</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5939,17 +6647,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Траншеекопатель</t>
+          <t>Скрепер самоходный</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>гусеничная, колёсная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Глубина траншеи, м; ширина, мм; рабочий орган (баровый, цепной, роторный)</t>
+          <t>Объём ковша, м³; ширина резания, м; глубина резания, мм</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -5957,29 +6665,25 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Погрузочные</t>
+          <t>Землеройные</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Фронтальный погрузчик</t>
+          <t>Траншеекопатель</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная, колёсная</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём основного ковша, м³; высота выгрузки, м; кинематика стрелы; быстросъём</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Амкодор 332/342, XCMG LW, SDLG L956, LiuGong 855, Shantui SL50, CAT 950</t>
-        </is>
-      </c>
+          <t>Глубина траншеи, м; ширина, мм; рабочий орган (баровый, цепной, роторный)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5989,22 +6693,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Мини-погрузчик</t>
+          <t>Фронтальный погрузчик</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, кг; опрокидывающая нагрузка, кг; высота до шарнира, м; тип стрелы; расход вспомогательной гидравлики, л/мин</t>
+          <t>Грузоподъёмность, т; высота выгрузки, м; кинематика стрелы; быстросъём</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Bobcat S/T, МКСМ-800, Case SR, XCMG XC7</t>
+          <t>Амкодор 332/342, XCMG LW, SDLG L956, LiuGong 855, Shantui SL50, CAT 950</t>
         </is>
       </c>
     </row>
@@ -6016,22 +6720,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Телескопический погрузчик</t>
+          <t>Мини-погрузчик</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; высота подъёма, м; вылет, м; стабилизаторы; поворотная платформа</t>
+          <t>Грузоподъёмность, кг; опрокидывающая нагрузка, кг; высота до шарнира, м; тип стрелы; расход вспомогательной гидравлики, л/мин</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>JCB 531/540, Manitou, Merlo</t>
+          <t>Bobcat S/T, МКСМ-800, Case SR, XCMG XC7</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6747,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик</t>
+          <t>Телескопический погрузчик</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6053,12 +6757,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; высота подъёма, м; тип мачты; привод (дизель, газ, электро); аккумулятор (напряжение, ёмкость, год); боковой сдвиг вил</t>
+          <t>Грузоподъёмность, т; высота подъёма, м; вылет, м; стабилизаторы; поворотная платформа</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>HELI, Hangcha, Toyota, Linde, Балканкар</t>
+          <t>JCB 531/540, Manitou, Merlo</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6774,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Ричстакер</t>
+          <t>Вилочный погрузчик</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6080,12 +6784,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность по рядам, т; ярусов; спредер (20/40 футов)</t>
+          <t>Грузоподъёмность, т; высота подъёма, м; тип мачты; привод (дизель, газ, электро); аккумулятор (напряжение, ёмкость, год); боковой сдвиг вил</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Kalmar, Konecranes, SANY</t>
+          <t>HELI, Hangcha, Toyota, Linde, Балканкар</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6801,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Самоходный штабелёр</t>
+          <t>Ричстакер</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6107,20 +6811,24 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, кг; высота подъёма, м; площадка оператора</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность по рядам, т; ярусов; спредер (20/40 футов)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Kalmar, Konecranes, SANY</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Дорожные</t>
+          <t>Погрузочные</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Автогрейдер</t>
+          <t>Самоходный штабелёр</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -6130,14 +6838,10 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Длина отвала, м; колёсная формула (1×2×3, 1×3×3); передний отвал или кирковщик; задний рыхлитель</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>ДЗ-98, ГС-14.02, XCMG GR, SDLG G9190, CAT 140</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность, кг; высота подъёма, м; площадка оператора</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6147,20 +6851,24 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Каток грунтовый</t>
+          <t>Автогрейдер</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>вальцовая + пневмоколёса</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ширина вальца, мм; валец (гладкий, кулачковый); частота вибрации, Гц; амплитуда, мм; центробежная сила, кН</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>Длина отвала, м; колёсная формула (1×2×3, 1×3×3); передний отвал или кирковщик; задний рыхлитель</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>ДЗ-98, ГС-14.02, XCMG GR, SDLG G9190, CAT 140</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -6170,24 +6878,20 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Каток асфальтовый</t>
+          <t>Каток грунтовый</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>вальцовая</t>
+          <t>вальцовая + пневмоколёса</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ширина вальца, мм; вибрация или осцилляция; орошение</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Тандемный, комбинированный</t>
-        </is>
-      </c>
+          <t>Ширина вальца, мм; валец (гладкий, кулачковый); частота вибрации, Гц; амплитуда, мм; центробежная сила, кН</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -6197,20 +6901,24 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Каток пневмоколёсный</t>
+          <t>Каток асфальтовый</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>вальцовая</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Масса с балластом, т; шин; ширина уплотнения, мм</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>Ширина вальца, мм; вибрация или осцилляция; орошение</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Тандемный, комбинированный</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -6220,17 +6928,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Асфальтоукладчик</t>
+          <t>Каток пневмоколёсный</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>гусеничная, колёсная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ширина укладки min/max, м; толщина слоя, мм; производительность, т/ч; выглаживающая плита; бункер, т</t>
+          <t>Масса с балластом, т; шин; ширина уплотнения, мм</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -6243,7 +6951,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Дорожная фреза</t>
+          <t>Асфальтоукладчик</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6253,7 +6961,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ширина фрезерования, мм; глубина, мм; конвейер</t>
+          <t>Ширина укладки min/max, м; толщина слоя, мм; производительность, т/ч; выглаживающая плита; бункер, т</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -6266,17 +6974,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Ресайклер (стабилизатор грунта)</t>
+          <t>Дорожная фреза</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная, колёсная</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ширина обработки, мм; глубина, мм; дозирование вяжущего</t>
+          <t>Ширина фрезерования, мм; глубина, мм; конвейер</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -6284,29 +6992,25 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Дорожные</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Кран гусеничный</t>
+          <t>Ресайклер (стабилизатор грунта)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; длина стрелы, м; гусек, м; тип стрелы (решётчатая, телескопическая); учётный номер в надзоре</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>РДК-250, ДЭК-251, SANY SCC, XCMG XGC</t>
-        </is>
-      </c>
+          <t>Ширина обработки, мм; глубина, мм; дозирование вяжущего</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -6316,22 +7020,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Кран пневмоколёсный (короткобазовый)</t>
+          <t>Кран гусеничный</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Как у гусеничного; выносные опоры</t>
+          <t>Грузоподъёмность, т; длина стрелы, м; гусек, м; тип стрелы (решётчатая, телескопическая); учётный номер в надзоре</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>КС-5363, rough-terrain</t>
+          <t>РДК-250, ДЭК-251, SANY SCC, XCMG XGC</t>
         </is>
       </c>
     </row>
@@ -6343,22 +7047,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Трубоукладчик</t>
+          <t>Кран пневмоколёсный (короткобазовый)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; момент устойчивости, т·м; вылет, м</t>
+          <t>Как у гусеничного; выносные опоры</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ТГ-124, Komatsu D355C</t>
+          <t>КС-5363, rough-terrain</t>
         </is>
       </c>
     </row>
@@ -6370,47 +7074,51 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Самоходный подъёмник</t>
+          <t>Трубоукладчик</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Тип (ножничный, коленчатый, телескопический); рабочая высота, м; вылет, м; грузоподъёмность, кг; привод</t>
+          <t>Грузоподъёмность, т; момент устойчивости, т·м; вылет, м</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Genie, JLG, Haulotte, Dingli</t>
+          <t>ТГ-124, Komatsu D355C</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Горные</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Погрузочно-доставочная машина</t>
+          <t>Самоходный подъёмник</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём ковша, м³; привод (дизель, кабель)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>Тип (ножничный, коленчатый, телескопический); рабочая высота, м; вылет, м; грузоподъёмность, кг; привод</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Genie, JLG, Haulotte, Dingli</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6420,7 +7128,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Карьерный самосвал</t>
+          <t>Погрузочно-доставочная машина</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -6430,14 +7138,10 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём кузова, м³; трансмиссия (механическая, гидромеханическая, электромеханическая)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>БелАЗ, Komatsu HD, CAT 770–777; сочленённый (Volvo A30, Bell) — сюда же</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность, т; объём ковша, м³; привод (дизель, кабель)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6447,47 +7151,51 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Буровой станок карьерный</t>
+          <t>Карьерный самосвал</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Диаметр бурения, мм; глубина, м; тип (шарошечный, пневмоударный, погружной); компрессор, м³/мин</t>
+          <t>Грузоподъёмность, т; объём кузова, м³; трансмиссия (механическая, гидромеханическая, электромеханическая)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>СБШ-250, Epiroc</t>
+          <t>БелАЗ, Komatsu HD, CAT 770–777; сочленённый (Volvo A30, Bell) — сюда же</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Лесные</t>
+          <t>Горные</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Харвестер</t>
+          <t>Буровой станок карьерный</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Вылет манипулятора, м; харвестерная головка; диаметр среза, см</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Диаметр бурения, мм; глубина, м; тип (шарошечный, пневмоударный, погружной); компрессор, м³/мин</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>СБШ-250, Epiroc</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6497,17 +7205,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Форвардер</t>
+          <t>Харвестер</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; площадь коника, м²; вылет, м</t>
+          <t>Вылет манипулятора, м; харвестерная головка; диаметр среза, см</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -6520,49 +7228,45 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Трелёвочный трактор</t>
+          <t>Форвардер</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>гусеничная, колёсная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Трелёвочное оборудование; тяговое усилие лебёдки, кН</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>ТДТ-55, ЛТ-154</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность, т; площадь коника, м²; вылет, м</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Лесные</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Трактор колёсный</t>
+          <t>Трелёвочный трактор</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная, колёсная</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Тяговый класс (ГОСТ 27021-86); колёсная формула; ВОМ, об/мин; задняя навеска (категория); передняя навеска</t>
+          <t>Трелёвочное оборудование; тяговое усилие лебёдки, кН</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>МТЗ-80/82/1221, Т-150К, К-700, LOVOL, John Deere</t>
+          <t>ТДТ-55, ЛТ-154</t>
         </is>
       </c>
     </row>
@@ -6574,22 +7278,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Трактор гусеничный</t>
+          <t>Трактор колёсный</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Тяговый класс; тип гусениц; колея, мм</t>
+          <t>Тяговый класс (ГОСТ 27021-86); колёсная формула; ВОМ, об/мин; задняя навеска (категория); передняя навеска</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ДТ-75, Т-4А</t>
+          <t>МТЗ-80/82/1221, Т-150К, К-700, LOVOL, John Deere</t>
         </is>
       </c>
     </row>
@@ -6601,22 +7305,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Комбайн зерноуборочный</t>
+          <t>Трактор гусеничный</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки</t>
+          <t>Тяговый класс; тип гусениц; колея, мм</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Нива, Енисей, Дон-1500, Акрос, Палессе, Claas</t>
+          <t>ДТ-75, Т-4А</t>
         </is>
       </c>
     </row>
@@ -6628,22 +7332,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Комбайн кормоуборочный</t>
+          <t>Комбайн зерноуборочный</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Мощность; ножей измельчителя</t>
+          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки (жатка — навесное оборудование отдельной записью)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Дон-680, Палессе FS, Claas Jaguar</t>
+          <t>Нива, Енисей, Дон-1500, Акрос, Палессе, Claas</t>
         </is>
       </c>
     </row>
@@ -6655,7 +7359,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Самоходный опрыскиватель</t>
+          <t>Комбайн кормоуборочный</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -6665,10 +7369,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Ёмкость бака, л; ширина штанги, м; клиренс, мм</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Мощность; ножей измельчителя</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Дон-680, Палессе FS, Claas Jaguar</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6678,7 +7386,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Самоходная косилка</t>
+          <t>Самоходный опрыскиватель</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -6688,39 +7396,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Ширина захвата, м; плющилка</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>КСУ-1, Палессе CS</t>
-        </is>
-      </c>
+          <t>Ёмкость бака, л; ширина штанги, м; клиренс, мм</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Вездеходы</t>
+          <t>Сельскохозяйственные</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Снегоболотоход</t>
+          <t>Самоходная косилка</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Полная масса, т; мест; грузоподъёмность, т; плавающий</t>
+          <t>Ширина захвата, м; плющилка</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ТРЭКОЛ, Шерп, Бурлак</t>
+          <t>КСУ-1, Палессе CS</t>
         </is>
       </c>
     </row>
@@ -6732,49 +7436,49 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Гусеничный транспортёр</t>
+          <t>Снегоболотоход</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; буксируемая масса, т; мест; плавающий; исходная модель; переоборудование (вид, документ)</t>
+          <t>Полная масса, т; мест; грузоподъёмность, т; плавающий</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>МТ-ЛБ, ГАЗ-71, ГТ-Т, «Витязь»</t>
+          <t>ТРЭКОЛ, Шерп, Бурлак</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Вездеходы</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Самоходная подметальная машина</t>
+          <t>Гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ширина подметания, м; бункер, л; увлажнение</t>
+          <t>Грузоподъёмность, т; буксируемая масса, т; мест; плавающий; исходная модель; переоборудование (вид, документ)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Tennant, Hako</t>
+          <t>МТ-ЛБ, ГАЗ-71, ГТ-Т, «Витязь»</t>
         </is>
       </c>
     </row>
@@ -6786,27 +7490,54 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
+          <t>Самоходная подметальная машина</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>колёсная</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Ширина подметания, м; бункер, л; увлажнение</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Tennant, Hako</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Коммунальные</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>Коммунальный минитрактор</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>колёсная</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Мощность; передняя навеска; ВОМ</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Беларус-132Н, Holder</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E41"/>
+  <autoFilter ref="A1:E42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7095,7 +7826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8053,59 +8784,113 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Сменные кузова</t>
+          <t>Дорожные и коммунальные</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Контейнер мультилифта</t>
+          <t>Пескоразбрасыватель сменный</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Перевозка</t>
+          <t>Разбрасывание песка и реагентов</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Мультилифт</t>
+          <t>КДМ, малое коммунальное шасси</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Вид (самосвальный, мусорный, цистерна, бытовка); объём, м³</t>
+          <t>Объём бункера, м³; ширина распределения, м</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>Дорожные и коммунальные</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Поливомоечное оборудование сменное</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Полив и мойка</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>КДМ, малое коммунальное шасси</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>Сменные кузова</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Контейнер мультилифта</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Мультилифт</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Вид (самосвальный, мусорный, цистерна, бытовка); объём, м³</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Сменные кузова</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Бункер бункеровоза</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Мусор</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Бункеровоз</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Объём, м³</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E37"/>
+  <autoFilter ref="A1:E39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -16,29 +16,27 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля самоходной машины" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навесное и сменное" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля навесного" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Типы прицепов" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Модули'!$A$1:$E$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Модули'!$A$1:$D$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Самоходные машины'!$A$1:$E$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля самоходной машины'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Типы прицепов'!$A$1:$C$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Решения'!$A$1:$C$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Источники'!$A$1:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Решения'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Источники'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -514,683 +512,306 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Каждая единица относится ровно к одному виду: колёсное ТС (база + модули), прицеп или полуприцеп (тип), самоходная машина собственной конструкции, сменное навесное оборудование.</t>
+          <t>Каждая единица относится ровно к одному виду: колёсное ТС (база + модули), прицеп или полуприцеп (база + модули), самоходная машина собственной конструкции, сменное навесное оборудование.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1а</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>База и модуль</t>
+          <t>Категория из техпаспорта</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Спецоборудование, смонтированное на шасси, — модуль. Модуль записывается отдельно от базы всегда, в том числе когда его не переставляют (самосвальный кузов, бортовая платформа, пожарная надстройка): на ту же базу могли поставить другой модуль. Штатный кузов цельнометаллического фургона без переоборудования — «Базовый модуль». Шасси без надстройки или с демонтированной надстройкой — «модуль отсутствует».</t>
+          <t>Категория базы берётся из техпаспорта, как её там и написали: легковое, грузовое, автобусы, мототехника, прицепы и полуприцепы, спецтехника. Внутри категории выбирается база (лист «Базы»).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2б</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Прицепы — типом</t>
+          <t>База и модуль</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Прицеп и полуприцеп описываются ТИПОМ (цистерна, рефрижератор, самосвальный, трал, прицепная машина), а не базой с модулем: рама сама по себе модульности не создаёт. Тот же агрегат, смонтированный на шасси, — модуль: передвижная АЗС, электростанция, компрессор бывают и типом прицепа, и модулем.</t>
+          <t>Спецоборудование, смонтированное на шасси, — модуль. Модуль записывается отдельно от базы всегда, в том числе когда его не переставляют (самосвальный кузов, бортовая платформа, пожарная надстройка): на ту же базу могли поставить другой модуль. Штатный кузов цельнометаллического фургона без переоборудования — «Базовый модуль». Шасси без надстройки или с демонтированной надстройкой — «модуль отсутствует».</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2в</t>
+          <t>2а</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Навесное вместо полей</t>
+          <t>Где модульность</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Ковши, вилы, жатки, отвалы, щётки, бункеры — всегда навесное оборудование отдельной записью, даже когда пришли вместе с машиной. В поля машины они не выносятся.</t>
+          <t>Модульность — только когда машина построена на серийном продукте (серийное шасси, серийный трактор). Изделие, созданное целиком, а не на базе серийного, — цельное, без деления на базу и модуль.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2г</t>
+          <t>2б</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Что не входит</t>
+          <t>Модуль на любую базу</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Малая механизация с оператором — виброплита, ручной виброкаток и подобное — инструмент, а не техника: в классификатор не входит. Самодельные и кустарные надстройки не учитываются.</t>
+          <t>Ограничений «этот модуль только на такое шасси» нет: цистерна, рефрижератор, самосвальный кузов, низкорамная платформа ставятся и на грузовое шасси, и на прицеп, и на полуприцеп. База и модуль выбираются независимо друг от друга.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2а</t>
+          <t>2в</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Где модульность</t>
+          <t>Навесное вместо полей</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Модульность — только когда машина построена на серийном продукте (серийное шасси, серийный трактор). Изделие, созданное целиком, а не на базе серийного, — цельное, без деления на базу и модуль.</t>
+          <t>Ковши, вилы, жатки, отвалы, щётки, бункеры — всегда навесное оборудование отдельной записью, даже когда пришли вместе с машиной. В поля машины они не выносятся.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2г</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Несколько модулей</t>
+          <t>Что не входит</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>На базе может стоять несколько модулей, каждый записывается отдельно: КамАЗ + бортовая платформа + кран-манипулятор — база и два модуля. Название машины складывается из модулей.</t>
+          <t>Малая механизация с оператором — виброплита, ручной виброкаток и подобное — инструмент, а не техника: в классификатор не входит. Самодельные и кустарные надстройки не учитываются.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Отдельный модуль или параметр</t>
+          <t>Несколько модулей</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Отдельный модуль — у оборудования есть свой изготовитель и заводской номер (или свой учёт в надзоре) и его можно снять, не разрушив соседний модуль. Иначе это параметр модуля: секции цистерны, насос бензовоза, тент бортовой платформы.</t>
+          <t>На базе может стоять несколько модулей, каждый записывается отдельно: КамАЗ + бортовая платформа + кран-манипулятор — база и два модуля. Название машины складывается из модулей.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина</t>
+          <t>Отдельный модуль или параметр</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись, параметры рабочего органа — поля машины.</t>
+          <t>Отдельный модуль — у оборудования есть свой изготовитель и заводской номер (или свой учёт в надзоре) и его можно снять, не разрушив соседний модуль. Иначе это параметр модуля: секции цистерны, насос бензовоза, тент бортовой платформы.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Трактор как база</t>
+          <t>Самоходная машина</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Оборудование на тракторе, который сам по себе работает как трактор, — модуль на базе «Трактор»: навесной экскаватор на МТЗ, бульдозерный отвал на ДТ-75, погрузчик ПКУ-0,8. Отдельной записи «экскаватор» при этом не заводится — это трактор с модулем.</t>
+          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись, параметры рабочего органа — поля машины.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Прицеп или навесное</t>
+          <t>Трактор как база</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Есть свои колёса — прицеп (тип «прицепная машина»): прицепная сеялка, пресс-подборщик, плуг на колёсах. Без колёс — навесное оборудование: навесной плуг, отвал, ковш.</t>
+          <t>Оборудование на тракторе, который сам по себе работает как трактор, — модуль на базе «Трактор»: навесной экскаватор на МТЗ, бульдозерный отвал на ДТ-75, погрузчик ПКУ-0,8. Отдельной записи «экскаватор» при этом не заводится — это трактор с модулем.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Сменное навесное</t>
+          <t>Прицеп или навесное</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Оборудование, которое ставится штатно и поочерёдно (быстросъём, трёхточечная навеска), — отдельная запись со связью «установлено на». Оценивается и в составе машины, и отдельно. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
+          <t>Есть свои колёса — прицеп (база «Прицепная машина»): прицепная сеялка, пресс-подборщик, плуг на колёсах. Без колёс — навесное оборудование: навесной плуг, отвал, ковш.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Кран на шасси</t>
+          <t>Сменное навесное</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Автокран на автомобильном шасси: база «Тяжёлый грузовик» + модуль «Автокран». Кран на собственном крановом спецшасси: база «Специальное многоосное шасси» + тот же модуль — это другой класс. Гусеничный и пневмоколёсный кран — самоходные машины.</t>
+          <t>Оборудование, которое ставится штатно и поочерёдно (быстросъём, трёхточечная навеска), — отдельная запись со связью «установлено на». Оценивается и в составе машины, и отдельно. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Тягач и полуприцеп</t>
+          <t>Кран на шасси</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Седельный тягач и полуприцеп — две записи. Седельно-сцепное устройство — часть базы тягача. У полуприцепа указывается тип (цистерна, рефрижератор, самосвальный).</t>
+          <t>Автокран на автомобильном шасси: база «Тяжёлый грузовик» + модуль «Автокран». Кран на собственном крановом спецшасси: база «Специальное многоосное шасси» + тот же модуль — это другой класс. Гусеничный и пневмоколёсный кран — самоходные машины.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Контейнеры и адаптеры</t>
+          <t>Тягач и полуприцеп</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Сменные контейнеры мультилифта, бункеры бункеровоза, жатки комбайна — сменное оборудование, отдельные записи, а не модуль ТС.</t>
+          <t>Седельный тягач и полуприцеп — две записи. Седельно-сцепное устройство — часть базы тягача. У полуприцепа указывается свой модуль (цистерна, рефрижератор, самосвальный кузов) — так же, как у шасси.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Полный привод</t>
+          <t>Контейнеры и адаптеры</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Полный привод — признак базы («повышенной проходимости», колёсная формула), а не отдельная категория: Урал-4320 — тяжёлый грузовик с признаком полного привода.</t>
+          <t>Сменные контейнеры мультилифта, бункеры бункеровоза, жатки комбайна — сменное оборудование, отдельные записи, а не модуль ТС.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Полный привод</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Полный привод — признак базы («повышенной проходимости», колёсная формула), а не отдельная категория: Урал-4320 — тяжёлый грузовик с признаком полного привода.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Масса</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Полная масса базы — по документу шасси, полная масса машины целиком — по СТС. Категория базы определяется по массе, а не по модели: Sprinter на 5 т — среднетоннажный.</t>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Полная масса базы — по документу шасси, полная масса машины целиком — по СТС. База внутри категории выбирается по массе, а не по модели: Sprinter на 5 т — среднетоннажный.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Назначение</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Поля сверх общих полей прицепа</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Бортовой</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Платформа с бортами</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Длина, ширина, высота бортов, мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Тентованный</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Платформа с каркасом и тентом</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; способ загрузки; европаллет</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Самосвальный</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Кузов с опрокидыванием</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; разгрузка (назад, на три стороны, вбок)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Цистерна</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Наливные и сыпучие грузы</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Продукт; объём, м³; секций; материал; насос; класс ДОПОГ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Изотермический</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Утеплённый фургон без охлаждения</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; класс изотермии</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Рефрижератор</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Фургон с холодильной установкой</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; класс ATP; установка: марка, номер, моточасы</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Фургон промтоварный</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Закрытый кузов</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Внутренние размеры; объём, м³; гидроборт</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Контейнеровоз</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Платформа под контейнеры</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Контейнеры (20, 40, 45 футов); фитинговых замков</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Трал (низкорамный)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Перевозка техники</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; погрузочная высота, мм; аппарели; раздвижной</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Лесовоз, сортиментовоз</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Перевозка леса</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Коников; длина сортимента, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Автовоз</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Перевозка автомобилей</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Мест; ярусов</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Скотовоз</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Перевозка животных</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Ярусов; голов; поение; вентиляция</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Зерновоз</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Перевозка зерна</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; разгрузка</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Цементовоз (сыпучие)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Пневморазгрузка</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; компрессор, м³/мин</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Роспуск</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Для длинномеров</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; раздвижной</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Передвижная АЗС</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Заправка техники на месте</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; секций; насос; счётчик; раздаточных пистолетов</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Электростанция</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Автономное питание</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Мощность, кВт; напряжение; топливный бак, л; моточасы</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Компрессорная установка</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Сжатый воздух</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Производительность, м³/мин; давление, бар; моточасы</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Мотопомпа</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Перекачка воды</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Подача, л/мин; напор, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка (вагончик)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Бытовые помещения</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Мест; отопление; санузел</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Прицепная машина</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Сельхозорудие на своих колёсах</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Вид (лист «Прицепные машины»); ширина захвата, м</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C22"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1341,7 +962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1538,19 +1159,15 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Прицеп: полуприцеп, тип «трал»</t>
+          <t>База: полуприцеп</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Описывается типом, модуля нет</t>
-        </is>
-      </c>
+          <t>Модуль: низкорамная платформа (трал)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1560,17 +1177,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Прицеп: полуприцеп, тип «цистерна»</t>
+          <t>База: полуприцеп</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Модуль: цистерна по продукту (бензовоз)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>«Безрамный» — свойство полуприцепа</t>
+          <t>«Безрамный» — свойство базы</t>
         </is>
       </c>
     </row>
@@ -1582,17 +1199,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Прицеп, тип «передвижная АЗС»</t>
+          <t>База: прицеп</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Модуль: передвижная АЗС</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>На шасси та же АЗС была бы модулем</t>
+          <t>Тот же модуль ставится и на шасси</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1279,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Две записи: седельный тягач; полуприцеп типа «цистерна»</t>
+          <t>Две записи: седельный тягач; полуприцеп</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Модуль полуприцепа: бензовоз</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1824,13 +1441,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1970,170 +1587,187 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Полуприцеп типа «трал»: прицеп описывается типом, модуля нет</t>
+          <t>База «Полуприцеп» + модуль «Низкорамная платформа (трал)»</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Кран на собственном шасси</t>
+          <t>Категория базы</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Liebherr LTM</t>
+          <t>Техпаспорт: «грузовой», «прицеп», «спецтехника»</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>База + модуль: на ту же базу могли поставить другой модуль</t>
+          <t>Категория берётся из техпаспорта и не выводится из надстройки: автокран на шасси КамАЗ — грузовое с модулем «Автокран», а не спецтехника</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Прицепы и полуприцепы</t>
+          <t>Кран на собственном шасси</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Полуприцеп-цистерна, трал, прицеп-АЗС</t>
+          <t>Liebherr LTM</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Описываются типом прицепа; рама модульности не создаёт. Тот же агрегат на шасси — модуль</t>
+          <t>База + модуль: на ту же базу могли поставить другой модуль</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Безрамная цистерна</t>
+          <t>Прицепы и полуприцепы</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Полуприцеп с несущей цистерной</t>
+          <t>Полуприцеп-цистерна, трал, прицеп-АЗС</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Полуприцеп типа «цистерна», «безрамный» — свойство</t>
+          <t>Прицеп и полуприцеп — такая же база, как шасси: категория из техпаспорта, сверху модуль. Один и тот же модуль ставится на любую базу</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Ковш, вилы, жатка</t>
+          <t>Безрамная цистерна</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Штатный ковш экскаватора, жатка комбайна</t>
+          <t>Полуприцеп с несущей цистерной</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Навесное оборудование отдельной записью, в поля машины не выносится</t>
+          <t>База «Полуприцеп» + модуль-цистерна; «безрамный» — свойство базы</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Комбинированная дорожная машина</t>
+          <t>Ковш, вилы, жатка</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>КДМ с отвалом, щёткой и разбрасывателем</t>
+          <t>Штатный ковш экскаватора, жатка комбайна</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Модуль КДМ, а отвал, щётка и бункер — навесное оборудование</t>
+          <t>Навесное оборудование отдельной записью, в поля машины не выносится</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Лестница пожарной автоцистерны</t>
+          <t>Комбинированная дорожная машина</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>АЦЛ</t>
+          <t>КДМ с отвалом, щёткой и разбрасывателем</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Параметр модуля, отдельным модулем не заводится</t>
+          <t>Модуль КДМ, а отвал, щётка и бункер — навесное оборудование</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Трактор с навесным экскаватором</t>
+          <t>Лестница пожарной автоцистерны</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>МТЗ-82 + ЭО-2621</t>
+          <t>АЦЛ</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Трактор + модуль «экскаваторное оборудование»; отдельной записи «экскаватор» нет</t>
+          <t>Параметр модуля, отдельным модулем не заводится</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Малая механизация</t>
+          <t>Трактор с навесным экскаватором</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Виброплита с оператором, ручной виброкаток</t>
+          <t>МТЗ-82 + ЭО-2621</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Инструмент, в классификатор не входит</t>
+          <t>Трактор + модуль «экскаваторное оборудование»; отдельной записи «экскаватор» нет</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Малая механизация</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Виброплита с оператором, ручной виброкаток</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Инструмент, в классификатор не входит</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Самодельные надстройки</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Бочка на раме, гаражный кунг</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Не учитываются: переоборудование незаконно</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2188,7 +1822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2453,27 +2087,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Вид</t>
+          <t>Категория (техпаспорт)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Категория базы</t>
+          <t>База</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2494,18 +2127,13 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Поля сверх общих</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Что на ней строят</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Легковое</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2531,18 +2159,13 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Тип кузова (седан, универсал, внедорожник, пикап)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Патрульная, служебная, сопровождения</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Грузовое</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2568,425 +2191,365 @@
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Исполнение базы; монтажная длина рамы, мм; высота крыши; длина кузова (L1–L4)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Скорая, лаборатория, автовышка малая, эвакуатор лёгкий, автолавка</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Грузовое</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Малое коммунальное шасси</t>
+          <t>Среднетоннажный грузовик (3,5–12 т)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>N1, N2</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Компактный носитель сменного коммунального оборудования: отвал, щётка, бункер, поливалка. Не лёгкий коммерческий и не трактор.</t>
+          <t>Две оси, обычно 4×2, кабина капотная или бескапотная.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Multicar и китайские аналоги, коммунальные минишасси</t>
+          <t>ГАЗ-3307/3309, ГАЗон Next, ЗИЛ-130/5301/4331, МАЗ-4371, Isuzu NQR/NPR, Hyundai HD-65/78/120, Mitsubishi Canter, Hino 300, FAW, Foton</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Монтажная длина рамы, мм; передняя навеска; гидровыводы</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Коммунальное сменное оборудование</t>
+          <t>Монтажная длина рамы, мм; высота рамы, мм</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Грузовое</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Среднетоннажный грузовик (3,5–12 т)</t>
+          <t>Тяжёлый грузовик (свыше 12 т)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Две оси, обычно 4×2, кабина капотная или бескапотная.</t>
+          <t>2–4 оси, 4×2, 6×4, 8×4; бескапотная кабина.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ГАЗ-3307/3309, ГАЗон Next, ЗИЛ-130/5301/4331, МАЗ-4371, Isuzu NQR/NPR, Hyundai HD-65/78/120, Mitsubishi Canter, Hino 300, FAW, Foton</t>
+          <t>КамАЗ-5320/65115/6520, МАЗ-5516/6501, Howo, Shacman, FAW, Dongfeng, MAN TGS, Volvo FM, Scania, Mercedes Actros/Arocs</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Монтажная длина рамы, мм; высота рамы, мм</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Мусоровоз, автовышка до 22 м, КДМ, цистерна до 6 м³, лёгкий автокран</t>
+          <t>Нагрузка на заднюю тележку, кг; тип подвески тележки; число ведущих осей; подъёмная ось</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Грузовое</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Тяжёлый грузовик (свыше 12 т)</t>
+          <t>Седельный тягач</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2, N3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2–4 оси, 4×2, 6×4, 8×4; бескапотная кабина.</t>
+          <t>Короткая рама, седельно-сцепное устройство, без грузовой платформы.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ-5320/65115/6520, МАЗ-5516/6501, Howo, Shacman, FAW, Dongfeng, MAN TGS, Volvo FM, Scania, Mercedes Actros/Arocs</t>
+          <t>КамАЗ-5410/5490/65116, МАЗ-5440/6430, Volvo FH, Scania R, MAN TGX, Howo T7H, Shacman X3000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Нагрузка на заднюю тележку, кг; тип подвески тележки; число ведущих осей; подъёмная ось</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Самосвал, миксер, автокран на автошасси, бетононасос, КМУ, топливозаправщик</t>
+          <t>Высота седельного устройства, мм; нагрузка на седло, кг; полная масса автопоезда, кг; гидравлика для полуприцепа</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Автобусы</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Седельный тягач</t>
+          <t>Автобус</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>N2, N3</t>
+          <t>M2, M3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Короткая рама, седельно-сцепное устройство, без грузовой платформы.</t>
+          <t>Больше 8 пассажирских мест. Кузов-вагон или кузов стороннего завода на автобусном шасси — всё равно база целиком.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ-5410/5490/65116, МАЗ-5440/6430, Volvo FH, Scania R, MAN TGX, Howo T7H, Shacman X3000</t>
+          <t>ПАЗ, ЛиАЗ, МАЗ-103, Yutong, Higer, King Long, Hyundai County, Isuzu Novo</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Высота седельного устройства, мм; нагрузка на седло, кг; полная масса автопоезда, кг; гидравлика для полуприцепа</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Работает с полуприцепами — отдельными записями</t>
+          <t>Посадочных мест; общая вместимость; класс автобуса; расположение двигателя; высота пола; изготовитель кузова</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Мототехника</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Специальное многоосное шасси</t>
+          <t>Мототехника</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>N3, N3G</t>
+          <t>L1–L7</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Шасси спроектировано под конкретную машину и отдельно не продаётся: 3–9 осей, многоосное рулевое, выносные опоры в раме, часто вторая кабина. Марка шасси и крана обычно совпадают.</t>
+          <t>Мотоциклы, мотороллеры, квадрициклы.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Liebherr LTM, Grove GMK, Tadano, XCMG QAY, Zoomlion, SANY; МЗКТ «Волат»; «Ивановец», «Галичанин» на собственных спецшасси</t>
+          <t>Грузовые мотороллеры, квадроциклы</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Число управляемых осей; тип подвески (гидропневматическая, рессорная); максимальная скорость, км/ч; нагрузка на ось, кг</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Автокран тяжёлый, аэродромная пожарная, тяжёлая буровая</t>
+          <t>Тип (мотоцикл, мотороллер, квадрицикл)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Прицепы и полуприцепы</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Автобус</t>
+          <t>Прицеп</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>M2, M3</t>
+          <t>O1–O4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Больше 8 пассажирских мест. Кузов-вагон или кузов стороннего завода на автобусном шасси — всё равно база целиком.</t>
+          <t>Буксируется, своего двигателя нет; полный, центральноосный или роспуск.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ПАЗ, ЛиАЗ, МАЗ-103, Yutong, Higer, King Long, Hyundai County, Isuzu Novo</t>
+          <t>СЗАП, МАЗ-8926, Нефаз, Тонар, ГКБ-8350, Krone, Schmitz, CIMC</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Посадочных мест; общая вместимость; класс автобуса; расположение двигателя; высота пола; изготовитель кузова</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Передвижной медпункт, штаб — через модуль «спецоборудование салона»</t>
+          <t>Число осей; полная масса, кг; снаряжённая масса, кг; тормоза; подвеска; сцепное устройство; размерность шин</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Колёсное ТС</t>
+          <t>Прицепы и полуприцепы</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Мототехника</t>
+          <t>Полуприцеп</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>L1–L7</t>
+          <t>O3, O4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Мотоциклы, мотороллеры, квадрициклы.</t>
+          <t>Опирается на седло тягача шкворнем, передней оси нет. Бывает безрамным — несущая цистерна.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Грузовые мотороллеры, квадроциклы</t>
+          <t>МАЗ-9397/9758, Нефаз-9334, Тонар, ЧМЗАП, Schmitz, Krone, Kögel, Wielton, CIMC</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Тип (мотоцикл, мотороллер, квадрицикл)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Как база — редко</t>
+          <t>Всё как у прицепа, плюс диаметр шкворня; нагрузка на седло, кг; подъёмные и управляемые оси; конструкция (рамный, безрамный — свойство, а не отдельный вид)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>Прицепы и полуприцепы</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>Тракторный прицеп</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>O1–O4</t>
+          <t>R1–R4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Буксируется, своего двигателя нет; полный, центральноосный или роспуск.</t>
+          <t>Прицеп или полуприцеп к трактору.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>СЗАП, МАЗ-8926, Нефаз, Тонар, ГКБ-8350, Krone, Schmitz, CIMC</t>
+          <t>2ПТС-4/6, 1ПТС-9, ПСТ-6/9/12, ПСЕ-12,5, МЖТ</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Тип прицепа (лист «Типы прицепов»); число осей; полная масса, кг; снаряжённая масса, кг; тормоза; подвеска; сцепное устройство; размерность шин</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Описывается типом, модуль не заводится</t>
+          <t>Грузоподъёмность, т; объём кузова, м³; скоростной индекс (a, b)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>Прицепы и полуприцепы</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Полуприцеп</t>
+          <t>Прицепная машина</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>O3, O4</t>
+          <t>S (по Регламенту ЕС 167/2013)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Опирается на седло тягача шкворнем, передней оси нет. Бывает безрамным — несущая цистерна.</t>
+          <t>Рабочее орудие на своей транспортной оси (решение: со своими колёсами — прицеп).</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>МАЗ-9397/9758, Нефаз-9334, Тонар, ЧМЗАП, Schmitz, Krone, Kögel, Wielton, CIMC</t>
+          <t>Прицепная сеялка СЗ-3,6, опрыскиватель ОП-2000, пресс-подборщик ПРФ-180, косилка КДН, разбрасыватель РОУ, кормораздатчик КТУ-10, борона БДТ-7, прицепной скрепер ДЗ-111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Всё как у прицепа, плюс диаметр шкворня; нагрузка на седло, кг; подъёмные и управляемые оси; конструкция (рамный, безрамный — свойство, а не отдельный вид)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Описывается типом: цистерна, рефрижератор, самосвальный, контейнеровоз, трал</t>
+          <t>Общие поля прицепа плюс: вид машины; ширина захвата, м; ёмкость бака или бункера; привод от ВОМ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>Спецтехника</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Тракторный прицеп</t>
+          <t>Малое коммунальное шасси</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>R1–R4</t>
+          <t>N1, N2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Прицеп или полуприцеп к трактору.</t>
+          <t>Компактный носитель сменного коммунального оборудования: отвал, щётка, бункер, поливалка. Не лёгкий коммерческий и не трактор.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2ПТС-4/6, 1ПТС-9, ПСТ-6/9/12, ПСЕ-12,5, МЖТ</t>
+          <t>Multicar и китайские аналоги, коммунальные минишасси</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Тип прицепа; грузоподъёмность, т; объём кузова, м³; скоростной индекс (a, b)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Цистерна для жидких удобрений, водовозка — типы</t>
+          <t>Монтажная длина рамы, мм; передняя навеска; гидровыводы</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Прицеп</t>
+          <t>Спецтехника</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Прицепная машина</t>
+          <t>Специальное многоосное шасси</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>S (по Регламенту ЕС 167/2013)</t>
+          <t>N3, N3G</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Рабочее орудие на своей транспортной оси (решение: со своими колёсами — прицеп).</t>
+          <t>Шасси спроектировано под конкретную машину и отдельно не продаётся: 3–9 осей, многоосное рулевое, выносные опоры в раме, часто вторая кабина. Марка шасси и крана обычно совпадают.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Прицепная сеялка СЗ-3,6, опрыскиватель ОП-2000, пресс-подборщик ПРФ-180, косилка КДН, разбрасыватель РОУ, кормораздатчик КТУ-10, борона БДТ-7, прицепной скрепер ДЗ-111</t>
+          <t>Liebherr LTM, Grove GMK, Tadano, XCMG QAY, Zoomlion, SANY; МЗКТ «Волат»; «Ивановец», «Галичанин» на собственных спецшасси</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Общие поля прицепа плюс: вид машины; ширина захвата, м; ёмкость бака или бункера; привод от ВОМ</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Виды — на листе «Прицепные машины»</t>
+          <t>Число управляемых осей; тип подвески (гидропневматическая, рессорная); максимальная скорость, км/ч; нагрузка на ось, кг</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина</t>
+          <t>Спецтехника</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3012,18 +2575,13 @@
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Тяговый класс; колёсная формула или гусеничный ход; ВОМ; передняя и задняя навеска; моточасы</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Навесной экскаватор, бульдозерный отвал, погрузчик ПКУ, траншеекопатель</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина</t>
+          <t>Спецтехника</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3051,14 +2609,9 @@
           <t>Тип движителя; давление на грунт; плавающий; исходная модель и документ о переоборудовании</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Буровая, ППУ, кунг связи, медпункт, манипулятор</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3864,14 +3417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3887,15 +3439,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Базы</t>
+          <t>Поля модуля</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Поля модуля</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -3914,15 +3461,10 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ЛК (цельнометаллический фургон)</t>
+          <t>Объём грузового отсека, м³; высота крыши; перегородка кабины</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Объём грузового отсека, м³; высота крыши; перегородка кабины</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Штатный кузов без переоборудования</t>
         </is>
@@ -3941,15 +3483,10 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
           <t>Длина платформы, мм; ширина, мм; высота бортов, мм; материал бортов; откидных бортов; гидроборт</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3964,15 +3501,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
           <t>Длина, ширина, высота; объём, м³; европаллет; способ загрузки (задняя, боковая, верхняя, шторная)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3987,15 +3519,10 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Объём, м³; разгрузка (назад, на три стороны, вбок); материал днища; толщина днища, мм; подогрев выхлопом; полог</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; разгрузка (назад, на три стороны, вбок); материал днища; толщина днища, мм; подогрев выхлопом; полог</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Карьерный самосвал — самоходная машина, не модуль</t>
         </is>
@@ -4014,15 +3541,10 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
           <t>Внутренние длина, ширина, высота; объём, м³; материал стенок; дверей; гидроборт</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4037,15 +3559,10 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
+          <t>Объём, м³; толщина стенок, мм; класс изотермии (IN, IR)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; толщина стенок, мм; класс изотермии (IN, IR)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Сам не охлаждает</t>
         </is>
@@ -4064,15 +3581,10 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
+          <t>Объём, м³; класс ATP (A–F); диапазон температур; холодильная установка: марка, модель, заводской номер, моточасы; многотемпературный; питание от сети на стоянке</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; класс ATP (A–F); диапазон температур; холодильная установка: марка, модель, заводской номер, моточасы; многотемпературный; питание от сети на стоянке</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Один модуль, устанавливаемый на базу; охлаждает — этим отличается от изотермического</t>
         </is>
@@ -4091,15 +3603,10 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
           <t>Контейнеры (20, 40, 45 футов); фитинговых замков</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4114,15 +3621,10 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Тяговое усилие, т; длина контейнеров, мм; высота крюка, мм</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Тяговое усилие, т; длина контейнеров, мм; высота крюка, мм</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Контейнеры — сменное оборудование</t>
         </is>
@@ -4141,15 +3643,10 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Грузоподъёмность подъёма, т; объём бункера, м³</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность подъёма, т; объём бункера, м³</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Бункеры — сменное оборудование</t>
         </is>
@@ -4168,15 +3665,10 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ТТ + роспуск</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
           <t>Коников; длина хлыста, м</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4191,15 +3683,10 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>Коников; стоек; длина сортимента, м</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Коников; стоек; длина сортимента, м</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Лесной манипулятор — дополнительный модуль</t>
         </is>
@@ -4218,15 +3705,10 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
           <t>Грузоподъёмность, т; высота кассеты, мм</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -4241,15 +3723,10 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
           <t>Мест; ярусов</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -4264,15 +3741,10 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
           <t>Объём, м³; разгрузка; надставные борта</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4287,67 +3759,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
           <t>Ярусов; голов по видам; поение; вентиляция</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Цистерны</t>
+          <t>Грузовые кузова</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Бензовоз (светлые нефтепродукты)</t>
+          <t>Низкорамная платформа (трал)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Грузоподъёмность, т; погрузочная высота, мм; аппарели (механические, гидравлические); раздвижная рама; уширители</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
+          <t>Чаще на полуприцепе</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Цистерны</t>
+          <t>Грузовые кузова</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Топливозаправщик</t>
+          <t>Коники для длинномеров (роспуск)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Коников; длина груза, м; раздвижная база</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Заправляет технику на месте</t>
+          <t>Чаще на прицепе</t>
         </is>
       </c>
     </row>
@@ -4359,20 +3816,19 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Масловоз, маслозаправщик</t>
+          <t>Бензовоз (светлые нефтепродукты)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; продуктов</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4382,20 +3838,19 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Нефтевоз, мазутовоз</t>
+          <t>Топливозаправщик</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; подогрев</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Заправляет технику на месте</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4405,20 +3860,15 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Битумовоз</t>
+          <t>Масловоз, маслозаправщик</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; горелка; температура удержания, °C</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; продуктов</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4428,20 +3878,15 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Газовоз (пропан-бутан)</t>
+          <t>Нефтевоз, мазутовоз</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; рабочее давление, МПа</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; подогрев</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4451,20 +3896,15 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Водовоз технический</t>
+          <t>Битумовоз</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; горелка; температура удержания, °C</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4474,20 +3914,15 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Водовоз питьевой</t>
+          <t>Газовоз (пропан-бутан)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; рабочее давление, МПа</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4497,20 +3932,15 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Молоковоз</t>
+          <t>Водовоз технический</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
           <t>Общие для цистерн</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4520,20 +3950,15 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Пищевая цистерна</t>
+          <t>Водовоз питьевой</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4543,20 +3968,15 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Цементовоз, муковоз (сыпучие)</t>
+          <t>Молоковоз</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>Общие для цистерн</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4566,20 +3986,15 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Химическая цистерна</t>
+          <t>Пищевая цистерна</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; футеровка</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4589,20 +4004,15 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Ассенизаторская (вакуумная)</t>
+          <t>Цементовоз, муковоз (сыпучие)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4612,93 +4022,69 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Илососная</t>
+          <t>Химическая цистерна</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; футеровка</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Цистерны</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Автокран</t>
+          <t>Ассенизаторская (вакуумная)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Класс различает база</t>
-        </is>
-      </c>
+          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Цистерны</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Кран-манипулятор (КМУ)</t>
+          <t>Илососная</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Цистерны</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Лесной гидроманипулятор</t>
+          <t>Передвижная АЗС</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>Объём, м³; секций; насос; счётчик; раздаточных пистолетов; заземление</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4708,162 +4094,131 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Автовышка</t>
+          <t>Автокран</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
+          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Автогидроподъёмник (АГП) — синоним</t>
+          <t>Класс различает база</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Эвакуаторы</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с платформой</t>
+          <t>Кран-манипулятор (КМУ)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Эвакуаторы</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с частичной погрузкой</t>
+          <t>Лесной гидроманипулятор</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Эвакуаторы</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор-ротатор</t>
+          <t>Автовышка</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
+          <t>Автогидроподъёмник (АГП) — синоним</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Строительные и дорожные</t>
+          <t>Эвакуаторы</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Автобетоносмеситель (миксер)</t>
+          <t>Эвакуатор с платформой</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Строительные и дорожные</t>
+          <t>Эвакуаторы</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Автобетононасос</t>
+          <t>Эвакуатор с частичной погрузкой</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
+          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Строительные и дорожные</t>
+          <t>Эвакуаторы</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Буровая установка</t>
+          <t>Эвакуатор-ротатор</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси, вездеход</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4873,20 +4228,15 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Ямобур (бурильно-крановая машина)</t>
+          <t>Автобетоносмеситель (миксер)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4896,20 +4246,15 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Автогудронатор</t>
+          <t>Автобетононасос</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4919,20 +4264,15 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Асфальтовоз-термос</t>
+          <t>Буровая установка</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Объём кузова, м³; подогрев</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr"/>
+          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4942,24 +4282,15 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Распределитель щебня</t>
+          <t>Ямобур (бурильно-крановая машина)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Ширина распределения, м</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Обычно дополнительный модуль на самосвале</t>
-        </is>
-      </c>
+          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4969,89 +4300,73 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Дорожный ремонтёр (ямочный ремонт)</t>
+          <t>Автогудронатор</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Термобункер, м³; ёмкость эмульсии, л</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
+          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с задней загрузкой</t>
+          <t>Асфальтовоз-термос</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
+          <t>Объём кузова, м³; подогрев</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с боковой загрузкой</t>
+          <t>Распределитель щебня</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Ширина распределения, м</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; манипулятор, грузоподъёмность</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+          <t>Обычно дополнительный модуль на самосвале</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с фронтальной загрузкой</t>
+          <t>Дорожный ремонтёр (ямочный ремонт)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; грузоподъёмность вил, т</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+          <t>Термобункер, м³; ёмкость эмульсии, л</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5061,24 +4376,15 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Комбинированная дорожная машина (КДМ)</t>
+          <t>Мусоровоз с задней загрузкой</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Гидравлика для сменного оборудования; места навески (переднее, среднее, заднее)</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Отвалы, щётка, пескоразбрасыватель, поливомоечная цистерна — навесное оборудование отдельными записями, а не поля модуля</t>
-        </is>
-      </c>
+          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5088,20 +4394,15 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Поливомоечная машина</t>
+          <t>Мусоровоз с боковой загрузкой</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+          <t>Объём, м³; манипулятор, грузоподъёмность</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5111,20 +4412,15 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Подметально-уборочная машина</t>
+          <t>Мусоровоз с фронтальной загрузкой</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>Объём, м³; грузоподъёмность вил, т</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5134,20 +4430,19 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Пескоразбрасыватель</t>
+          <t>Комбинированная дорожная машина (КДМ)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
+          <t>Гидравлика для сменного оборудования; места навески (переднее, среднее, заднее)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³; ширина распределения, м</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+          <t>Отвалы, щётка, пескоразбрасыватель, поливомоечная цистерна — навесное оборудование отдельными записями, а не поля модуля</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5157,20 +4452,15 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Шнекороторный снегоочиститель</t>
+          <t>Поливомоечная машина</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Производительность, т/ч; ширина захвата, м</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5180,20 +4470,15 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочная машина</t>
+          <t>Подметально-уборочная машина</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5203,97 +4488,73 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочно-илососная машина</t>
+          <t>Пескоразбрасыватель</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Поля каналопромывочной и илососной</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Один модуль</t>
-        </is>
-      </c>
+          <t>Объём бункера, м³; ширина распределения, м</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автоцистерна (АЦ)</t>
+          <t>Шнекороторный снегоочиститель</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
-        </is>
-      </c>
+          <t>Производительность, т/ч; ширина захвата, м</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автолестница (АЛ)</t>
+          <t>Каналопромывочная машина</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Пожарный подъёмник (АКП, АТП)</t>
+          <t>Каналопромывочно-илососная машина</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
+          <t>Поля каналопромывочной и илососной</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>Один модуль</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5303,20 +4564,19 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Пожарная насосная станция (ПНС)</t>
+          <t>Пожарная автоцистерна (АЦ)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
+          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5326,20 +4586,15 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Насосно-рукавный пожарный (АНР)</t>
+          <t>Пожарная автолестница (АЛ)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Подача насоса, л/с; запас рукавов, м</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5349,20 +4604,15 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Пожарный первой помощи (АПП)</t>
+          <t>Пожарный подъёмник (АКП, АТП)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Подача насоса, л/с; запас воды, л</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5372,20 +4622,15 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Пожарный пенного, порошкового или газового тушения</t>
+          <t>Пожарная насосная станция (ПНС)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Огнетушащее вещество; масса или объём</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
+          <t>Подача насоса, л/с</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5395,20 +4640,15 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Аэродромный пожарный</t>
+          <t>Насосно-рукавный пожарный (АНР)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>спецшасси</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>Подача насоса, л/с; запас рукавов, м</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5418,93 +4658,69 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
+          <t>Пожарный первой помощи (АПП)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Вид; класс по массе (L, M, S); комплектность</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+          <t>Подача насоса, л/с; запас воды, л</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса A (санитарная)</t>
+          <t>Пожарный пенного, порошкового или газового тушения</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ЛК</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>По ГОСТ 33665-2015</t>
-        </is>
-      </c>
+          <t>Огнетушащее вещество; масса или объём</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса B (экстренная)</t>
+          <t>Аэродромный пожарный</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>ЛК</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Реанимобиль (класс C)</t>
+          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Реанимационный комплект (перечень); автономное электропитание</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+          <t>Вид; класс по массе (L, M, S); комплектность</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5514,89 +4730,73 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Передвижной медицинский кабинет</t>
+          <t>Скорая помощь класса A (санитарная)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ, автобус</t>
+          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
+          <t>По ГОСТ 33665-2015</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Передвижная лаборатория</t>
+          <t>Скорая помощь класса B (экстренная)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Профиль; приборы (перечень)</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Передвижная автомастерская</t>
+          <t>Реанимобиль (класс C)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
+          <t>Реанимационный комплект (перечень); автономное электропитание</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Аварийная газовой службы</t>
+          <t>Передвижной медицинский кабинет</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Генератор, кВт; газоанализаторы</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
+          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5606,20 +4806,15 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Аварийно-ремонтная (электросети, водоканал)</t>
+          <t>Передвижная лаборатория</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
+          <t>Профиль; приборы (перечень)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5629,20 +4824,15 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Инкассаторский автомобиль</t>
+          <t>Передвижная автомастерская</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>ЛК</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Класс защиты (Бр1–Бр5); сейф</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5652,20 +4842,15 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Оперативный (патрульный)</t>
+          <t>Аварийная газовой службы</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>легковой, ЛК</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Спецсигналы; отсек для задержанных; связь</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>Генератор, кВт; газоанализаторы</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5675,20 +4860,15 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Штабной автомобиль</t>
+          <t>Аварийно-ремонтная (электросети, водоканал)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Рабочих мест; средства связи</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5698,20 +4878,15 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Передвижной офис (бытовка)</t>
+          <t>Инкассаторский автомобиль</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Мест; отопление; санузел</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
+          <t>Класс защиты (Бр1–Бр5); сейф</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5721,24 +4896,15 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Вахтовый автобус</t>
+          <t>Оперативный (патрульный)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
-        </is>
-      </c>
+          <t>Спецсигналы; отсек для задержанных; связь</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5748,20 +4914,15 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Автодом</t>
+          <t>Штабной автомобиль</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+          <t>Рабочих мест; средства связи</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5771,20 +4932,15 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Автолавка (торговый фургон)</t>
+          <t>Передвижной офис (бытовка)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Торговое окно; холодильные витрины; весы</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
+          <t>Мест; отопление; санузел</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5794,20 +4950,19 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Хлебный фургон</t>
+          <t>Вахтовый автобус</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ЛК, СТ</t>
+          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Лотков; стеллажи</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
+          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5817,20 +4972,15 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Катафалк</t>
+          <t>Автодом</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>легковой, ЛК</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Мест для гроба; сидячих мест</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5840,158 +4990,123 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Спецоборудование салона автобуса</t>
+          <t>Автолавка (торговый фургон)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>автобус</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Профиль; оборудование (перечень)</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>Торговое окно; холодильные витрины; весы</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Цементировочный агрегат (ЦА)</t>
+          <t>Хлебный фургон</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>ТТ повышенной проходимости</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
+          <t>Лотков; стеллажи</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Насосный агрегат</t>
+          <t>Катафалк</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Давление, МПа; подача, л/с</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
+          <t>Мест для гроба; сидячих мест</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Паропередвижная установка (ППУ)</t>
+          <t>Спецоборудование салона автобуса</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ТТ, вездеход</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
+          <t>Профиль; оборудование (перечень)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Агрегат депарафинизации (АДПМ)</t>
+          <t>Электростанция (дизель-генератор)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
+          <t>Мощность, кВт; напряжение, В; топливный бак, л; моточасы; кожух</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Подъёмник ремонта скважин</t>
+          <t>Компрессорная установка</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ТТ, спецшасси</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
+          <t>Производительность, м³/мин; рабочее давление, бар; моточасы; приёмник</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Смесительная установка</t>
+          <t>Насосная установка (мотопомпа)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Объём бункера, м³</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
+          <t>Подача, л/мин; напор, м; диаметр патрубков, мм; привод</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6001,227 +5116,290 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Каротажный подъёмник (лаборатория)</t>
+          <t>Цементировочный агрегат (ЦА)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ТТ</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Глубина, м; кабель, м</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
+          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Кормовоз</t>
+          <t>Насосный агрегат</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
+          <t>Давление, МПа; подача, л/с</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Кормораздатчик на шасси</t>
+          <t>Паропередвижная установка (ППУ)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>СТ, ТТ</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; взвешивание</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
+          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Экскаваторное оборудование</t>
+          <t>Агрегат депарафинизации (АДПМ)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>трактор</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Объём ковша, м³; глубина копания, м; заводской номер</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
-        </is>
-      </c>
+          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Погрузочное оборудование</t>
+          <t>Подъёмник ремонта скважин</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>трактор</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; объём ковша, м³</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>ПКУ-0,8</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Бульдозерное оборудование</t>
+          <t>Смесительная установка</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>трактор</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Ширина отвала, мм; высота, мм; поворотный</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>ДЗ-42 на ДТ-75</t>
-        </is>
-      </c>
+          <t>Объём бункера, м³</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Траншеекопатель</t>
+          <t>Каротажный подъёмник (лаборатория)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>трактор</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Глубина траншеи, м; ширина, мм</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>ЭТЦ на МТЗ</t>
-        </is>
-      </c>
+          <t>Глубина, м; кабель, м</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Сельскохозяйственные</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Коммунальное оборудование</t>
+          <t>Кормовоз</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>трактор</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Отвал; щётка; разбрасыватель — перечень</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
+          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Кормораздатчик на шасси</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; взвешивание</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
           <t>Навесное на тракторе</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Экскаваторное оборудование</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Объём ковша, м³; глубина копания, м; заводской номер</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Навесное на тракторе</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Погрузочное оборудование</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность, т; объём ковша, м³</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>ПКУ-0,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Навесное на тракторе</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Бульдозерное оборудование</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Ширина отвала, мм; высота, мм; поворотный</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>ДЗ-42 на ДТ-75</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Навесное на тракторе</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Траншеекопатель</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Глубина траншеи, м; ширина, мм</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>ЭТЦ на МТЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Навесное на тракторе</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Коммунальное оборудование</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Отвал; щётка; разбрасыватель — перечень</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Навесное на тракторе</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Трубоукладочное оборудование</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>трактор</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Грузоподъёмность, т; момент устойчивости, т·м</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>На Т-170</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E98"/>
+  <autoFilter ref="A1:D104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -10,33 +10,35 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Базы" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля базы" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модули" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля модуля" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Самоходные машины" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля самоходной машины" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навесное и сменное" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля навесного" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Особые поля баз" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Модули" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля модуля" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Самоходные машины" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля самоходной машины" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навесное и сменное" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля навесного" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Модули'!$A$1:$D$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Самоходные машины'!$A$1:$E$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля самоходной машины'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Решения'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Источники'!$A$1:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Особые поля баз'!$A$1:$E$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Модули'!$A$1:$D$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Самоходные машины'!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Поля самоходной машины'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Решения'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Источники'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -784,7 +786,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Полный привод — признак базы («повышенной проходимости», колёсная формула), а не отдельная категория: Урал-4320 — тяжёлый грузовик с признаком полного привода.</t>
+          <t>Полный привод — не отдельная категория, а колёсная формула с осмотра: Урал-4320 — тяжёлый грузовик 6×6.</t>
         </is>
       </c>
     </row>
@@ -801,17 +803,294 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Полная масса базы — по документу шасси, полная масса машины целиком — по СТС. База внутри категории выбирается по массе, а не по модели: Sprinter на 5 т — среднетоннажный.</t>
+          <t>Масса без нагрузки и максимальная разрешённая масса — по свидетельству о регистрации. База внутри категории выбирается по массе, а не по модели: Sprinter на 5 т — среднетоннажный.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Способ поворота</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Шарнирно-сочленённая (ломающаяся) рама — признак машины, а не отдельная база: поле «Способ поворота» у трактора, спецшасси, вездехода и самоходной машины. Кировец К-700, фронтальный погрузчик, сочленённый самосвал Bell остаются в своих видах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Какие поля держим</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Поле остаётся, если оно есть в документе или помогает установить собственника и подобрать аналоги (марка, модель, год, пробег, страна сборки, руль). Инженерные параметры, которые не найти ни в документе, ни на осмотре, не заводятся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Не легло в базу</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Машина не подходит ни под одну базу своей категории — база «Прочее» в категории из техпаспорта, вид описывается текстом. Общие поля бланка и осмотра заполняются как у всех.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C19"/>
+  <autoFilter ref="A1:C22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Пояснение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Назначение</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Изготовитель</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Заводской номер</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Год выпуска</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>год</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Класс машины-носителя по массе</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>для экскаватора: 1–3, 3–8, 12–25, 25–40 т</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Тип крепления</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>штифты, гидробыстросъём, механический быстросъём, Euro, SAE-плита, трёхточечная навеска кат. 1/2/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Требуемая гидравлика</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>бар; л/мин; линий</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>давление, расход, число линий — отдельными полями</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Установлено на</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>связь с машиной</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>необязательно; с датами</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Входит в заводскую комплектацию</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Техническое состояние</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>шкала осмотра</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -962,7 +1241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1441,7 +1720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1767,7 +2046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1822,7 +2101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2087,15 +2366,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2111,22 +2388,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>По регламенту</t>
+          <t>Как узнать</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Как узнать</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Примеры</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Поля сверх общих</t>
         </is>
       </c>
     </row>
@@ -2143,22 +2410,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>M1, M1G</t>
+          <t>До 8 пассажирских мест, полная масса до 3,5 т. Пикап относится по полю «Тип ТС, вид кузова» в свидетельстве.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>До 8 пассажирских мест, полная масса до 3,5 т. Пикап бывает и M1, и N1 — категория по СТС.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
           <t>Lada Niva, УАЗ Патриот, Toyota Land Cruiser, Mitsubishi Pajero, Hyundai, Kia</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Тип кузова (седан, универсал, внедорожник, пикап)</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2432,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>N1, M2</t>
+          <t>Полная масса до 3,5 т. Исполнения: шасси с кабиной, цельнометаллический фургон, микроавтобус, пикап.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Полная масса до 3,5 т. Исполнения: шасси с кабиной, цельнометаллический фургон, микроавтобус, пикап.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>ГАЗель, Соболь, УАЗ-3303 и «Профи», Mercedes Sprinter, Ford Transit, Fiat Ducato, Iveco Daily, Hyundai Porter, Kia Bongo, Foton, JAC</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Исполнение базы; монтажная длина рамы, мм; высота крыши; длина кузова (L1–L4)</t>
         </is>
       </c>
     </row>
@@ -2207,22 +2454,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>Две оси, обычно 4×2, кабина капотная или бескапотная.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Две оси, обычно 4×2, кабина капотная или бескапотная.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
           <t>ГАЗ-3307/3309, ГАЗон Next, ЗИЛ-130/5301/4331, МАЗ-4371, Isuzu NQR/NPR, Hyundai HD-65/78/120, Mitsubishi Canter, Hino 300, FAW, Foton</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Монтажная длина рамы, мм; высота рамы, мм</t>
         </is>
       </c>
     </row>
@@ -2239,22 +2476,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>2–4 оси, 4×2, 6×4, 8×4; бескапотная кабина.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2–4 оси, 4×2, 6×4, 8×4; бескапотная кабина.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
           <t>КамАЗ-5320/65115/6520, МАЗ-5516/6501, Howo, Shacman, FAW, Dongfeng, MAN TGS, Volvo FM, Scania, Mercedes Actros/Arocs</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Нагрузка на заднюю тележку, кг; тип подвески тележки; число ведущих осей; подъёмная ось</t>
         </is>
       </c>
     </row>
@@ -2271,22 +2498,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>N2, N3</t>
+          <t>Короткая рама, седельно-сцепное устройство, без грузовой платформы.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Короткая рама, седельно-сцепное устройство, без грузовой платформы.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>КамАЗ-5410/5490/65116, МАЗ-5440/6430, Volvo FH, Scania R, MAN TGX, Howo T7H, Shacman X3000</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Высота седельного устройства, мм; нагрузка на седло, кг; полная масса автопоезда, кг; гидравлика для полуприцепа</t>
         </is>
       </c>
     </row>
@@ -2303,22 +2520,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>M2, M3</t>
+          <t>Больше 8 пассажирских мест. Кузов-вагон или кузов стороннего завода на автобусном шасси — всё равно база целиком.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Больше 8 пассажирских мест. Кузов-вагон или кузов стороннего завода на автобусном шасси — всё равно база целиком.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
           <t>ПАЗ, ЛиАЗ, МАЗ-103, Yutong, Higer, King Long, Hyundai County, Isuzu Novo</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Посадочных мест; общая вместимость; класс автобуса; расположение двигателя; высота пола; изготовитель кузова</t>
         </is>
       </c>
     </row>
@@ -2335,22 +2542,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>L1–L7</t>
+          <t>Мотоциклы, мотороллеры, квадрициклы.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Мотоциклы, мотороллеры, квадрициклы.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
           <t>Грузовые мотороллеры, квадроциклы</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Тип (мотоцикл, мотороллер, квадрицикл)</t>
         </is>
       </c>
     </row>
@@ -2367,22 +2564,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>O1–O4</t>
+          <t>Буксируется, своего двигателя нет; полный, центральноосный или роспуск.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Буксируется, своего двигателя нет; полный, центральноосный или роспуск.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
           <t>СЗАП, МАЗ-8926, Нефаз, Тонар, ГКБ-8350, Krone, Schmitz, CIMC</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Число осей; полная масса, кг; снаряжённая масса, кг; тормоза; подвеска; сцепное устройство; размерность шин</t>
         </is>
       </c>
     </row>
@@ -2399,22 +2586,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>O3, O4</t>
+          <t>Опирается на седло тягача шкворнем, передней оси нет. Бывает безрамным — несущая цистерна.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Опирается на седло тягача шкворнем, передней оси нет. Бывает безрамным — несущая цистерна.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
           <t>МАЗ-9397/9758, Нефаз-9334, Тонар, ЧМЗАП, Schmitz, Krone, Kögel, Wielton, CIMC</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Всё как у прицепа, плюс диаметр шкворня; нагрузка на седло, кг; подъёмные и управляемые оси; конструкция (рамный, безрамный — свойство, а не отдельный вид)</t>
         </is>
       </c>
     </row>
@@ -2431,22 +2608,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>R1–R4</t>
+          <t>Прицеп или полуприцеп к трактору.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Прицеп или полуприцеп к трактору.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
           <t>2ПТС-4/6, 1ПТС-9, ПСТ-6/9/12, ПСЕ-12,5, МЖТ</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; объём кузова, м³; скоростной индекс (a, b)</t>
         </is>
       </c>
     </row>
@@ -2463,22 +2630,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>S (по Регламенту ЕС 167/2013)</t>
+          <t>Рабочее орудие на своей транспортной оси (решение: со своими колёсами — прицеп).</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Рабочее орудие на своей транспортной оси (решение: со своими колёсами — прицеп).</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
           <t>Прицепная сеялка СЗ-3,6, опрыскиватель ОП-2000, пресс-подборщик ПРФ-180, косилка КДН, разбрасыватель РОУ, кормораздатчик КТУ-10, борона БДТ-7, прицепной скрепер ДЗ-111</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Общие поля прицепа плюс: вид машины; ширина захвата, м; ёмкость бака или бункера; привод от ВОМ</t>
         </is>
       </c>
     </row>
@@ -2495,22 +2652,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>N1, N2</t>
+          <t>Компактный носитель сменного коммунального оборудования: отвал, щётка, бункер, поливалка. Не лёгкий коммерческий и не трактор.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Компактный носитель сменного коммунального оборудования: отвал, щётка, бункер, поливалка. Не лёгкий коммерческий и не трактор.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
           <t>Multicar и китайские аналоги, коммунальные минишасси</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Монтажная длина рамы, мм; передняя навеска; гидровыводы</t>
         </is>
       </c>
     </row>
@@ -2527,22 +2674,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>N3, N3G</t>
+          <t>Шасси спроектировано под конкретную машину и отдельно не продаётся: 3–9 осей, многоосное рулевое, выносные опоры в раме, часто вторая кабина. Марка шасси и крана обычно совпадают.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Шасси спроектировано под конкретную машину и отдельно не продаётся: 3–9 осей, многоосное рулевое, выносные опоры в раме, часто вторая кабина. Марка шасси и крана обычно совпадают.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
           <t>Liebherr LTM, Grove GMK, Tadano, XCMG QAY, Zoomlion, SANY; МЗКТ «Волат»; «Ивановец», «Галичанин» на собственных спецшасси</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Число управляемых осей; тип подвески (гидропневматическая, рессорная); максимальная скорость, км/ч; нагрузка на ось, кг</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2696,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>T1–T5, C1–C5</t>
+          <t>Работает сам по себе и несёт навесное оборудование — тогда он база.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Работает сам по себе и несёт навесное оборудование — тогда он база.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
           <t>МТЗ «Беларус», ЮМЗ-6, Т-40, Т-150К, К-700, ДТ-75, Т-130/170, LOVOL, YTO</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Тяговый класс; колёсная формула или гусеничный ход; ВОМ; передняя и задняя навеска; моточасы</t>
         </is>
       </c>
     </row>
@@ -2591,27 +2718,39 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AII, AIII, E</t>
+          <t>Гусеничный или колёсный ход сверхвысокой проходимости, учёт как самоходной машины.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Гусеничный или колёсный ход сверхвысокой проходимости, учёт как самоходной машины.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
           <t>ГАЗ-71/34039, МТ-ЛБ, ТМ-140, «Витязь», ТРЭКОЛ, Шерп</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Тип движителя; давление на грунт; плавающий; исходная модель и документ о переоборудовании</t>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>По техпаспорту</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Машина не подходит ни под одну базу своей категории.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Редкие и штучные машины, переоборудованные из военной техники</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2622,7 +2761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2634,7 +2773,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Раздел</t>
+          <t>Откуда</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2656,7 +2795,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2671,64 +2810,68 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>лист «Базы»</t>
+          <t>лист «Базы»; выбирается по полю «Тип ТС, вид кузова»</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Категория по ТР ТС</t>
+          <t>Марка</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>M1, M2, M3, N1, N2, N3, O1–O4, L; для тракторов T1–T5, C1–C5, R1–R4</t>
+          <t>на бланке «Марка, модель» — одной строкой</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Повышенная проходимость (G)</t>
+          <t>Модель</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>да / нет</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>вместе с индексом модификации: ИМЗ-8.103-10, КамАЗ-43118</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Марка</t>
+          <t>Год выпуска</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -2736,12 +2879,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Цвет</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2754,12 +2897,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Модификация (индекс)</t>
+          <t>Идентификационный номер (VIN)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2769,19 +2912,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ-43118, ГАЗ-3309</t>
+          <t>у старых машин — короткий заводской номер</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Страна и завод сборки</t>
+          <t>№ кузова, № шасси</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2791,198 +2934,210 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>для китайских марок и лицензионной сборки</t>
+          <t>до двух значений: у машин с рамой на бланке бывают обе строки</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Год выпуска</t>
+          <t>Тип ТС, вид кузова</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>год</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>легковой, седан; мото, мотоцикл; грузовой, бортовой …</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Дата первой регистрации</t>
+          <t>Руль</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>дата</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>левый, правый</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VIN по СТС</t>
+          <t>Количество мест</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>у машины после монтажа модуля бывает свой VIN</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Номер шасси (рамы)</t>
+          <t>Тип топлива</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>бензин, дизель, газ, газ-бензин, гибрид, электро</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Номер кузова (кабины)</t>
+          <t>Рабочий объём двигателя</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>см³</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>у электромобиля пусто</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Государственный номер</t>
+          <t>Мощность двигателя</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>кВт</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>у двигателя внутреннего сгорания на бланке пусто; заполняется у электромобилей</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Идентификация</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Номер ПТС, СТС или ЭПТС</t>
+          <t>Масса без нагрузки</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>у самоходных машин — технический паспорт</t>
-        </is>
-      </c>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Колёсная формула</t>
+          <t>Максимальная разрешённая масса</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8, 10×4</t>
-        </is>
-      </c>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Число осей</t>
+          <t>Регистрационный номер</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>01KG430BR</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Число управляемых осей</t>
+          <t>Уникальный идентификатор (VID)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>число</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -2990,17 +3145,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Колёсная база</t>
+          <t>Собственник</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>мм</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -3008,159 +3163,159 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Тип кабины</t>
+          <t>ИНН (ПИН) собственника</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>капотная, бескапотная</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Исполнение кабины</t>
+          <t>Адрес собственника</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>однорядная, двухрядная, со спальным местом</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Мест в кабине</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>регистрация за текущим собственником</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Конструкция</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Коробка отбора мощности</t>
+          <t>Серия и номер свидетельства</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>да / нет</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>нужна почти всем модулям с гидравликой</t>
+          <t>AB 1783965</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Массы</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Полная масса шасси</t>
+          <t>Пробег</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>по документу шасси</t>
-        </is>
-      </c>
+          <t>км</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Массы</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Снаряжённая масса шасси</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Массы</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Нагрузка на переднюю ось</t>
+          <t>Колёсная формула</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Массы</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Нагрузка на заднюю ось (тележку)</t>
+          <t>Число осей</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>число</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -3168,17 +3323,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Двигатель</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Модель двигателя</t>
+          <t>Число управляемых осей</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>число</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -3186,232 +3341,1002 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Двигатель</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Номер двигателя</t>
+          <t>Тип КПП</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>механическая, автоматическая, роботизированная</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Двигатель</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Вид топлива</t>
+          <t>Коробка отбора мощности</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>да / нет</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>дизель, бензин, метан, пропан, двухтопливный, гибрид, электро</t>
+          <t>нужна модулям с гидравликой</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Двигатель</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Рабочий объём</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>см³</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>шкала осмотра</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Двигатель</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Мощность</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>кВт / л.с.</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>число с выбором единицы</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Двигатель</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Экологический класс</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Евро-0 … Евро-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Трансмиссия</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Тип КПП</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>механическая, автоматическая, роботизированная</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Трансмиссия</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Число передач</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Наработка</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Пробег</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>км</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Наработка</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Моточасы двигателя</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>ч</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Состояние</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Техническое состояние</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Состояние</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Комплектность</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D39"/>
+  <autoFilter ref="A1:D32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Категория (техпаспорт)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>База</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Варианты и пояснение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Легковое</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Легковой автомобиль и внедорожник</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Лёгкий коммерческий (до 3,5 т)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Исполнение базы</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>шасси с кабиной, цельнометаллический фургон, микроавтобус, пикап</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Лёгкий коммерческий (до 3,5 т)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Среднетоннажный грузовик (3,5–12 т)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Тяжёлый грузовик (свыше 12 т)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Число ведущих осей</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Тяжёлый грузовик (свыше 12 т)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Подъёмная ось</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Тяжёлый грузовик (свыше 12 т)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Седельный тягач</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Гидравлика для полуприцепа</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>для самосвальных полуприцепов</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Грузовое</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Седельный тягач</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Автобусы</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Автобус</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Класс автобуса</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>городской, пригородный, междугородный, туристический</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Автобусы</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Автобус</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Изготовитель кузова</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>когда кузов строил не завод шасси</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Автобусы</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Автобус</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Прицепы и полуприцепы</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Прицеп</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Тормоза</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Прицепы и полуприцепы</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Прицеп</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Сцепное устройство</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>петля, шар</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Прицепы и полуприцепы</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Конструкция</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>рамный, безрамный</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Прицепы и полуприцепы</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Полуприцеп</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Подъёмные оси</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Прицепы и полуприцепы</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Прицепная машина</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Вид машины</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>лист «Прицепные машины»</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Прицепы и полуприцепы</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Прицепная машина</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Ширина захвата</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Малое коммунальное шасси</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Передняя навеска</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Малое коммунальное шасси</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Гидровыводы</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Малое коммунальное шасси</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Специальное многоосное шасси</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Способ поворота</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Специальное многоосное шасси</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Трактор</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Ходовая</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>колёсная, гусеничная</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Трактор</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Способ поворота</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Трактор</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ВОМ</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>вал отбора мощности</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Трактор</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Навеска</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>передняя, задняя, обе</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Трактор</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Вездеходное шасси (транспортёр)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Тип движителя</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>колёсный, гусеничный, шнековый</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Вездеходное шасси (транспортёр)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Способ поворота</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Вездеходное шасси (транспортёр)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Плавающий</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Спецтехника</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Вездеходное шасси (транспортёр)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Документ о переоборудовании</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>для машин, собранных из военных</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>По техпаспорту</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>что это за машина — своими словами</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E34"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5404,7 +6329,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5612,7 +6537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6720,7 +7645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6909,25 +7834,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Эксплуатационная масса</t>
+          <t>Способ поворота</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот (гусеницы, мини-погрузчик)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Государственный номер</t>
+          <t>Эксплуатационная масса</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>т</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -6935,7 +7864,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Технический паспорт</t>
+          <t>Государственный номер</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -6948,19 +7877,15 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Категория по ТР ТС или допуску</t>
+          <t>Технический паспорт</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>T, C; B, C, D, E, F; AI–AIV</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -6998,7 +7923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8071,230 +8996,4 @@
   <autoFilter ref="A1:E39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Пояснение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Вид</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Назначение</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Изготовитель</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Заводской номер</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Год выпуска</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>год</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Масса</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Класс машины-носителя по массе</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>для экскаватора: 1–3, 3–8, 12–25, 25–40 т</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Тип крепления</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>штифты, гидробыстросъём, механический быстросъём, Euro, SAE-плита, трёхточечная навеска кат. 1/2/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Требуемая гидравлика</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>бар; л/мин; линий</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>давление, расход, число линий — отдельными полями</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Установлено на</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>связь с машиной</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>необязательно; с датами</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Входит в заводскую комплектацию</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>да / нет</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Техническое состояние</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C14"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -24,13 +24,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Особые поля баз'!$A$1:$E$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Модули'!$A$1:$D$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Самоходные машины'!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Самоходные машины'!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Поля самоходной машины'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -858,8 +858,25 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Ходовая</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Ходовая — множественный выбор, а не признак отдельного вида: экскаватор, трактор, кран бывают на гусеницах, на колёсах и на том и другом сразу — вид один, отмечается всё, что есть. Гусеничные машины без рабочего органа (транспортёры, тягачи) — база «Вездеход, гусеничный транспортёр».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C22"/>
+  <autoFilter ref="A1:C23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2713,7 +2730,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Вездеходное шасси (транспортёр)</t>
+          <t>Вездеход, гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3434,7 +3451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4082,12 +4099,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>несколько из списка</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная, гусеничная; можно несколько</t>
         </is>
       </c>
     </row>
@@ -4207,22 +4224,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Вездеходное шасси (транспортёр)</t>
+          <t>Вездеход, гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Тип движителя</t>
+          <t>Ходовая</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>несколько из списка</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>колёсный, гусеничный, шнековый</t>
+          <t>колёсная, гусеничная, шнековая; можно несколько</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4251,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Вездеходное шасси (транспортёр)</t>
+          <t>Вездеход, гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4261,7 +4278,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Вездеходное шасси (транспортёр)</t>
+          <t>Вездеход, гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -4284,7 +4301,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Вездеходное шасси (транспортёр)</t>
+          <t>Вездеход, гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4330,8 +4347,35 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>По техпаспорту</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Ходовая</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>несколько из списка</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>колёсная, гусеничная, вальцовая, шнековая, шагающая; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E34"/>
+  <autoFilter ref="A1:E35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6543,12 +6587,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
@@ -6566,7 +6610,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ходовая</t>
+          <t>Ходовая (варианты)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -6588,22 +6632,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Экскаватор гусеничный</t>
+          <t>Экскаватор</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>гусеничная, колёсная; бывают обе сразу</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Глубина копания, м; радиус копания, м; тип стрелы; ширина башмака, мм; быстросъём</t>
+          <t>Глубина копания, м; радиус копания, м; тип стрелы; ширина башмака, мм; выносные опоры; отвал; быстросъём</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Komatsu PC, Hitachi ZX, CAT 320, XCMG XE, SANY SY, Doosan</t>
+          <t>Komatsu PC, Hitachi ZX, CAT 320, XCMG XE, SANY SY, Doosan; ЭО-3323, Hyundai R, Liebherr A</t>
         </is>
       </c>
     </row>
@@ -6615,22 +6659,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Экскаватор колёсный</t>
+          <t>Мини-экскаватор (до 6 т)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Как у гусеничного; выносные опоры; отвал</t>
+          <t>Как у гусеничного; неповоротная хвостовая часть</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ЭО-3323, Hyundai R, Liebherr A</t>
+          <t>Kubota, Takeuchi, Bobcat E</t>
         </is>
       </c>
     </row>
@@ -6642,22 +6686,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Мини-экскаватор (до 6 т)</t>
+          <t>Экскаватор-погрузчик</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Как у гусеничного; неповоротная хвостовая часть</t>
+          <t>Глубина копания, м; грузоподъёмность погрузчика, т; телескопическая рукоять; привод 2WD/4WD (ковши — навесное оборудование)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kubota, Takeuchi, Bobcat E</t>
+          <t>JCB 3CX/4CX, CAT 428, Амкодор 702, ЭО-2626</t>
         </is>
       </c>
     </row>
@@ -6669,22 +6713,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Экскаватор-погрузчик</t>
+          <t>Бульдозер</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Глубина копания, м; грузоподъёмность погрузчика, т; телескопическая рукоять; привод 2WD/4WD (ковши — навесное оборудование)</t>
+          <t>Тяговый класс, т; тип отвала; ширина и высота отвала, мм; объём отвала, м³; рыхлитель (зубьев)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>JCB 3CX/4CX, CAT 428, Амкодор 702, ЭО-2626</t>
+          <t>ЧТЗ Т-130/170, Б10М, Shantui SD16/22/32, Komatsu D65, CAT D6–D9</t>
         </is>
       </c>
     </row>
@@ -6696,22 +6740,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Бульдозер</t>
+          <t>Думпер (мини-самосвал)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Тяговый класс, т; тип отвала; ширина и высота отвала, мм; объём отвала, м³; рыхлитель (зубьев)</t>
+          <t>Грузоподъёмность, т; объём ковша, м³; опрокидывание (вперёд, поворотное); самозагрузка</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ЧТЗ Т-130/170, Б10М, Shantui SD16/22/32, Komatsu D65, CAT D6–D9</t>
+          <t>Wacker Neuson, Ausa, Thwaites, китайские аналоги</t>
         </is>
       </c>
     </row>
@@ -6723,24 +6767,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Думпер (мини-самосвал)</t>
+          <t>Скрепер самоходный</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём ковша, м³; опрокидывание (вперёд, поворотное); самозагрузка</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Wacker Neuson, Ausa, Thwaites, китайские аналоги</t>
-        </is>
-      </c>
+          <t>Объём ковша, м³; ширина резания, м; глубина резания, мм</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6750,17 +6790,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Скрепер самоходный</t>
+          <t>Траншеекопатель</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная, колёсная</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Объём ковша, м³; ширина резания, м; глубина резания, мм</t>
+          <t>Глубина траншеи, м; ширина, мм; рабочий орган (баровый, цепной, роторный)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -6768,25 +6808,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Землеройные</t>
+          <t>Погрузочные</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Траншеекопатель</t>
+          <t>Фронтальный погрузчик</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>гусеничная, колёсная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Глубина траншеи, м; ширина, мм; рабочий орган (баровый, цепной, роторный)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; высота выгрузки, м; кинематика стрелы; быстросъём</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Амкодор 332/342, XCMG LW, SDLG L956, LiuGong 855, Shantui SL50, CAT 950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6796,22 +6840,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Фронтальный погрузчик</t>
+          <t>Мини-погрузчик</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; высота выгрузки, м; кинематика стрелы; быстросъём</t>
+          <t>Грузоподъёмность, кг; опрокидывающая нагрузка, кг; высота до шарнира, м; тип стрелы; расход вспомогательной гидравлики, л/мин</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Амкодор 332/342, XCMG LW, SDLG L956, LiuGong 855, Shantui SL50, CAT 950</t>
+          <t>Bobcat S/T, МКСМ-800, Case SR, XCMG XC7</t>
         </is>
       </c>
     </row>
@@ -6823,22 +6867,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Мини-погрузчик</t>
+          <t>Телескопический погрузчик</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, кг; опрокидывающая нагрузка, кг; высота до шарнира, м; тип стрелы; расход вспомогательной гидравлики, л/мин</t>
+          <t>Грузоподъёмность, т; высота подъёма, м; вылет, м; стабилизаторы; поворотная платформа</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Bobcat S/T, МКСМ-800, Case SR, XCMG XC7</t>
+          <t>JCB 531/540, Manitou, Merlo</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6894,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Телескопический погрузчик</t>
+          <t>Вилочный погрузчик</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -6860,12 +6904,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; высота подъёма, м; вылет, м; стабилизаторы; поворотная платформа</t>
+          <t>Грузоподъёмность, т; высота подъёма, м; тип мачты; привод (дизель, газ, электро); аккумулятор (напряжение, ёмкость, год); боковой сдвиг вил</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>JCB 531/540, Manitou, Merlo</t>
+          <t>HELI, Hangcha, Toyota, Linde, Балканкар</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6921,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Вилочный погрузчик</t>
+          <t>Ричстакер</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6887,12 +6931,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; высота подъёма, м; тип мачты; привод (дизель, газ, электро); аккумулятор (напряжение, ёмкость, год); боковой сдвиг вил</t>
+          <t>Грузоподъёмность по рядам, т; ярусов; спредер (20/40 футов)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>HELI, Hangcha, Toyota, Linde, Балканкар</t>
+          <t>Kalmar, Konecranes, SANY</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6948,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ричстакер</t>
+          <t>Самоходный штабелёр</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6914,24 +6958,20 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность по рядам, т; ярусов; спредер (20/40 футов)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Kalmar, Konecranes, SANY</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность, кг; высота подъёма, м; площадка оператора</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Погрузочные</t>
+          <t>Дорожные</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Самоходный штабелёр</t>
+          <t>Автогрейдер</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -6941,10 +6981,14 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, кг; высота подъёма, м; площадка оператора</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+          <t>Длина отвала, м; колёсная формула (1×2×3, 1×3×3); передний отвал или кирковщик; задний рыхлитель</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>ДЗ-98, ГС-14.02, XCMG GR, SDLG G9190, CAT 140</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6954,24 +6998,20 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Автогрейдер</t>
+          <t>Каток грунтовый</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>вальцовая, колёсная</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Длина отвала, м; колёсная формула (1×2×3, 1×3×3); передний отвал или кирковщик; задний рыхлитель</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>ДЗ-98, ГС-14.02, XCMG GR, SDLG G9190, CAT 140</t>
-        </is>
-      </c>
+          <t>Ширина вальца, мм; валец (гладкий, кулачковый); частота вибрации, Гц; амплитуда, мм; центробежная сила, кН</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -6981,20 +7021,24 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Каток грунтовый</t>
+          <t>Каток асфальтовый</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>вальцовая + пневмоколёса</t>
+          <t>вальцовая</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ширина вальца, мм; валец (гладкий, кулачковый); частота вибрации, Гц; амплитуда, мм; центробежная сила, кН</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>Ширина вальца, мм; вибрация или осцилляция; орошение</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Тандемный, комбинированный</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -7004,24 +7048,20 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Каток асфальтовый</t>
+          <t>Каток пневмоколёсный</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>вальцовая</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ширина вальца, мм; вибрация или осцилляция; орошение</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Тандемный, комбинированный</t>
-        </is>
-      </c>
+          <t>Масса с балластом, т; шин; ширина уплотнения, мм</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -7031,17 +7071,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Каток пневмоколёсный</t>
+          <t>Асфальтоукладчик</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная, колёсная</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Масса с балластом, т; шин; ширина уплотнения, мм</t>
+          <t>Ширина укладки min/max, м; толщина слоя, мм; производительность, т/ч; выглаживающая плита; бункер, т</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -7054,7 +7094,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Асфальтоукладчик</t>
+          <t>Дорожная фреза</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7064,7 +7104,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ширина укладки min/max, м; толщина слоя, мм; производительность, т/ч; выглаживающая плита; бункер, т</t>
+          <t>Ширина фрезерования, мм; глубина, мм; конвейер</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -7077,17 +7117,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Дорожная фреза</t>
+          <t>Ресайклер (стабилизатор грунта)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>гусеничная, колёсная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ширина фрезерования, мм; глубина, мм; конвейер</t>
+          <t>Ширина обработки, мм; глубина, мм; дозирование вяжущего</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -7095,25 +7135,29 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Дорожные</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Ресайклер (стабилизатор грунта)</t>
+          <t>Кран стреловой самоходный</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная, колёсная</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Ширина обработки, мм; глубина, мм; дозирование вяжущего</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; длина стрелы, м; гусек, м; тип стрелы (решётчатая, телескопическая); выносные опоры; учётный номер в надзоре</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>РДК-250, ДЭК-251, SANY SCC, XCMG XGC; КС-5363, rough-terrain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -7123,7 +7167,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Кран гусеничный</t>
+          <t>Трубоукладчик</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -7133,12 +7177,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; длина стрелы, м; гусек, м; тип стрелы (решётчатая, телескопическая); учётный номер в надзоре</t>
+          <t>Грузоподъёмность, т; момент устойчивости, т·м; вылет, м</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>РДК-250, ДЭК-251, SANY SCC, XCMG XGC</t>
+          <t>ТГ-124, Komatsu D355C</t>
         </is>
       </c>
     </row>
@@ -7150,76 +7194,72 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Кран пневмоколёсный (короткобазовый)</t>
+          <t>Самоходный подъёмник</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Как у гусеничного; выносные опоры</t>
+          <t>Тип (ножничный, коленчатый, телескопический); рабочая высота, м; вылет, м; грузоподъёмность, кг; привод</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>КС-5363, rough-terrain</t>
+          <t>Genie, JLG, Haulotte, Dingli</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Горные</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Трубоукладчик</t>
+          <t>Погрузочно-доставочная машина</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; момент устойчивости, т·м; вылет, м</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>ТГ-124, Komatsu D355C</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность, т; объём ковша, м³; привод (дизель, кабель)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Горные</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Самоходный подъёмник</t>
+          <t>Карьерный самосвал</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Тип (ножничный, коленчатый, телескопический); рабочая высота, м; вылет, м; грузоподъёмность, кг; привод</t>
+          <t>Грузоподъёмность, т; объём кузова, м³; трансмиссия (механическая, гидромеханическая, электромеханическая)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Genie, JLG, Haulotte, Dingli</t>
+          <t>БелАЗ, Komatsu HD, CAT 770–777; сочленённый (Volvo A30, Bell) — сюда же</t>
         </is>
       </c>
     </row>
@@ -7231,74 +7271,70 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Погрузочно-доставочная машина</t>
+          <t>Буровой станок карьерный</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём ковша, м³; привод (дизель, кабель)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Диаметр бурения, мм; глубина, м; тип (шарошечный, пневмоударный, погружной); компрессор, м³/мин</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>СБШ-250, Epiroc</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Горные</t>
+          <t>Лесные</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Карьерный самосвал</t>
+          <t>Харвестер</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём кузова, м³; трансмиссия (механическая, гидромеханическая, электромеханическая)</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>БелАЗ, Komatsu HD, CAT 770–777; сочленённый (Volvo A30, Bell) — сюда же</t>
-        </is>
-      </c>
+          <t>Вылет манипулятора, м; харвестерная головка; диаметр среза, см</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Горные</t>
+          <t>Лесные</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Буровой станок карьерный</t>
+          <t>Форвардер</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Диаметр бурения, мм; глубина, м; тип (шарошечный, пневмоударный, погружной); компрессор, м³/мин</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>СБШ-250, Epiroc</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность, т; площадь коника, м²; вылет, м</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -7308,68 +7344,76 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Харвестер</t>
+          <t>Трелёвочный трактор</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>гусеничная, колёсная</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Вылет манипулятора, м; харвестерная головка; диаметр среза, см</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
+          <t>Трелёвочное оборудование; тяговое усилие лебёдки, кН</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>ТДТ-55, ЛТ-154</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Лесные</t>
+          <t>Сельскохозяйственные</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Форвардер</t>
+          <t>Трактор</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; площадь коника, м²; вылет, м</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>Тяговый класс (ГОСТ 27021-86); колёсная формула; тип гусениц; колея, мм; ВОМ, об/мин; задняя навеска (категория); передняя навеска</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ-80/82/1221, Т-150К, К-700, LOVOL, John Deere; ДТ-75, Т-4А</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Лесные</t>
+          <t>Сельскохозяйственные</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Трелёвочный трактор</t>
+          <t>Комбайн зерноуборочный</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>гусеничная, колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Трелёвочное оборудование; тяговое усилие лебёдки, кН</t>
+          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки (жатка — навесное оборудование отдельной записью)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ТДТ-55, ЛТ-154</t>
+          <t>Нива, Енисей, Дон-1500, Акрос, Палессе, Claas</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7425,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Трактор колёсный</t>
+          <t>Комбайн кормоуборочный</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -7391,12 +7435,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Тяговый класс (ГОСТ 27021-86); колёсная формула; ВОМ, об/мин; задняя навеска (категория); передняя навеска</t>
+          <t>Мощность; ножей измельчителя</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>МТЗ-80/82/1221, Т-150К, К-700, LOVOL, John Deere</t>
+          <t>Дон-680, Палессе FS, Claas Jaguar</t>
         </is>
       </c>
     </row>
@@ -7408,24 +7452,20 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Трактор гусеничный</t>
+          <t>Самоходный опрыскиватель</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Тяговый класс; тип гусениц; колея, мм</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>ДТ-75, Т-4А</t>
-        </is>
-      </c>
+          <t>Ёмкость бака, л; ширина штанги, м; клиренс, мм</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7435,84 +7475,88 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Комбайн зерноуборочный</t>
+          <t>Самоходная косилка</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки (жатка — навесное оборудование отдельной записью)</t>
+          <t>Ширина захвата, м; плющилка</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Нива, Енисей, Дон-1500, Акрос, Палессе, Claas</t>
+          <t>КСУ-1, Палессе CS</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Вездеходы</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Комбайн кормоуборочный</t>
+          <t>Снегоболотоход</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>колёсная, гусеничная</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Мощность; ножей измельчителя</t>
+          <t>Полная масса, т; мест; грузоподъёмность, т; плавающий</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Дон-680, Палессе FS, Claas Jaguar</t>
+          <t>ТРЭКОЛ, Шерп, Бурлак</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Вездеходы</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Самоходный опрыскиватель</t>
+          <t>Гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>колёсная</t>
+          <t>гусеничная</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Ёмкость бака, л; ширина штанги, м; клиренс, мм</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; буксируемая масса, т; мест; плавающий; исходная модель; переоборудование (вид, документ)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>МТ-ЛБ, ГАЗ-71, ГТ-Т, «Витязь»</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Самоходная косилка</t>
+          <t>Самоходная подметальная машина</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7522,125 +7566,44 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Ширина захвата, м; плющилка</t>
+          <t>Ширина подметания, м; бункер, л; увлажнение</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>КСУ-1, Палессе CS</t>
+          <t>Tennant, Hako</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Вездеходы</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Снегоболотоход</t>
+          <t>Коммунальный минитрактор</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Полная масса, т; мест; грузоподъёмность, т; плавающий</t>
+          <t>Мощность; передняя навеска; ВОМ</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>ТРЭКОЛ, Шерп, Бурлак</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Вездеходы</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Гусеничный транспортёр</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>гусеничная</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; буксируемая масса, т; мест; плавающий; исходная модель; переоборудование (вид, документ)</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>МТ-ЛБ, ГАЗ-71, ГТ-Т, «Витязь»</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Коммунальные</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Самоходная подметальная машина</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>колёсная</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Ширина подметания, м; бункер, л; увлажнение</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Tennant, Hako</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Коммунальные</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Коммунальный минитрактор</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>колёсная</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Мощность; передняя навеска; ВОМ</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
           <t>Беларус-132Н, Holder</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E42"/>
+  <autoFilter ref="A1:E39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7822,12 +7785,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>несколько из списка</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>гусеничная, колёсная, вальцовая</t>
+          <t>колёсная, гусеничная, вальцовая, шнековая, шагающая; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
         </is>
       </c>
     </row>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -24,14 +24,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Модули'!$A$1:$D$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Самоходные машины'!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Поля самоходной машины'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Поля самоходной машины'!$A$1:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Каждая единица относится ровно к одному виду: колёсное ТС (база + модули), прицеп или полуприцеп (база + модули), самоходная машина собственной конструкции, сменное навесное оборудование.</t>
+          <t>Каждая единица относится ровно к одному виду: ТС одной из категорий техпаспорта (база + модули; прицеп и полуприцеп — тоже база), самоходная машина собственной конструкции, сменное навесное оборудование.</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ковши, вилы, жатки, отвалы, щётки, бункеры — всегда навесное оборудование отдельной записью, даже когда пришли вместе с машиной. В поля машины они не выносятся.</t>
+          <t>Ковши, вилы, жатки, отвалы, щётки, бункеры — всегда навесное оборудование отдельной записью, даже когда пришли вместе с машиной. В поля машины они не выносятся. Исключение — несъёмный кузов-ковш думпера и скрепера: это часть машины.</t>
         </is>
       </c>
     </row>
@@ -875,8 +875,42 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Поля одним списком</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Поля не делятся на группы «техпаспорт» и «осмотр»: источник — пометка у поля. Вид документа не заводится: бланки меняются (прежний «КР №», книжка 2019 года, карта 2025 года), а поля по сути те же.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Дополнительные поля</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Особые отметки документа и всё, чему нет своего поля, — в таблицу дополнительных полей: название и значение пишет пользователь.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C23"/>
+  <autoFilter ref="A1:C25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1321,7 +1355,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>База: тяжёлый грузовик, повышенной проходимости</t>
+          <t>База: тяжёлый грузовик, 6×6</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1557,7 +1591,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>База: тяжёлый грузовик, повышенной проходимости</t>
+          <t>База: тяжёлый грузовик, 6×6</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1815,7 +1849,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Признак базы, не категория</t>
+          <t>Колёсная формула с осмотра, не категория и не отдельная база</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2483,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Полная масса до 3,5 т. Исполнения: шасси с кабиной, цельнометаллический фургон, микроавтобус, пикап.</t>
+          <t>Максимальная разрешённая масса до 3,5 т. Исполнения: шасси с кабиной, цельнометаллический фургон, микроавтобус, пикап.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2778,10 +2812,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -2790,7 +2824,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Откуда</t>
+          <t>Источник</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2849,7 +2883,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>на бланке «Марка, модель» — одной строкой</t>
+          <t>на старом бланке марка и модель одной строкой — «Модели»</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2905,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>вместе с индексом модификации: ИМЗ-8.103-10, КамАЗ-43118</t>
+          <t>вместе с индексом модификации: ИМЗ-8.103-10, ВАЗ-21074</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2925,11 @@
           <t>год</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>при замене кузова, рамы или двигателя не меняется</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2929,7 +2967,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>у старых машин — короткий заводской номер</t>
+          <t>у японских машин и старой техники часто пусто; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2979,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>№ кузова, № шасси</t>
+          <t>№ кузова (коляски)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2951,7 +2989,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>до двух значений: у машин с рамой на бланке бывают обе строки</t>
+          <t>у японских машин здесь стоит идентификатор; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
     </row>
@@ -2963,17 +3001,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Тип ТС, вид кузова</t>
+          <t>№ шасси (рамы)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>легковой, седан; мото, мотоцикл; грузовой, бортовой …</t>
+          <t>из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
     </row>
@@ -2985,17 +3023,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Руль</t>
+          <t>№ двигателя</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>левый, правый</t>
+          <t>необязательное: есть на свидетельствах прежнего образца, в советских техпаспортах и в документах на тракторы</t>
         </is>
       </c>
     </row>
@@ -3007,25 +3045,29 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Количество мест</t>
+          <t>Тип ТС, вид кузова</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>легковой, седан; мото, мотоцикл; грузовой, бортовой …</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Техпаспорт или осмотр</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Тип топлива</t>
+          <t>Руль</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3035,7 +3077,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>бензин, дизель, газ, газ-бензин, гибрид, электро</t>
+          <t>левый, правый; на бланках до 2019 года графы нет — по осмотру</t>
         </is>
       </c>
     </row>
@@ -3047,19 +3089,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Рабочий объём двигателя</t>
+          <t>Количество мест</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>см³</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>у электромобиля пусто</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3069,17 +3107,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Тип топлива</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>кВт</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>у двигателя внутреннего сгорания на бланке пусто; заполняется у электромобилей</t>
+          <t>бензин, дизель, газ, газ-бензин, гибрид, электро; на старом бланке — рядом с объёмом («1588 Б»)</t>
         </is>
       </c>
     </row>
@@ -3091,15 +3129,19 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Масса без нагрузки</t>
+          <t>Рабочий объём двигателя</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>см³</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>у электромобиля пусто</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3109,15 +3151,19 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Максимальная разрешённая масса</t>
+          <t>Мощность двигателя</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>кВт или л.с.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>единица выбирается; у двигателя внутреннего сгорания на новом бланке пусто, «0.00» тоже считается пустым; в старых документах — в л.с.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3127,17 +3173,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Регистрационный номер</t>
+          <t>Масса без нагрузки</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>01KG430BR</t>
+          <t>у легковых часто не заполнена</t>
         </is>
       </c>
     </row>
@@ -3149,15 +3195,19 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Уникальный идентификатор (VID)</t>
+          <t>Максимальная разрешённая масса</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>у легковых часто не заполнена</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3167,7 +3217,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Собственник</t>
+          <t>Регистрационный номер</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3175,7 +3225,11 @@
           <t>текст</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>01KG430BR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3185,7 +3239,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ИНН (ПИН) собственника</t>
+          <t>Уникальный идентификатор (VID)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3193,7 +3247,11 @@
           <t>текст</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>на части старых бланков нет</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3203,7 +3261,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Адрес собственника</t>
+          <t>Собственник</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3221,19 +3279,15 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Дата регистрации</t>
+          <t>ИНН (ПИН) собственника</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>дата</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>регистрация за текущим собственником</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3243,7 +3297,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Серия и номер свидетельства</t>
+          <t>Адрес собственника</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3253,47 +3307,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>AB 1783965</t>
+          <t>на старом бланке — «место регистрации»</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Пробег</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>км</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>регистрация за текущим собственником</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Серия и номер документа</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
     </row>
@@ -3305,19 +3363,15 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Колёсная формула</t>
+          <t>Пробег</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
-        </is>
-      </c>
+          <t>км</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3327,15 +3381,19 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Число осей</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3345,15 +3403,19 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Число управляемых осей</t>
+          <t>Колёсная формула</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3363,19 +3425,15 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Тип КПП</t>
+          <t>Число осей</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>механическая, автоматическая, роботизированная</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3385,19 +3443,15 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Коробка отбора мощности</t>
+          <t>Число управляемых осей</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>да / нет</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>нужна модулям с гидравликой</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3407,7 +3461,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Тип КПП</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3417,7 +3471,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>шкала осмотра</t>
+          <t>механическая, автоматическая, роботизированная</t>
         </is>
       </c>
     </row>
@@ -3429,18 +3483,84 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>Коробка отбора мощности</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>да / нет</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>нужна модулям с гидравликой</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Техническое состояние</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>шкала осмотра</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>Комплектность</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Дополнительные поля</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>таблица: название и значение</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D32"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6252,7 +6372,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Объём ковша, м³; глубина копания, м; заводской номер</t>
+          <t>Глубина копания, м; заводской номер</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6274,7 +6394,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём ковша, м³</t>
+          <t>Грузоподъёмность, т</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6750,7 +6870,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём ковша, м³; опрокидывание (вперёд, поворотное); самозагрузка</t>
+          <t>Грузоподъёмность, т; объём кузова-ковша, м³; опрокидывание (вперёд, поворотное); самозагрузка</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6777,7 +6897,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Объём ковша, м³; ширина резания, м; глубина резания, мм</t>
+          <t>Объём кузова-ковша, м³; ширина резания, м; глубина резания, мм</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -7231,7 +7351,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; объём ковша, м³; привод (дизель, кабель)</t>
+          <t>Грузоподъёмность, т; привод (дизель, кабель)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -7614,26 +7734,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Поле</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Пояснение</t>
         </is>
@@ -7642,246 +7768,493 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>Марка</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>Модель</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>Изготовитель</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Страна</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Страна сборки</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>Год выпуска</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>год</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>при замене рамы, двигателя, КПП или моста не меняется</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Заводской номер машины (рамы)</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>Цвет</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Номер двигателя</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Заводской № машины (рамы)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>кВт / л.с.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+          <t>№ двигателя</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Вид топлива</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>Мощность двигателя</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>дизель, бензин, газ, электро</t>
+          <t>кВт или л.с.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>единица выбирается; у двигателя внутреннего сгорания на новом бланке пусто, «0.00» тоже считается пустым; в старых документах — в л.с.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>Тип топлива</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>основной показатель наработки</t>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>дизель, бензин, газ, электро</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Ходовая</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>несколько из списка</t>
+          <t>Конструкционная масса</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная, вальцовая, шнековая, шагающая; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>так в техническом паспорте</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Способ поворота</t>
+          <t>Техпаспорт или осмотр</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>Ходовая</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот (гусеницы, мини-погрузчик)</t>
+          <t>несколько из списка</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>колёсная, гусеничная, полугусеничная, вальцовая, шнековая, шагающая, на полозьях; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Эксплуатационная масса</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>Способ поворота</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Государственный номер</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>Регистрационный номер</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>01KG430BR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Технический паспорт</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>Уникальный идентификатор (VID)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>на части старых бланков нет</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>Собственник</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ИНН (ПИН) собственника</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Адрес собственника</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>на старом бланке — «место регистрации»</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Дата регистрации</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>регистрация за текущим собственником</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Техпаспорт</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Серия и номер документа</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Моточасы</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>основной показатель наработки</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Техническое состояние</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>шкала осмотра</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>Комплектность</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Дополнительные поля</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>таблица: название и значение</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:D25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -24,13 +24,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Модули'!$A$1:$D$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Модули'!$A$1:$D$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Самоходные машины'!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Самоходные машины'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Поля самоходной машины'!$A$1:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Спецоборудование, смонтированное на шасси, — модуль. Модуль записывается отдельно от базы всегда, в том числе когда его не переставляют (самосвальный кузов, бортовая платформа, пожарная надстройка): на ту же базу могли поставить другой модуль. Штатный кузов цельнометаллического фургона без переоборудования — «Базовый модуль». Шасси без надстройки или с демонтированной надстройкой — «модуль отсутствует».</t>
+          <t>Спецоборудование, смонтированное на шасси, — модуль. Модуль записывается отдельно от базы всегда, в том числе когда его не переставляют (самосвальный кузов, бортовая платформа, пожарная надстройка): на ту же базу могли поставить другой модуль. Цельнометаллический фургон без переоборудования — исполнение базы, модуль не заводится. Шасси без надстройки или со снятой надстройкой — база без модулей.</t>
         </is>
       </c>
     </row>
@@ -909,8 +909,25 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Трактор и вездеход — только базы</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Трактор (в том числе мини-трактор) и вездеход, гусеничный транспортёр заводятся только базой категории «Спецтехника», на листе самоходных машин их нет. Без навесного — база без модулей, с навесным или кунгом — база и модули.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C25"/>
+  <autoFilter ref="A1:C26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1733,7 +1750,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Самоходная машина: гусеничный транспортёр (переоборудован)</t>
+          <t>База: вездеход, гусеничный транспортёр</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1741,7 +1758,11 @@
           <t>Модуль: передвижной офис (кунг)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Переоборудование — особое поле базы</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1815,7 +1836,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>База + «Базовый модуль»</t>
+          <t>База «Лёгкий коммерческий», исполнение «цельнометаллический фургон»; модуль не заводится</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1853,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>База без модуля, пометка «модуль отсутствует»</t>
+          <t>База без модулей</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2773,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>МТЗ «Беларус», ЮМЗ-6, Т-40, Т-150К, К-700, ДТ-75, Т-130/170, LOVOL, YTO</t>
+          <t>МТЗ «Беларус», мини-тракторы (Беларус-132Н, Holder), ЮМЗ-6, Т-40, Т-150К, К-700, ДТ-75, Т-130/170, LOVOL, YTO</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2795,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ГАЗ-71/34039, МТ-ЛБ, ТМ-140, «Витязь», ТРЭКОЛ, Шерп</t>
+          <t>ГАЗ-71/34039, МТ-ЛБ, ГТ-Т, ТМ-140, «Витязь», ТРЭКОЛ, Шерп, Бурлак</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4540,24 +4561,20 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Базовый</t>
+          <t>Грузовые кузова</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Базовый модуль</t>
+          <t>Бортовая платформа</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Объём грузового отсека, м³; высота крыши; перегородка кабины</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Штатный кузов без переоборудования</t>
-        </is>
-      </c>
+          <t>Длина платформы, мм; ширина, мм; высота бортов, мм; материал бортов; откидных бортов; гидроборт</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4567,12 +4584,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бортовая платформа</t>
+          <t>Тентованная платформа</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Длина платформы, мм; ширина, мм; высота бортов, мм; материал бортов; откидных бортов; гидроборт</t>
+          <t>Длина, ширина, высота; объём, м³; европаллет; способ загрузки (задняя, боковая, верхняя, шторная)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -4585,15 +4602,19 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Тентованная платформа</t>
+          <t>Самосвальный кузов</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Длина, ширина, высота; объём, м³; европаллет; способ загрузки (задняя, боковая, верхняя, шторная)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>Объём, м³; разгрузка (назад, на три стороны, вбок); материал днища; толщина днища, мм; подогрев выхлопом; полог</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Карьерный самосвал — самоходная машина, не модуль</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4603,19 +4624,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Самосвальный кузов</t>
+          <t>Промтоварный фургон</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; разгрузка (назад, на три стороны, вбок); материал днища; толщина днища, мм; подогрев выхлопом; полог</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Карьерный самосвал — самоходная машина, не модуль</t>
-        </is>
-      </c>
+          <t>Внутренние длина, ширина, высота; объём, м³; материал стенок; дверей; гидроборт</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4625,15 +4642,19 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Промтоварный фургон</t>
+          <t>Изотермический фургон</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Внутренние длина, ширина, высота; объём, м³; материал стенок; дверей; гидроборт</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>Объём, м³; толщина стенок, мм; класс изотермии (IN, IR)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Сам не охлаждает</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4643,17 +4664,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Изотермический фургон</t>
+          <t>Рефрижератор</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; толщина стенок, мм; класс изотермии (IN, IR)</t>
+          <t>Объём, м³; класс ATP (A–F); диапазон температур; холодильная установка: марка, модель, заводской номер, моточасы; многотемпературный; питание от сети на стоянке</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Сам не охлаждает</t>
+          <t>Один модуль, устанавливаемый на базу; охлаждает — этим отличается от изотермического</t>
         </is>
       </c>
     </row>
@@ -4665,19 +4686,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Рефрижератор</t>
+          <t>Контейнеровоз</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; класс ATP (A–F); диапазон температур; холодильная установка: марка, модель, заводской номер, моточасы; многотемпературный; питание от сети на стоянке</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Один модуль, устанавливаемый на базу; охлаждает — этим отличается от изотермического</t>
-        </is>
-      </c>
+          <t>Контейнеры (20, 40, 45 футов); фитинговых замков</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4687,15 +4704,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Контейнеровоз</t>
+          <t>Мультилифт (крюковой погрузчик)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Контейнеры (20, 40, 45 футов); фитинговых замков</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>Тяговое усилие, т; длина контейнеров, мм; высота крюка, мм</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Контейнеры — сменное оборудование</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4705,17 +4726,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Мультилифт (крюковой погрузчик)</t>
+          <t>Бункеровоз (портальный погрузчик)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Тяговое усилие, т; длина контейнеров, мм; высота крюка, мм</t>
+          <t>Грузоподъёмность подъёма, т; объём бункера, м³</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Контейнеры — сменное оборудование</t>
+          <t>Бункеры — сменное оборудование</t>
         </is>
       </c>
     </row>
@@ -4727,19 +4748,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Бункеровоз (портальный погрузчик)</t>
+          <t>Лесовоз</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность подъёма, т; объём бункера, м³</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Бункеры — сменное оборудование</t>
-        </is>
-      </c>
+          <t>Коников; длина хлыста, м</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4749,15 +4766,19 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Лесовоз</t>
+          <t>Сортиментовоз</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Коников; длина хлыста, м</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>Коников; стоек; длина сортимента, м</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Лесной манипулятор — дополнительный модуль</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -4767,19 +4788,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Сортиментовоз</t>
+          <t>Панелевоз</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Коников; стоек; длина сортимента, м</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Лесной манипулятор — дополнительный модуль</t>
-        </is>
-      </c>
+          <t>Грузоподъёмность, т; высота кассеты, мм</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -4789,12 +4806,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Панелевоз</t>
+          <t>Автовоз</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; высота кассеты, мм</t>
+          <t>Мест; ярусов</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -4807,12 +4824,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Автовоз</t>
+          <t>Зерновоз</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Мест; ярусов</t>
+          <t>Объём, м³; разгрузка; надставные борта</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
@@ -4825,12 +4842,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Зерновоз</t>
+          <t>Скотовоз</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; разгрузка; надставные борта</t>
+          <t>Ярусов; голов по видам; поение; вентиляция</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -4843,15 +4860,19 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Скотовоз</t>
+          <t>Низкорамная платформа (трал)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ярусов; голов по видам; поение; вентиляция</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; погрузочная высота, мм; аппарели (механические, гидравлические); раздвижная рама; уширители</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Чаще на полуприцепе</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4861,39 +4882,39 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Низкорамная платформа (трал)</t>
+          <t>Коники для длинномеров (роспуск)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; погрузочная высота, мм; аппарели (механические, гидравлические); раздвижная рама; уширители</t>
+          <t>Коников; длина груза, м; раздвижная база</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Чаще на полуприцепе</t>
+          <t>Чаще на прицепе</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Грузовые кузова</t>
+          <t>Цистерны</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Коники для длинномеров (роспуск)</t>
+          <t>Бензовоз (светлые нефтепродукты)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Коников; длина груза, м; раздвижная база</t>
+          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Чаще на прицепе</t>
+          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
         </is>
       </c>
     </row>
@@ -4905,17 +4926,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Бензовоз (светлые нефтепродукты)</t>
+          <t>Топливозаправщик</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
+          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
+          <t>Заправляет технику на месте</t>
         </is>
       </c>
     </row>
@@ -4927,19 +4948,15 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Топливозаправщик</t>
+          <t>Масловоз, маслозаправщик</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Заправляет технику на месте</t>
-        </is>
-      </c>
+          <t>Общие для цистерн; продуктов</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4949,12 +4966,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Масловоз, маслозаправщик</t>
+          <t>Нефтевоз, мазутовоз</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; продуктов</t>
+          <t>Общие для цистерн; подогрев</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -4967,12 +4984,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Нефтевоз, мазутовоз</t>
+          <t>Битумовоз</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; подогрев</t>
+          <t>Общие для цистерн; горелка; температура удержания, °C</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -4985,12 +5002,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Битумовоз</t>
+          <t>Газовоз (пропан-бутан)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; горелка; температура удержания, °C</t>
+          <t>Общие для цистерн; рабочее давление, МПа</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -5003,12 +5020,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Газовоз (пропан-бутан)</t>
+          <t>Водовоз технический</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; рабочее давление, МПа</t>
+          <t>Общие для цистерн</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -5021,12 +5038,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Водовоз технический</t>
+          <t>Водовоз питьевой</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн</t>
+          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -5039,12 +5056,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Водовоз питьевой</t>
+          <t>Молоковоз</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
+          <t>Общие для цистерн</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -5057,12 +5074,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Молоковоз</t>
+          <t>Пищевая цистерна</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн</t>
+          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -5075,12 +5092,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Пищевая цистерна</t>
+          <t>Цементовоз, муковоз (сыпучие)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
+          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -5093,12 +5110,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Цементовоз, муковоз (сыпучие)</t>
+          <t>Химическая цистерна</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
+          <t>Общие для цистерн; футеровка</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -5111,12 +5128,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Химическая цистерна</t>
+          <t>Ассенизаторская (вакуумная)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; футеровка</t>
+          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -5129,12 +5146,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Ассенизаторская (вакуумная)</t>
+          <t>Илососная</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
+          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -5147,12 +5164,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Илососная</t>
+          <t>Передвижная АЗС</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
+          <t>Объём, м³; секций; насос; счётчик; раздаточных пистолетов; заземление</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -5160,20 +5177,24 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Цистерны</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Передвижная АЗС</t>
+          <t>Автокран</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; секций; насос; счётчик; раздаточных пистолетов; заземление</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Класс различает база</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -5183,19 +5204,15 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Автокран</t>
+          <t>Кран-манипулятор (КМУ)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Класс различает база</t>
-        </is>
-      </c>
+          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5205,12 +5222,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Кран-манипулятор (КМУ)</t>
+          <t>Лесной гидроманипулятор</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
+          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -5223,37 +5240,37 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Лесной гидроманипулятор</t>
+          <t>Автовышка</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Автогидроподъёмник (АГП) — синоним</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Эвакуаторы</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Автовышка</t>
+          <t>Эвакуатор с платформой</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Автогидроподъёмник (АГП) — синоним</t>
-        </is>
-      </c>
+          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5263,12 +5280,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с платформой</t>
+          <t>Эвакуатор с частичной погрузкой</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
+          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -5281,12 +5298,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с частичной погрузкой</t>
+          <t>Эвакуатор-ротатор</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
+          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -5294,17 +5311,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Эвакуаторы</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор-ротатор</t>
+          <t>Автобетоносмеситель (миксер)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
+          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -5317,12 +5334,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Автобетоносмеситель (миксер)</t>
+          <t>Автобетононасос</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
+          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -5335,12 +5352,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Автобетононасос</t>
+          <t>Буровая установка</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
+          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -5353,12 +5370,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Буровая установка</t>
+          <t>Ямобур (бурильно-крановая машина)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
+          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -5371,12 +5388,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Ямобур (бурильно-крановая машина)</t>
+          <t>Автогудронатор</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
+          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -5389,12 +5406,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Автогудронатор</t>
+          <t>Асфальтовоз-термос</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
+          <t>Объём кузова, м³; подогрев</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -5407,15 +5424,19 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Асфальтовоз-термос</t>
+          <t>Распределитель щебня</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Объём кузова, м³; подогрев</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>Ширина распределения, м</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Обычно дополнительный модуль на самосвале</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5425,34 +5446,30 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Распределитель щебня</t>
+          <t>Дорожный ремонтёр (ямочный ремонт)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Ширина распределения, м</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Обычно дополнительный модуль на самосвале</t>
-        </is>
-      </c>
+          <t>Термобункер, м³; ёмкость эмульсии, л</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Строительные и дорожные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Дорожный ремонтёр (ямочный ремонт)</t>
+          <t>Мусоровоз с задней загрузкой</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Термобункер, м³; ёмкость эмульсии, л</t>
+          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -5465,12 +5482,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с задней загрузкой</t>
+          <t>Мусоровоз с боковой загрузкой</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
+          <t>Объём, м³; манипулятор, грузоподъёмность</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -5483,12 +5500,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с боковой загрузкой</t>
+          <t>Мусоровоз с фронтальной загрузкой</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; манипулятор, грузоподъёмность</t>
+          <t>Объём, м³; грузоподъёмность вил, т</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -5501,15 +5518,19 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с фронтальной загрузкой</t>
+          <t>Комбинированная дорожная машина (КДМ)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; грузоподъёмность вил, т</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>Гидравлика для сменного оборудования; места навески (переднее, среднее, заднее)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Отвалы, щётка, пескоразбрасыватель, поливомоечная цистерна — навесное оборудование отдельными записями, а не поля модуля</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5519,19 +5540,15 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Комбинированная дорожная машина (КДМ)</t>
+          <t>Поливомоечная машина</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Гидравлика для сменного оборудования; места навески (переднее, среднее, заднее)</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Отвалы, щётка, пескоразбрасыватель, поливомоечная цистерна — навесное оборудование отдельными записями, а не поля модуля</t>
-        </is>
-      </c>
+          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5541,12 +5558,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Поливомоечная машина</t>
+          <t>Подметально-уборочная машина</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
+          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -5559,12 +5576,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Подметально-уборочная машина</t>
+          <t>Пескоразбрасыватель</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
+          <t>Объём бункера, м³; ширина распределения, м</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -5577,12 +5594,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Пескоразбрасыватель</t>
+          <t>Шнекороторный снегоочиститель</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³; ширина распределения, м</t>
+          <t>Производительность, т/ч; ширина захвата, м</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -5595,12 +5612,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Шнекороторный снегоочиститель</t>
+          <t>Каналопромывочная машина</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Производительность, т/ч; ширина захвата, м</t>
+          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -5613,35 +5630,39 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочная машина</t>
+          <t>Каналопромывочно-илососная машина</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>Поля каналопромывочной и илососной</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Один модуль</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочно-илососная машина</t>
+          <t>Пожарная автоцистерна (АЦ)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Поля каналопромывочной и илососной</t>
+          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Один модуль</t>
+          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5674,15 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автоцистерна (АЦ)</t>
+          <t>Пожарная автолестница (АЛ)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
-        </is>
-      </c>
+          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5675,12 +5692,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автолестница (АЛ)</t>
+          <t>Пожарный подъёмник (АКП, АТП)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
+          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -5693,12 +5710,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Пожарный подъёмник (АКП, АТП)</t>
+          <t>Пожарная насосная станция (ПНС)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
+          <t>Подача насоса, л/с</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -5711,12 +5728,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Пожарная насосная станция (ПНС)</t>
+          <t>Насосно-рукавный пожарный (АНР)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с</t>
+          <t>Подача насоса, л/с; запас рукавов, м</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -5729,12 +5746,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Насосно-рукавный пожарный (АНР)</t>
+          <t>Пожарный первой помощи (АПП)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с; запас рукавов, м</t>
+          <t>Подача насоса, л/с; запас воды, л</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -5747,12 +5764,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Пожарный первой помощи (АПП)</t>
+          <t>Пожарный пенного, порошкового или газового тушения</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с; запас воды, л</t>
+          <t>Огнетушащее вещество; масса или объём</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -5765,12 +5782,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Пожарный пенного, порошкового или газового тушения</t>
+          <t>Аэродромный пожарный</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Огнетушащее вещество; масса или объём</t>
+          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -5783,12 +5800,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Аэродромный пожарный</t>
+          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
+          <t>Вид; класс по массе (L, M, S); комплектность</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -5796,20 +5813,24 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
+          <t>Скорая помощь класса A (санитарная)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Вид; класс по массе (L, M, S); комплектность</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>По ГОСТ 33665-2015</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5819,19 +5840,15 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса A (санитарная)</t>
+          <t>Скорая помощь класса B (экстренная)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>По ГОСТ 33665-2015</t>
-        </is>
-      </c>
+          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5841,12 +5858,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса B (экстренная)</t>
+          <t>Реанимобиль (класс C)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
+          <t>Реанимационный комплект (перечень); автономное электропитание</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -5859,12 +5876,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Реанимобиль (класс C)</t>
+          <t>Передвижной медицинский кабинет</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Реанимационный комплект (перечень); автономное электропитание</t>
+          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -5872,17 +5889,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Передвижной медицинский кабинет</t>
+          <t>Передвижная лаборатория</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
+          <t>Профиль; приборы (перечень)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -5895,12 +5912,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Передвижная лаборатория</t>
+          <t>Передвижная автомастерская</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Профиль; приборы (перечень)</t>
+          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -5913,12 +5930,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Передвижная автомастерская</t>
+          <t>Аварийная газовой службы</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
+          <t>Генератор, кВт; газоанализаторы</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -5931,12 +5948,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Аварийная газовой службы</t>
+          <t>Аварийно-ремонтная (электросети, водоканал)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Генератор, кВт; газоанализаторы</t>
+          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -5949,12 +5966,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Аварийно-ремонтная (электросети, водоканал)</t>
+          <t>Инкассаторский автомобиль</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
+          <t>Класс защиты (Бр1–Бр5); сейф</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -5967,12 +5984,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Инкассаторский автомобиль</t>
+          <t>Оперативный (патрульный)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Класс защиты (Бр1–Бр5); сейф</t>
+          <t>Спецсигналы; отсек для задержанных; связь</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -5985,12 +6002,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Оперативный (патрульный)</t>
+          <t>Штабной автомобиль</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Спецсигналы; отсек для задержанных; связь</t>
+          <t>Рабочих мест; средства связи</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -6003,12 +6020,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Штабной автомобиль</t>
+          <t>Передвижной офис (бытовка)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Рабочих мест; средства связи</t>
+          <t>Мест; отопление; санузел</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -6021,15 +6038,19 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Передвижной офис (бытовка)</t>
+          <t>Вахтовый автобус</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Мест; отопление; санузел</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6039,19 +6060,15 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Вахтовый автобус</t>
+          <t>Автодом</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
-        </is>
-      </c>
+          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6061,12 +6078,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Автодом</t>
+          <t>Автолавка (торговый фургон)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
+          <t>Торговое окно; холодильные витрины; весы</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -6079,12 +6096,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Автолавка (торговый фургон)</t>
+          <t>Хлебный фургон</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Торговое окно; холодильные витрины; весы</t>
+          <t>Лотков; стеллажи</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -6097,12 +6114,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Хлебный фургон</t>
+          <t>Катафалк</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Лотков; стеллажи</t>
+          <t>Мест для гроба; сидячих мест</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -6115,12 +6132,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Катафалк</t>
+          <t>Спецоборудование салона автобуса</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Мест для гроба; сидячих мест</t>
+          <t>Профиль; оборудование (перечень)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -6133,12 +6150,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Спецоборудование салона автобуса</t>
+          <t>Электростанция (дизель-генератор)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Профиль; оборудование (перечень)</t>
+          <t>Мощность, кВт; напряжение, В; топливный бак, л; моточасы; кожух</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -6151,12 +6168,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Электростанция (дизель-генератор)</t>
+          <t>Компрессорная установка</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Мощность, кВт; напряжение, В; топливный бак, л; моточасы; кожух</t>
+          <t>Производительность, м³/мин; рабочее давление, бар; моточасы; приёмник</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -6169,12 +6186,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Компрессорная установка</t>
+          <t>Насосная установка (мотопомпа)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Производительность, м³/мин; рабочее давление, бар; моточасы; приёмник</t>
+          <t>Подача, л/мин; напор, м; диаметр патрубков, мм; привод</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -6182,17 +6199,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Насосная установка (мотопомпа)</t>
+          <t>Цементировочный агрегат (ЦА)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Подача, л/мин; напор, м; диаметр патрубков, мм; привод</t>
+          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -6205,12 +6222,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Цементировочный агрегат (ЦА)</t>
+          <t>Насосный агрегат</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
+          <t>Давление, МПа; подача, л/с</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -6223,12 +6240,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Насосный агрегат</t>
+          <t>Паропередвижная установка (ППУ)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Давление, МПа; подача, л/с</t>
+          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -6241,12 +6258,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Паропередвижная установка (ППУ)</t>
+          <t>Агрегат депарафинизации (АДПМ)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
+          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -6259,12 +6276,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Агрегат депарафинизации (АДПМ)</t>
+          <t>Подъёмник ремонта скважин</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
+          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -6277,12 +6294,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Подъёмник ремонта скважин</t>
+          <t>Смесительная установка</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
+          <t>Объём бункера, м³</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -6295,12 +6312,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Смесительная установка</t>
+          <t>Каротажный подъёмник (лаборатория)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³</t>
+          <t>Глубина, м; кабель, м</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -6308,17 +6325,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Сельскохозяйственные</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Каротажный подъёмник (лаборатория)</t>
+          <t>Кормовоз</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Глубина, м; кабель, м</t>
+          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -6331,12 +6348,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Кормовоз</t>
+          <t>Кормораздатчик на шасси</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
+          <t>Объём, м³; взвешивание</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -6344,20 +6361,24 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Навесное на тракторе</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Кормораздатчик на шасси</t>
+          <t>Экскаваторное оборудование</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; взвешивание</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>Глубина копания, м; заводской номер</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6367,17 +6388,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Экскаваторное оборудование</t>
+          <t>Погрузочное оборудование</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Глубина копания, м; заводской номер</t>
+          <t>Грузоподъёмность, т</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
+          <t>ПКУ-0,8</t>
         </is>
       </c>
     </row>
@@ -6389,17 +6410,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Погрузочное оборудование</t>
+          <t>Бульдозерное оборудование</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т</t>
+          <t>Ширина отвала, мм; высота, мм; поворотный</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>ПКУ-0,8</t>
+          <t>ДЗ-42 на ДТ-75</t>
         </is>
       </c>
     </row>
@@ -6411,17 +6432,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Бульдозерное оборудование</t>
+          <t>Траншеекопатель</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Ширина отвала, мм; высота, мм; поворотный</t>
+          <t>Глубина траншеи, м; ширина, мм</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>ДЗ-42 на ДТ-75</t>
+          <t>ЭТЦ на МТЗ</t>
         </is>
       </c>
     </row>
@@ -6433,19 +6454,15 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Траншеекопатель</t>
+          <t>Коммунальное оборудование</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Глубина траншеи, м; ширина, мм</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>ЭТЦ на МТЗ</t>
-        </is>
-      </c>
+          <t>Отвал; щётка; разбрасыватель — перечень</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6455,40 +6472,22 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Коммунальное оборудование</t>
+          <t>Трубоукладочное оборудование</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Отвал; щётка; разбрасыватель — перечень</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Навесное на тракторе</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Трубоукладочное оборудование</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
           <t>Грузоподъёмность, т; момент устойчивости, т·м</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>На Т-170</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D104"/>
+  <autoFilter ref="A1:D103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6707,7 +6706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7491,7 +7490,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Трактор</t>
+          <t>Комбайн зерноуборочный</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -7501,12 +7500,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Тяговый класс (ГОСТ 27021-86); колёсная формула; тип гусениц; колея, мм; ВОМ, об/мин; задняя навеска (категория); передняя навеска</t>
+          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки (жатка — навесное оборудование отдельной записью)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>МТЗ-80/82/1221, Т-150К, К-700, LOVOL, John Deere; ДТ-75, Т-4А</t>
+          <t>Нива, Енисей, Дон-1500, Акрос, Палессе, Claas</t>
         </is>
       </c>
     </row>
@@ -7518,22 +7517,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Комбайн зерноуборочный</t>
+          <t>Комбайн кормоуборочный</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная</t>
+          <t>колёсная</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки (жатка — навесное оборудование отдельной записью)</t>
+          <t>Мощность; ножей измельчителя</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Нива, Енисей, Дон-1500, Акрос, Палессе, Claas</t>
+          <t>Дон-680, Палессе FS, Claas Jaguar</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7544,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Комбайн кормоуборочный</t>
+          <t>Самоходный опрыскиватель</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -7555,14 +7554,10 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Мощность; ножей измельчителя</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Дон-680, Палессе FS, Claas Jaguar</t>
-        </is>
-      </c>
+          <t>Ёмкость бака, л; ширина штанги, м; клиренс, мм</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -7572,7 +7567,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Самоходный опрыскиватель</t>
+          <t>Самоходная косилка</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -7582,20 +7577,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Ёмкость бака, л; ширина штанги, м; клиренс, мм</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>Ширина захвата, м; плющилка</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>КСУ-1, Палессе CS</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Самоходная косилка</t>
+          <t>Самоходная подметальная машина</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -7605,125 +7604,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Ширина захвата, м; плющилка</t>
+          <t>Ширина подметания, м; бункер, л; увлажнение</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>КСУ-1, Палессе CS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Вездеходы</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Снегоболотоход</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>колёсная, гусеничная</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Полная масса, т; мест; грузоподъёмность, т; плавающий</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>ТРЭКОЛ, Шерп, Бурлак</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Вездеходы</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Гусеничный транспортёр</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>гусеничная</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; буксируемая масса, т; мест; плавающий; исходная модель; переоборудование (вид, документ)</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>МТ-ЛБ, ГАЗ-71, ГТ-Т, «Витязь»</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Коммунальные</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Самоходная подметальная машина</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>колёсная</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Ширина подметания, м; бункер, л; увлажнение</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
           <t>Tennant, Hako</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Коммунальные</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Коммунальный минитрактор</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>колёсная</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Мощность; передняя навеска; ВОМ</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Беларус-132Н, Holder</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E39"/>
+  <autoFilter ref="A1:E35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -37,8 +37,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Решения'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Не проверено'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Источники'!$A$1:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Не проверено'!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Источники'!$A$1:$B$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2124,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2146,29 +2146,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Регистрация техники в КР</t>
+          <t>Надзор за подъёмными сооружениями в КР</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Точный текст ПП КР №407 о регистрации тракторов и самоходных машин не проверен</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Надзор за подъёмными сооружениями в КР</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
           <t>Какой орган ведёт учёт кранов, подъёмников и КМУ — нужно для поля «учёт в надзоре»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2179,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2426,8 +2414,56 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Кыргызстан: Правила государственной регистрации ТС, установок и оборудования (ПП № 407 от 23.06.2017)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://cbd.minjust.gov.kg/100149/edition/11377/ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Кыргызстан: Правила регистрации и учёта автомототранспортных средств (МВД, 05.10.1999)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://cbd.minjust.gov.kg/51-569/edition/433613/ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт самоходной машины и других видов техники: графы бланка</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kontur-extern.ru/info/normativ/document/44/10349-pasport-samokhodnoy-mashiny-i-drugikh-vidov-tekhniki</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Кыргызстан: проверка ТС по госномеру (car check)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://portal.tunduk.kg/public_services/opisanie/207</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B20"/>
+  <autoFilter ref="A1:B24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -15,30 +15,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля модуля" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Самоходные машины" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля самоходной машины" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Навесное и сменное" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поля навесного" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Не проверено" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прицепные машины" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Примеры отнесения" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Решения" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Правила'!$A$1:$C$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Базы'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Поля базы'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Модули'!$A$1:$D$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Поля модуля'!$A$1:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Модули'!$A$1:$D$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Поля модуля'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Самоходные машины'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Поля самоходной машины'!$A$1:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Навесное и сменное'!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Поля навесного'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Решения'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Не проверено'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Источники'!$A$1:$B$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Прицепные машины'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Примеры отнесения'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Решения'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Источники'!$A$1:$B$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -514,7 +508,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Каждая единица относится ровно к одному виду: ТС одной из категорий техпаспорта (база + модули; прицеп и полуприцеп — тоже база), самоходная машина собственной конструкции, сменное навесное оборудование.</t>
+          <t>Каждая единица относится ровно к одному виду: ТС одной из категорий техпаспорта (база + модули; прицеп и полуприцеп — тоже база), самоходная машина собственной конструкции, модуль (надстройка, навесное и сменное оборудование) — на машине или без неё.</t>
         </is>
       </c>
     </row>
@@ -599,7 +593,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ковши, вилы, жатки, отвалы, щётки, бункеры — всегда навесное оборудование отдельной записью, даже когда пришли вместе с машиной. В поля машины они не выносятся. Исключение — несъёмный кузов-ковш думпера и скрепера: это часть машины.</t>
+          <t>Ковши, вилы, жатки, отвалы, щётки, бункеры — всегда модули, даже когда пришли вместе с машиной. В поля машины они не выносятся. Исключение — несъёмный кузов-ковш думпера и скрепера: это часть машины.</t>
         </is>
       </c>
     </row>
@@ -701,7 +695,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Есть свои колёса — прицеп (база «Прицепная машина»): прицепная сеялка, пресс-подборщик, плуг на колёсах. Без колёс — навесное оборудование: навесной плуг, отвал, ковш.</t>
+          <t>Есть свои колёса — прицеп (база «Прицепная машина»): прицепная сеялка, пресс-подборщик, плуг на колёсах. Без колёс — модуль: навесной плуг, отвал, ковш.</t>
         </is>
       </c>
     </row>
@@ -713,12 +707,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Сменное навесное</t>
+          <t>Навесное — это модули</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Оборудование, которое ставится штатно и поочерёдно (быстросъём, трёхточечная навеска), — отдельная запись со связью «установлено на». Оценивается и в составе машины, и отдельно. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
+          <t>Навесное и сменное оборудование (быстросъём, трёхточечная навеска) — модули, как надстройки. Модуль ставится на базу или на самоходную машину (экскаватор с гидромолотом, погрузчик с вилами, комбайн с жаткой) и может числиться без машины — снятый ковш, жатка на тележке. Виды различаются по назначению: ковш (грунт, сыпучее) и вилы (паллеты) — разные.</t>
         </is>
       </c>
     </row>
@@ -769,7 +763,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Сменные контейнеры мультилифта, бункеры бункеровоза, жатки комбайна — сменное оборудование, отдельные записи, а не модуль ТС.</t>
+          <t>Контейнер мультилифта, бункер бункеровоза, жатка комбайна — модули. Мультилифт с контейнером — два модуля на одной базе (правило 3).</t>
         </is>
       </c>
     </row>
@@ -900,12 +894,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Дополнительные поля</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Особые отметки документа и всё, чему нет своего поля, — в таблицу дополнительных полей: название и значение пишет пользователь.</t>
+          <t>Особые отметки документа и всё, чему нет своего поля, — в таблицу дополнительных параметров: название и значение пишет пользователь.</t>
         </is>
       </c>
     </row>
@@ -922,394 +916,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Трактор (в том числе мини-трактор) и вездеход, гусеничный транспортёр заводятся только базой категории «Спецтехника», на листе самоходных машин их нет. Без навесного — база без модулей, с навесным или кунгом — база и модули.</t>
+          <t>Трактор (в том числе мини-трактор) и вездеход, гусеничный транспортёр заводятся только базой категории «Спецтехника», на листе самоходных машин их нет. Без навесного — база без модулей, с навесным или кунгом — база и модули. Машины, которые только называются тракторами, а оборудование у них встроено (трелёвочный трактор), — самоходные (правило 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Поля модуля</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>У всех модулей одни поля: вид, изготовитель, модель установки, заводской номер, год, моточасы, состояние, комплектность — то, что видно в техпаспорте или по фото с осмотра. Остальное — в таблицу дополнительных параметров: поля модулей слишком разные, чтобы зашивать их.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C26"/>
+  <autoFilter ref="A1:C27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Поле</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Пояснение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Вид</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Назначение</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Изготовитель</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Заводской номер</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Год выпуска</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>год</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Масса</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Класс машины-носителя по массе</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>для экскаватора: 1–3, 3–8, 12–25, 25–40 т</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Тип крепления</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>штифты, гидробыстросъём, механический быстросъём, Euro, SAE-плита, трёхточечная навеска кат. 1/2/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Требуемая гидравлика</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>бар; л/мин; линий</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>давление, расход, число линий — отдельными полями</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Установлено на</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>связь с машиной</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>необязательно; с датами</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Входит в заводскую комплектацию</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>да / нет</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Техническое состояние</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C14"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Вид</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Поля сверх общих полей прицепа</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Сеялка прицепная</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, м; рядов; бункер, л</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Опрыскиватель прицепной</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Ёмкость бака, л; ширина штанги, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Пресс-подборщик</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Тип тюка (рулон, квадрат); размер тюка; ширина подборщика, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Косилка прицепная</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, м; плющилка</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Разбрасыватель удобрений</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; ширина разбрасывания, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Кормораздатчик (миксер) прицепной</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Объём бункера, м³</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Борона дисковая прицепная</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, м; рабочая глубина, см</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Культиватор прицепной</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, м; рабочая глубина, см</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Скрепер прицепной</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Объём ковша, м³</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Транспортная тележка жатки</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Длина, м; грузоподъёмность, т</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1488,15 +1122,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>База: лёгкий коммерческий, цельнометаллический фургон</t>
+          <t>База: лёгкий коммерческий, исполнение «цельнометаллический фургон»</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Модуль: базовый модуль</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Модуль не заводится</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1595,7 +1233,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Навесное: щётка; отвал снежный</t>
+          <t>Модули: щётка коммунальная; отвал снежный</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -1689,12 +1327,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Сменное: вилы паллетные; гидромолот</t>
+          <t>Модули: вилы паллетные; гидромолот</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Отдельные записи со связью</t>
+          <t>Модули на самоходной машине</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1344,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Сменное навесное: плуг навесной</t>
+          <t>Модуль без машины: плуг навесной</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1777,7 +1415,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Сменное: жатка зерновая</t>
+          <t>Модуль: жатка зерновая</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1792,7 +1430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2023,7 +1661,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Навесное оборудование отдельной записью, в поля машины не выносится</t>
+          <t>Модуль, в поля машины не выносится</t>
         </is>
       </c>
     </row>
@@ -2040,7 +1678,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Модуль КДМ, а отвал, щётка и бункер — навесное оборудование</t>
+          <t>Модуль КДМ, а отвал, щётка и пескоразбрасыватель — отдельные модули на той же базе</t>
         </is>
       </c>
     </row>
@@ -2118,50 +1756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Что</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Пояснение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Надзор за подъёмными сооружениями в КР</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Какой орган ведёт учёт кранов, подъёмников и КМУ — нужно для поля «учёт в надзоре»</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2518,7 +2113,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>До 8 пассажирских мест, полная масса до 3,5 т. Пикап относится по полю «Тип ТС, вид кузова» в свидетельстве.</t>
+          <t>До 8 пассажирских мест, максимальная разрешённая масса до 3,5 т. Пикап относится по полю «Тип ТС, вид кузова» в свидетельстве.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2804,7 +2399,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Работает сам по себе и несёт навесное оборудование — тогда он база.</t>
+          <t>Работает сам по себе и несёт навесные модули — тогда он база.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2826,7 +2421,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Гусеничный или колёсный ход сверхвысокой проходимости, учёт как самоходной машины.</t>
+          <t>Гусеничный или колёсный ход сверхвысокой проходимости; регистрируется по техническому паспорту, как самоходная машина.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3602,7 +3197,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Дополнительные поля</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3688,7 +3283,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3337,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3364,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3437,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3491,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3572,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -4200,7 +3795,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -4254,7 +3849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -4281,7 +3876,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная; можно несколько</t>
+          <t>колёсная, гусеничная, полугусеничная, вальцовая, шнековая, шагающая, на полозьях; можно несколько</t>
         </is>
       </c>
     </row>
@@ -4389,7 +3984,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>лицензионная и китайская сборка, рынок праворульных машин</t>
+          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4011,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная, шнековая; можно несколько</t>
+          <t>колёсная, гусеничная, полугусеничная, вальцовая, шнековая, шагающая, на полозьях; можно несколько</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4142,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная, вальцовая, шнековая, шагающая; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
+          <t>колёсная, гусеничная, полугусеничная, вальцовая, шнековая, шагающая, на полозьях; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4585,7 +4180,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Поля модуля</t>
+          <t>Что обычно вписывают в дополнительные параметры</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -4750,7 +4345,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Контейнеры — сменное оборудование</t>
+          <t>Контейнер — отдельный модуль на той же базе</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4367,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Бункеры — сменное оборудование</t>
+          <t>Бункер — отдельный модуль на той же базе</t>
         </is>
       </c>
     </row>
@@ -4935,44 +4530,44 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Цистерны</t>
+          <t>Грузовые кузова</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Бензовоз (светлые нефтепродукты)</t>
+          <t>Контейнер мультилифта</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
+          <t>Вид (самосвальный, мусорный, цистерна, бытовка); объём, м³</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
+          <t>Перевозка</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Цистерны</t>
+          <t>Грузовые кузова</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Топливозаправщик</t>
+          <t>Бункер бункеровоза</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
+          <t>Объём, м³</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Заправляет технику на месте</t>
+          <t>Мусор</t>
         </is>
       </c>
     </row>
@@ -4984,15 +4579,19 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Масловоз, маслозаправщик</t>
+          <t>Бензовоз (светлые нефтепродукты)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; продуктов</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>Общие для цистерн* ; нижний налив; возврат паров</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>* Общие для цистерн: продукт; объём, м³; секций и объём каждой; материал; изоляция и подогрев; насос; счётчик; класс ДОПОГ; дата освидетельствования</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5002,15 +4601,19 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Нефтевоз, мазутовоз</t>
+          <t>Топливозаправщик</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; подогрев</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>Общие для цистерн; раздаточный рукав; фильтр; раздаточный пистолет</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Заправляет технику на месте</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5020,12 +4623,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Битумовоз</t>
+          <t>Масловоз, маслозаправщик</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; горелка; температура удержания, °C</t>
+          <t>Общие для цистерн; продуктов</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -5038,12 +4641,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Газовоз (пропан-бутан)</t>
+          <t>Нефтевоз, мазутовоз</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; рабочее давление, МПа</t>
+          <t>Общие для цистерн; подогрев</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -5056,12 +4659,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Водовоз технический</t>
+          <t>Битумовоз</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн</t>
+          <t>Общие для цистерн; горелка; температура удержания, °C</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -5074,12 +4677,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Водовоз питьевой</t>
+          <t>Газовоз (пропан-бутан)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
+          <t>Общие для цистерн; рабочее давление, МПа</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -5092,7 +4695,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Молоковоз</t>
+          <t>Водовоз технический</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5110,12 +4713,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Пищевая цистерна</t>
+          <t>Водовоз питьевой</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
+          <t>Общие для цистерн; пищевое покрытие; санитарное разрешение</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -5128,12 +4731,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Цементовоз, муковоз (сыпучие)</t>
+          <t>Молоковоз</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
+          <t>Общие для цистерн</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -5146,12 +4749,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Химическая цистерна</t>
+          <t>Пищевая цистерна</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; футеровка</t>
+          <t>Общие для цистерн; продукт (масло, патока, спирт, вино)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -5164,12 +4767,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ассенизаторская (вакуумная)</t>
+          <t>Цементовоз, муковоз (сыпучие)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
+          <t>Общие для цистерн; компрессор, м³/мин; угол днища</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -5182,12 +4785,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Илососная</t>
+          <t>Химическая цистерна</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
+          <t>Общие для цистерн; футеровка</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -5200,12 +4803,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Передвижная АЗС</t>
+          <t>Ассенизаторская (вакуумная)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; секций; насос; счётчик; раздаточных пистолетов; заземление</t>
+          <t>Общие для цистерн; вакуумный насос: марка, производительность; глубина всасывания, м</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -5213,39 +4816,35 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Цистерны</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Автокран</t>
+          <t>Илососная</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Класс различает база</t>
-        </is>
-      </c>
+          <t>Общие для цистерн; вакуумный насос; стрела с рукавом; опрокидывание цистерны</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Подъёмные</t>
+          <t>Цистерны</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Кран-манипулятор (КМУ)</t>
+          <t>Передвижная АЗС</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
+          <t>Объём, м³; секций; насос; счётчик; раздаточных пистолетов; заземление</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -5258,15 +4857,19 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Лесной гидроманипулятор</t>
+          <t>Автокран</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Грузоподъёмность, т; длина стрелы, м; удлинитель, м; вылет, м; высота подъёма крюка, м; секций стрелы; привод (механический, гидравлический); противовес, т</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Класс различает база</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -5276,34 +4879,30 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Автовышка</t>
+          <t>Кран-манипулятор (КМУ)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Автогидроподъёмник (АГП) — синоним</t>
-        </is>
-      </c>
+          <t>Грузовой момент, т·м; грузоподъёмность, т; вылет, м; секций; место установки (за кабиной, сзади); ротатор</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Эвакуаторы</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с платформой</t>
+          <t>Лесной гидроманипулятор</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
+          <t>Вылет, м; грузовой момент, т·м; грейфер</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -5311,20 +4910,24 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Эвакуаторы</t>
+          <t>Подъёмные</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор с частичной погрузкой</t>
+          <t>Автовышка</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>Рабочая высота, м; вылет, м; грузоподъёмность люльки, кг; тип стрелы (телескопическая, коленчатая, комбинированная); изолированное исполнение</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Автогидроподъёмник (АГП) — синоним</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -5334,12 +4937,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Эвакуатор-ротатор</t>
+          <t>Эвакуатор с платформой</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
+          <t>Тип платформы (сдвижная, ломаная); длина платформы, мм; грузоподъёмность, т; лебёдка, т</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -5347,17 +4950,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Строительные и дорожные</t>
+          <t>Эвакуаторы</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Автобетоносмеситель (миксер)</t>
+          <t>Эвакуатор с частичной погрузкой</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
+          <t>Тип захвата; грузоподъёмность захвата, т; длина стрелы, м</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -5365,17 +4968,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Строительные и дорожные</t>
+          <t>Эвакуаторы</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Автобетононасос</t>
+          <t>Эвакуатор-ротатор</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
+          <t>Грузоподъёмность стрелы, т; поворот стрелы</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -5388,12 +4991,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Буровая установка</t>
+          <t>Автобетоносмеситель (миксер)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
+          <t>Объём барабана, м³; привод (от КОМ, свой двигатель); бак воды, л</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -5406,12 +5009,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Ямобур (бурильно-крановая машина)</t>
+          <t>Автобетононасос</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
+          <t>Длина стрелы, м; секций; производительность, м³/ч; давление, бар</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -5424,12 +5027,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Автогудронатор</t>
+          <t>Буровая установка</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
+          <t>Назначение (водозаборная, геологоразведочная); глубина бурения, м; диаметр, мм; мачта, м</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -5442,12 +5045,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Асфальтовоз-термос</t>
+          <t>Ямобур (бурильно-крановая машина)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Объём кузова, м³; подогрев</t>
+          <t>Диаметр ямы, мм; глубина, м; грузоподъёмность крана, т</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -5460,19 +5063,15 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Распределитель щебня</t>
+          <t>Автогудронатор</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Ширина распределения, м</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Обычно дополнительный модуль на самосвале</t>
-        </is>
-      </c>
+          <t>Объём цистерны, м³; ширина розлива, м; подогрев</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5482,12 +5081,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Дорожный ремонтёр (ямочный ремонт)</t>
+          <t>Асфальтовоз-термос</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Термобункер, м³; ёмкость эмульсии, л</t>
+          <t>Объём кузова, м³; подогрев</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -5495,35 +5094,39 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с задней загрузкой</t>
+          <t>Распределитель щебня</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>Ширина распределения, м</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Обычно дополнительный модуль на самосвале</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с боковой загрузкой</t>
+          <t>Дорожный ремонтёр (ямочный ремонт)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; манипулятор, грузоподъёмность</t>
+          <t>Термобункер, м³; ёмкость эмульсии, л</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -5531,132 +5134,156 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Мусоровоз с фронтальной загрузкой</t>
+          <t>Экскаваторное оборудование</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; грузоподъёмность вил, т</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
+          <t>Глубина копания, м; заводской номер</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Комбинированная дорожная машина (КДМ)</t>
+          <t>Трубоукладочное оборудование</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Гидравлика для сменного оборудования; места навески (переднее, среднее, заднее)</t>
+          <t>Грузоподъёмность, т; момент устойчивости, т·м</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Отвалы, щётка, пескоразбрасыватель, поливомоечная цистерна — навесное оборудование отдельными записями, а не поля модуля</t>
+          <t>На Т-170</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Поливомоечная машина</t>
+          <t>Отвал бульдозерный</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
+          <t>Ширина, мм; высота, мм; поворотный</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Перемещение грунта</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Подметально-уборочная машина</t>
+          <t>Фреза дорожная</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
+          <t>Ширина, мм; глубина, мм</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Снятие асфальта</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Пескоразбрасыватель</t>
+          <t>Мульчер (лесная фреза)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³; ширина распределения, м</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+          <t>Ширина захвата, мм; диаметр ствола, мм</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Расчистка поросли</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Шнекороторный снегоочиститель</t>
+          <t>Виброплита навесная</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Производительность, т/ч; ширина захвата, м</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>Усилие, кН; частота, Гц</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение в траншеях</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Коммунальные</t>
+          <t>Строительные и дорожные</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочная машина</t>
+          <t>Траншеекопатель навесной</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>Глубина, м; ширина, мм</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Траншеи под кабель</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5666,56 +5293,48 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Каналопромывочно-илососная машина</t>
+          <t>Мусоровоз с задней загрузкой</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Поля каналопромывочной и илососной</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Один модуль</t>
-        </is>
-      </c>
+          <t>Объём кузова, м³; коэффициент уплотнения; загрузка</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автоцистерна (АЦ)</t>
+          <t>Мусоровоз с боковой загрузкой</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
-        </is>
-      </c>
+          <t>Объём, м³; манипулятор, грузоподъёмность</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Пожарная автолестница (АЛ)</t>
+          <t>Мусоровоз с фронтальной загрузкой</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
+          <t>Объём, м³; грузоподъёмность вил, т</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -5723,53 +5342,61 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Пожарный подъёмник (АКП, АТП)</t>
+          <t>Комбинированная дорожная машина (КДМ)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
+          <t>Гидравлика для сменного оборудования; места навески (переднее, среднее, заднее)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Отвалы, щётка, пескоразбрасыватель, поливомоечное оборудование — отдельные модули на той же базе</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Пожарная насосная станция (ПНС)</t>
+          <t>Поливомоечное оборудование</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>стационарное или сменное</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Насосно-рукавный пожарный (АНР)</t>
+          <t>Подметально-уборочная машина</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с; запас рукавов, м</t>
+          <t>Объём бункера, м³; бак воды, л; ширина подметания, м; способ (вакуумный, механический)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -5777,35 +5404,39 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Пожарный первой помощи (АПП)</t>
+          <t>Пескоразбрасыватель</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Подача насоса, л/с; запас воды, л</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
+          <t>Объём бункера, м³; ширина распределения, м</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>стационарный или сменный</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Пожарный пенного, порошкового или газового тушения</t>
+          <t>Шнекороторный снегоочиститель</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Огнетушащее вещество; масса или объём</t>
+          <t>Производительность, т/ч; ширина захвата, м</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -5813,17 +5444,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Аэродромный пожарный</t>
+          <t>Каналопромывочная машина</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
+          <t>Давление, бар; производительность, л/мин; объём воды, м³; рукав, м</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -5831,111 +5462,127 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Пожарные</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
+          <t>Каналопромывочно-илососная машина</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Вид; класс по массе (L, M, S); комплектность</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+          <t>Поля каналопромывочной и илососной</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Один модуль</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса A (санитарная)</t>
+          <t>Отвал снежный</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
+          <t>Ширина, мм; угол поворота, °; нож (металл, полиуретан)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>По ГОСТ 33665-2015</t>
+          <t>Снегоочистка</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Скорая помощь класса B (экстренная)</t>
+          <t>Щётка коммунальная</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
+          <t>Ширина, мм; диаметр щётки, мм; бункер; увлажнение</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Подметание</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Коммунальные</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Реанимобиль (класс C)</t>
+          <t>Снегоочиститель фрезерно-роторный</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Реанимационный комплект (перечень); автономное электропитание</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
+          <t>Ширина, мм; дальность выброса, м</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Снегоочистка</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Медицинские</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Передвижной медицинский кабинет</t>
+          <t>Пожарная автоцистерна (АЦ)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Объём цистерны воды, м³; пенобак, л; подача насоса, л/с; напор, м; ступень высокого давления; лафетный ствол; боевой расчёт</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Обозначение по ГОСТ Р 53247: АЦ 3,0-40/4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Передвижная лаборатория</t>
+          <t>Пожарная автолестница (АЛ)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Профиль; приборы (перечень)</t>
+          <t>Высота лестницы, м; вылет, м; люлька, кг</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -5943,17 +5590,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Передвижная автомастерская</t>
+          <t>Пожарный подъёмник (АКП, АТП)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
+          <t>Рабочая высота, м; люлька, кг; лафетный ствол</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -5961,17 +5608,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Аварийная газовой службы</t>
+          <t>Пожарная насосная станция (ПНС)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Генератор, кВт; газоанализаторы</t>
+          <t>Подача насоса, л/с</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -5979,17 +5626,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Аварийно-ремонтная (электросети, водоканал)</t>
+          <t>Насосно-рукавный пожарный (АНР)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
+          <t>Подача насоса, л/с; запас рукавов, м</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -5997,17 +5644,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Инкассаторский автомобиль</t>
+          <t>Пожарный первой помощи (АПП)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Класс защиты (Бр1–Бр5); сейф</t>
+          <t>Подача насоса, л/с; запас воды, л</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -6015,17 +5662,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Оперативный (патрульный)</t>
+          <t>Пожарный пенного, порошкового или газового тушения</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Спецсигналы; отсек для задержанных; связь</t>
+          <t>Огнетушащее вещество; масса или объём</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -6033,17 +5680,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Штабной автомобиль</t>
+          <t>Аэродромный пожарный</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Рабочих мест; средства связи</t>
+          <t>Вода, м³; пена, л; порошок, кг; подача, л/с</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -6051,17 +5698,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Пожарные</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Передвижной офис (бытовка)</t>
+          <t>Пожарный вспомогательный (аварийно-спасательный, штабной, рукавный)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Мест; отопление; санузел</t>
+          <t>Вид; класс по массе (L, M, S); комплектность</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -6069,39 +5716,39 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Вахтовый автобус</t>
+          <t>Скорая помощь класса A (санитарная)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
+          <t>Носилочных мест; сидячих мест; спецсигналы; медоборудование (перечень)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
+          <t>По ГОСТ 33665-2015</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Автодом</t>
+          <t>Скорая помощь класса B (экстренная)</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
+          <t>Дефибриллятор; аппарат ИВЛ; монитор; кислород, л; медоборудование (перечень)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -6109,17 +5756,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Автолавка (торговый фургон)</t>
+          <t>Реанимобиль (класс C)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Торговое окно; холодильные витрины; весы</t>
+          <t>Реанимационный комплект (перечень); автономное электропитание</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -6127,17 +5774,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Служебные и аварийные</t>
+          <t>Медицинские</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Хлебный фургон</t>
+          <t>Передвижной медицинский кабинет</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Лотков; стеллажи</t>
+          <t>Профиль (флюорограф, маммограф, ФАП, стоматология); основное медоборудование: марка, год</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -6150,12 +5797,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Катафалк</t>
+          <t>Передвижная лаборатория</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Мест для гроба; сидячих мест</t>
+          <t>Профиль; приборы (перечень)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -6168,12 +5815,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Спецоборудование салона автобуса</t>
+          <t>Передвижная автомастерская</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Профиль; оборудование (перечень)</t>
+          <t>Сварочный агрегат, кВт; генератор, кВт; компрессор; кран-балка</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -6186,12 +5833,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Электростанция (дизель-генератор)</t>
+          <t>Аварийная газовой службы</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Мощность, кВт; напряжение, В; топливный бак, л; моточасы; кожух</t>
+          <t>Генератор, кВт; газоанализаторы</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -6204,12 +5851,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Компрессорная установка</t>
+          <t>Аварийно-ремонтная (электросети, водоканал)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Производительность, м³/мин; рабочее давление, бар; моточасы; приёмник</t>
+          <t>Профиль службы; генератор, кВт; компрессор; мотопомпа</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -6222,12 +5869,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Насосная установка (мотопомпа)</t>
+          <t>Инкассаторский автомобиль</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Подача, л/мин; напор, м; диаметр патрубков, мм; привод</t>
+          <t>Класс защиты (Бр1–Бр5); сейф</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -6235,17 +5882,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Цементировочный агрегат (ЦА)</t>
+          <t>Оперативный (патрульный)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
+          <t>Спецсигналы; отсек для задержанных; связь</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -6253,17 +5900,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Насосный агрегат</t>
+          <t>Штабной автомобиль</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Давление, МПа; подача, л/с</t>
+          <t>Рабочих мест; средства связи</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -6271,17 +5918,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Паропередвижная установка (ППУ)</t>
+          <t>Передвижной офис (бытовка)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
+          <t>Мест; отопление; санузел</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -6289,35 +5936,39 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Агрегат депарафинизации (АДПМ)</t>
+          <t>Вахтовый автобус</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
+          <t>Пассажирских мест; отопитель (свой, от двигателя); северное исполнение; багажный отсек</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Урал, КамАЗ, ГАЗ «Садко»</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Подъёмник ремонта скважин</t>
+          <t>Автодом</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
+          <t>Спальных мест; кухня; санузел; запас воды, л; генератор</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -6325,17 +5976,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Смесительная установка</t>
+          <t>Автолавка (торговый фургон)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Объём бункера, м³</t>
+          <t>Торговое окно; холодильные витрины; весы</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -6343,17 +5994,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Нефтегазовые</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Каротажный подъёмник (лаборатория)</t>
+          <t>Хлебный фургон</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Глубина, м; кабель, м</t>
+          <t>Лотков; стеллажи</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -6361,17 +6012,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Кормовоз</t>
+          <t>Катафалк</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
+          <t>Мест для гроба; сидячих мест</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -6379,17 +6030,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Сельскохозяйственные</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Кормораздатчик на шасси</t>
+          <t>Спецоборудование салона автобуса</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Объём, м³; взвешивание</t>
+          <t>Профиль; оборудование (перечень)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -6397,105 +6048,89 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Экскаваторное оборудование</t>
+          <t>Электростанция (дизель-генератор)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Глубина копания, м; заводской номер</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>ЭО-2621 на МТЗ, ЮМЗ</t>
-        </is>
-      </c>
+          <t>Мощность, кВт; напряжение, В; топливный бак, л; моточасы; кожух</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Погрузочное оборудование</t>
+          <t>Компрессорная установка</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>ПКУ-0,8</t>
-        </is>
-      </c>
+          <t>Производительность, м³/мин; рабочее давление, бар; моточасы; приёмник</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Служебные и аварийные</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Бульдозерное оборудование</t>
+          <t>Насосная установка (мотопомпа)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Ширина отвала, мм; высота, мм; поворотный</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>ДЗ-42 на ДТ-75</t>
-        </is>
-      </c>
+          <t>Подача, л/мин; напор, м; диаметр патрубков, мм; привод</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Траншеекопатель</t>
+          <t>Цементировочный агрегат (ЦА)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Глубина траншеи, м; ширина, мм</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>ЭТЦ на МТЗ</t>
-        </is>
-      </c>
+          <t>Давление, МПа; подача насоса, л/с; мерный бак, м³</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Коммунальное оборудование</t>
+          <t>Насосный агрегат</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Отвал; щётка; разбрасыватель — перечень</t>
+          <t>Давление, МПа; подача, л/с</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
@@ -6503,27 +6138,725 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Навесное на тракторе</t>
+          <t>Нефтегазовые</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Трубоукладочное оборудование</t>
+          <t>Паропередвижная установка (ППУ)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Грузоподъёмность, т; момент устойчивости, т·м</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>На Т-170</t>
+          <t>Паропроизводительность, т/ч; давление, МПа; температура пара, °C; цистерна воды, м³</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Нефтегазовые</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Агрегат депарафинизации (АДПМ)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Тепловая мощность, кВт; температура, °C; давление, МПа</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Нефтегазовые</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Подъёмник ремонта скважин</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность на крюке, т; высота мачты, м; глубина, м</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Нефтегазовые</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Смесительная установка</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Объём бункера, м³</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Нефтегазовые</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Каротажный подъёмник (лаборатория)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Глубина, м; кабель, м</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Кормовоз</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; разгрузка (шнековая, пневмо)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Кормораздатчик на шасси</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; взвешивание</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Плуг навесной</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Корпусов; ширина захвата корпуса, см; оборотный; категория навески</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Вспашка</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Культиватор навесной</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Ширина захвата, м; рабочие органы</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Обработка почвы</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Борона навесная</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Ширина захвата, м; тип (зубовая, дисковая)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Обработка почвы</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Косилка навесная</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Ширина захвата, м; тип (роторная, сегментная)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Скашивание</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Фреза почвенная</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Обработка почвы</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Сельскохозяйственные</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Картофелесажалка, копалка</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Рядов</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Посадка, уборка</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Грузозахватные</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Погрузочное оборудование</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность, т</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>ПКУ-0,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Грузозахватные</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Вилы паллетные</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность, т; длина вил, мм; класс каретки</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Паллеты, штучные грузы</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Грузозахватные</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Захват для брёвен</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие, м; ротатор</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Лес, трубы</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Грузозахватные</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Захват для рулонов (тюков)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Диаметр рулона, мм; масса рулона, кг</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Рулоны сена, соломы, бумаги</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Грузозахватные</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Грейфер</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; тип (канатный, гидравлический); ротатор</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Сыпучие грузы, металлолом, мусор</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Грузозахватные</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Крановая стрела (крюк)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность, т; вылет, м</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Штучные грузы</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Грузозахватные</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Люлька</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Грузоподъёмность, кг; человек</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Подъём людей</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Ковши</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Ковш основной</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; ширина, мм; зубьев; тип коронок</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Грунт I–III категории, сыпучие материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Ковши</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Ковш скальный</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; ширина, мм; марка стали; толщина, мм</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Скальный и мёрзлый грунт</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Ковши</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Ковш планировочный (откосный, поворотный)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм; угол поворота, °</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Планировка, откосы, каналы</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Ковши</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Ковш траншейный</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Узкие траншеи</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Ковши</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Ковш челюстной (4 в 1)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; ширина, мм; раскрытие, мм</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Погрузка, захват, планировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Ковши</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Ковш для лёгких материалов</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Объём, м³; ширина, мм</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Зерно, снег, уголь, щепа</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Ковши</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Ковш-грохот (дробильный)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Производительность, м³/ч; фракция, мм</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Сортировка и дробление на месте</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Разрушающие и бурильные</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Гидромолот</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Энергия удара, Дж; частота, уд/мин; диаметр пики, мм; давление, бар; расход, л/мин</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Бетон, скала, мёрзлый грунт</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Разрушающие и бурильные</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Гидробур (ямобур)</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Диаметр шнека, мм; глубина, м; крутящий момент, Н·м</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Скважины под сваи и столбы</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Разрушающие и бурильные</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Рыхлитель</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Зубьев; глубина рыхления, мм</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Мёрзлый и скальный грунт</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Разрушающие и бурильные</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Гидроножницы (демонтажные)</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Раскрытие, мм; усилие реза, т</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Снос</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Адаптеры комбайна</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Жатка зерновая</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Уборка зерновых</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Адаптеры комбайна</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Жатка кукурузная, подсолнечная</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, м; рядов</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Уборка пропашных</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Адаптеры комбайна</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Подборщик</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, м</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Подбор валков</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D103"/>
+  <autoFilter ref="A1:D136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6534,26 +6867,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Поле</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Пояснение</t>
         </is>
@@ -6562,176 +6901,199 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Техпаспорт или осмотр</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>Вид модуля</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>список</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>лист «Модули»</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>лист «Модули»; в свидетельстве тип ТС часто называет надстройку: «грузовой, автокран», «специальная автоцистерна»</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>Изготовитель модуля</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>отдельно от изготовителя базы; может быть неизвестен</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>по табличке или логотипу; отдельно от изготовителя машины</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>Модель (индекс) установки</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>КС-45717, АЦ 3,0-40/4, КМУ Palfinger PK 23500</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>по табличке: КС-45717, АЦ 3,0-40/4, Palfinger PK 23500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>Заводской номер</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>текст</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>по табличке</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Осмотр</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>Год выпуска модуля</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>год</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>по табличке</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Год монтажа на эту базу</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>год</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
+          <t>Моточасы модуля</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>счётчик крана, насоса, КМУ, холодильной установки</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Моточасы модуля</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>счётчик крана, насоса, КМУ, холодильной установки</t>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>шкала осмотра</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Привод</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>от КОМ базы, свой двигатель, электро</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Учёт в надзоре</t>
+          <t>Пользователь</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>да / нет + номер</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>краны, подъёмники, КМУ, сосуды под давлением</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Техническое состояние</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Комплектность</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+          <t>таблица: название и значение</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>пишет пользователь; что обычно вписывают — колонка на листе «Модули». Общее для многих: масса, привод (от КОМ, свой двигатель, электро), тип крепления, требуемая гидравлика, год монтажа, учёт в надзоре</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12"/>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6851,7 +7213,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Глубина копания, м; грузоподъёмность погрузчика, т; телескопическая рукоять; привод 2WD/4WD (ковши — навесное оборудование)</t>
+          <t>Глубина копания, м; грузоподъёмность погрузчика, т; телескопическая рукоять; привод 2WD/4WD (ковши — модули)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7536,7 +7898,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки (жатка — навесное оборудование отдельной записью)</t>
+          <t>Пропускная способность, кг/с; бункер, м³; молотильное устройство (барабан, ротор); моточасы молотилки (жатка — модуль)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -8166,7 +8528,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Дополнительные поля</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -8192,1071 +8554,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Группа</t>
+          <t>Вид</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Вид</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Назначение</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>На какой технике</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Поля сверх общих</t>
+          <t>Поля сверх общих полей прицепа</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ковши</t>
+          <t>Сеялка прицепная</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ковш основной</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Грунт I–III категории, сыпучие материалы</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор, погрузчик</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; ширина, мм; зубьев; тип коронок</t>
+          <t>Ширина захвата, м; рядов; бункер, л</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ковши</t>
+          <t>Опрыскиватель прицепной</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Ковш скальный</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Скальный и мёрзлый грунт</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; ширина, мм; марка стали; толщина, мм</t>
+          <t>Ёмкость бака, л; ширина штанги, м</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Ковши</t>
+          <t>Пресс-подборщик</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ковш планировочный (откосный, поворотный)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Планировка, откосы, каналы</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, мм; угол поворота, °</t>
+          <t>Тип тюка (рулон, квадрат); размер тюка; ширина подборщика, м</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Ковши</t>
+          <t>Косилка прицепная</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ковш траншейный</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Узкие траншеи</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, мм</t>
+          <t>Ширина захвата, м; плющилка</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ковши</t>
+          <t>Разбрасыватель удобрений</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ковш челюстной (4 в 1)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Погрузка, захват, планировка</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Погрузчик, экскаватор-погрузчик</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; ширина, мм; раскрытие, мм</t>
+          <t>Грузоподъёмность, т; ширина разбрасывания, м</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Ковши</t>
+          <t>Кормораздатчик (миксер) прицепной</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ковш для лёгких материалов</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Зерно, снег, уголь, щепа</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Погрузчик</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; ширина, мм</t>
+          <t>Объём бункера, м³</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Ковши</t>
+          <t>Борона дисковая прицепная</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ковш-грохот (дробильный)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Сортировка и дробление на месте</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор, погрузчик</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Производительность, м³/ч; фракция, мм</t>
+          <t>Ширина захвата, м; рабочая глубина, см</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Грузозахватные</t>
+          <t>Культиватор прицепной</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Вилы паллетные</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Паллеты, штучные грузы</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Погрузчик, телескопический погрузчик</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; длина вил, мм; класс каретки</t>
+          <t>Ширина захвата, м; рабочая глубина, см</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Грузозахватные</t>
+          <t>Скрепер прицепной</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Захват для брёвен</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Лес, трубы</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Погрузчик, манипулятор</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Раскрытие, м; ротатор</t>
+          <t>Объём кузова-ковша, м³</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Грузозахватные</t>
+          <t>Транспортная тележка жатки</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Захват для рулонов (тюков)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Рулоны сена, соломы, бумаги</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Погрузчик, трактор</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр рулона, мм; масса рулона, кг</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Грузозахватные</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Грейфер</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Сыпучие грузы, металлолом, мусор</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор, манипулятор</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³; тип (канатный, гидравлический); ротатор</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Грузозахватные</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Крановая стрела (крюк)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Штучные грузы</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Погрузчик</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, т; вылет, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Грузозахватные</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Люлька</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Подъём людей</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Телескопический погрузчик</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Грузоподъёмность, кг; человек</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Разрушающие и бурильные</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Гидромолот</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Бетон, скала, мёрзлый грунт</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор, мини-погрузчик</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Энергия удара, Дж; частота, уд/мин; диаметр пики, мм; давление, бар; расход, л/мин</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Разрушающие и бурильные</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Гидробур (ямобур)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Скважины под сваи и столбы</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор, погрузчик, КМУ</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр шнека, мм; глубина, м; крутящий момент, Н·м</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Разрушающие и бурильные</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Рыхлитель</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Мёрзлый и скальный грунт</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор, бульдозер</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Зубьев; глубина рыхления, мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Разрушающие и бурильные</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Гидроножницы (демонтажные)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Снос</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Раскрытие, мм; усилие реза, т</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Отвал бульдозерный</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Перемещение грунта</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Трактор, мини-погрузчик</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, мм; высота, мм; поворотный</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Отвал снежный</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Снегоочистка</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Трактор, грузовик, погрузчик</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, мм; угол поворота, °; нож (металл, полиуретан)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Щётка коммунальная</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Подметание</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Трактор, погрузчик</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, мм; диаметр щётки, мм; бункер; увлажнение</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Фреза дорожная</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Снятие асфальта</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Мини-погрузчик, экскаватор</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, мм; глубина, мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Мульчер (лесная фреза)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Расчистка поросли</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор, трактор</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, мм; диаметр ствола, мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Снегоочиститель фрезерно-роторный</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Снегоочистка</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Трактор, погрузчик</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, мм; дальность выброса, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Виброплита навесная</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Уплотнение в траншеях</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Экскаватор</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Усилие, кН; частота, Гц</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Траншеекопатель навесной</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Траншеи под кабель</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Мини-погрузчик, трактор</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Глубина, м; ширина, мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Сельскохозяйственные навесные</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Плуг навесной</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Вспашка</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Трактор</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Корпусов; ширина захвата корпуса, см; оборотный; категория навески</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Сельскохозяйственные навесные</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Культиватор навесной</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Обработка почвы</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Трактор</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, м; рабочие органы</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Сельскохозяйственные навесные</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Борона навесная</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Обработка почвы</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Трактор</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, м; тип (зубовая, дисковая)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Сельскохозяйственные навесные</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Косилка навесная</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Скашивание</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Трактор</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Ширина захвата, м; тип (роторная, сегментная)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Сельскохозяйственные навесные</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Фреза почвенная</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Обработка почвы</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Трактор</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Сельскохозяйственные навесные</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Картофелесажалка, копалка</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Посадка, уборка</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Трактор</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Рядов</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Адаптеры комбайна</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Жатка зерновая</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Уборка зерновых</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Комбайн</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Адаптеры комбайна</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Жатка кукурузная, подсолнечная</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Уборка пропашных</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Комбайн</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, м; рядов</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Адаптеры комбайна</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Подборщик</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Подбор валков</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Комбайн</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Ширина, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Пескоразбрасыватель сменный</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Разбрасывание песка и реагентов</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>КДМ, малое коммунальное шасси</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Объём бункера, м³; ширина распределения, м</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Дорожные и коммунальные</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Поливомоечное оборудование сменное</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Полив и мойка</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>КДМ, малое коммунальное шасси</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Объём цистерны, м³; ширина мойки, м; насос</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Сменные кузова</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Контейнер мультилифта</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Перевозка</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Мультилифт</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Вид (самосвальный, мусорный, цистерна, бытовка); объём, м³</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Сменные кузова</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Бункер бункеровоза</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Мусор</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Бункеровоз</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Объём, м³</t>
+          <t>Длина, м; грузоподъёмность, т</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E39"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись, параметры рабочего органа — поля машины.</t>
+          <t>Рабочий орган спроектирован вместе с рамой, без него машина теряет назначение, заводская табличка одна: экскаватор, бульдозер Б10М, каток, автогрейдер, фронтальный погрузчик, карьерный самосвал. Одна запись; параметры рабочего органа — в дополнительные параметры машины (правило 21).</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Поля модуля</t>
+          <t>Поля модуля и самоходной машины</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>У всех модулей одни поля: вид, изготовитель, модель установки, заводской номер, год, моточасы, состояние, комплектность — то, что видно в техпаспорте или по фото с осмотра. Остальное — в таблицу дополнительных параметров: поля модулей слишком разные, чтобы зашивать их.</t>
+          <t>У всех модулей одни поля: вид, изготовитель, модель установки, заводской номер, год, моточасы, состояние, комплектность — то, что видно в техпаспорте или по фото с осмотра. У самоходных машин так же: общие поля одни на все виды. Остальное — в таблицу дополнительных параметров: поля по видам слишком разные, чтобы зашивать их; на листах «Модули» и «Самоходные машины» они даны подсказкой.</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Поля сверх общих</t>
+          <t>Что обычно вписывают в дополнительные параметры</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
+          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля; что обычно вписывают по виду машины — колонка на листе «Самоходные машины»</t>
         </is>
       </c>
     </row>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Правила'!$A$1:$C$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Базы'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Модули'!$A$1:$D$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля модуля'!$A$1:$D$10</definedName>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Общие поля любой базы в порядке свидетельства о регистрации, затем поля осмотра; источник у каждого поля</t>
+          <t>Общие поля любой базы в порядке свидетельства о регистрации, затем поля осмотра; источник у каждого поля и где графа стоит на бланках свидетельства</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2932,14 +2932,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2963,7 +2964,12 @@
           <t>Варианты и пояснение</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Где на бланке</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>← Оглавление</t>
         </is>
@@ -2990,6 +2996,7 @@
           <t>лист «Базы»; выбирается по полю «Тип ТС, вид кузова»</t>
         </is>
       </c>
+      <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3012,6 +3019,11 @@
           <t>на старом бланке марка и модель одной строкой — «Модели»</t>
         </is>
       </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 1 — вместе с моделью; бланк «КР №»: справа, строка 3 «Модели» — вместе с моделью</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3034,6 +3046,11 @@
           <t>вместе с индексом модификации: ИМЗ-8.103-10, ВАЗ-21074</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 1 — вместе с маркой; бланк «КР №»: справа, строка 3 «Модели» — вместе с маркой</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3056,6 +3073,11 @@
           <t>при замене кузова, рамы или двигателя не меняется</t>
         </is>
       </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 2; бланк «КР №»: справа, строка 6</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3074,6 +3096,11 @@
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 3; бланк «КР №»: справа, строка 7</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3096,6 +3123,11 @@
           <t>у японских машин и старой техники часто пусто; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 4; бланк «КР №»: справа, строка 2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3118,6 +3150,11 @@
           <t>у японских машин здесь стоит идентификатор; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 5 — вместе с № шасси; бланк «КР №»: справа, строка 9</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3140,6 +3177,11 @@
           <t>из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 5 — вместе с № кузова; бланк «КР №»: справа, строка 8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3162,6 +3204,11 @@
           <t>необязательное: есть на свидетельствах прежнего образца, в советских техпаспортах и в документах на тракторы</t>
         </is>
       </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: нет графы; бланк «КР №»: справа, строка 10</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3184,6 +3231,11 @@
           <t>легковой, седан; мото, мотоцикл; грузовой, бортовой …</t>
         </is>
       </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 6; бланк «КР №»: справа, строка 4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3206,6 +3258,11 @@
           <t>левый, правый; на бланках до 2019 года графы нет — по осмотру</t>
         </is>
       </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 7 — в строке категории; бланк «КР №»: нет графы</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3224,6 +3281,11 @@
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 7 — в строке категории; бланк «КР №»: справа, строка 5 — в строке категории</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3246,6 +3308,11 @@
           <t>бензин, дизель, газ, газ-бензин, гибрид, электро; на старом бланке — рядом с объёмом («1588 Б»)</t>
         </is>
       </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 8; бланк «КР №»: справа, строка 12 — рядом с объёмом</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3268,6 +3335,11 @@
           <t>у электромобиля пусто</t>
         </is>
       </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 9; бланк «КР №»: справа, строка 12</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3290,6 +3362,11 @@
           <t>единица выбирается; у двигателя внутреннего сгорания на новом бланке пусто, «0.00» тоже считается пустым; в старых документах — в л.с.</t>
         </is>
       </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 10; бланк «КР №»: справа, строка 11</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3312,6 +3389,11 @@
           <t>у легковых часто не заполнена</t>
         </is>
       </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 11; бланк «КР №»: слева, строка 4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3334,6 +3416,11 @@
           <t>у легковых часто не заполнена</t>
         </is>
       </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева, строка 12; бланк «КР №»: слева, строка 3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3356,6 +3443,11 @@
           <t>01KG430BR</t>
         </is>
       </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: справа, строка 1; бланк «КР №»: справа, строка 1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3378,6 +3470,11 @@
           <t>на части старых бланков нет</t>
         </is>
       </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: справа, строка 2; бланк «КР №»: слева, под местом регистрации</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -3396,6 +3493,11 @@
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: справа, строка 3; бланк «КР №»: слева, строка 1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -3414,6 +3516,11 @@
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: справа, строка 4; бланк «КР №»: слева, строка 1 — под названием владельца</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3436,6 +3543,11 @@
           <t>на старом бланке — «место регистрации»</t>
         </is>
       </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: справа, строка 5; бланк «КР №»: слева, строка 5 «Место регистрации»</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3458,6 +3570,11 @@
           <t>регистрация за текущим собственником</t>
         </is>
       </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: справа, строка 7; бланк «КР №»: слева, строка 7</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3480,6 +3597,11 @@
           <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>книжка с 2019 г.: слева внизу, «AB …»; бланк «КР №»: справа внизу, «КР № …»</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3498,6 +3620,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -3520,6 +3643,7 @@
           <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
         </is>
       </c>
+      <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3542,6 +3666,7 @@
           <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
         </is>
       </c>
+      <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3560,6 +3685,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -3578,6 +3704,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -3600,6 +3727,7 @@
           <t>механическая, автоматическая, роботизированная</t>
         </is>
       </c>
+      <c r="E31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -3622,6 +3750,7 @@
           <t>нужна модулям с гидравликой</t>
         </is>
       </c>
+      <c r="E32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -3644,6 +3773,7 @@
           <t>шкала осмотра</t>
         </is>
       </c>
+      <c r="E33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -3662,6 +3792,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3684,11 +3815,12 @@
           <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
         </is>
       </c>
+      <c r="E35" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35"/>
+  <autoFilter ref="A1:E35"/>
   <hyperlinks>
-    <hyperlink ref="E1" location="'Оглавление'!A1" display="← Оглавление"/>
+    <hyperlink ref="F1" location="'Оглавление'!A1" display="← Оглавление"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -24,12 +24,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Правила'!$A$1:$C$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Базы'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$E$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Модули'!$A$1:$D$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля модуля'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Самоходные машины'!$A$1:$E$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля самоходной машины'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля самоходной машины'!$A$1:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Прицепные машины'!$A$1:$B$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Решения'!$A$1:$C$19</definedName>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -2932,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>ИНН (ПИН) собственника</t>
+          <t>Адрес собственника</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3515,10 +3515,14 @@
           <t>текст</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>на старом бланке — «место регистрации»</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 4; бланк «КР №»: слева, строка 1 — под названием владельца</t>
+          <t>книжка с 2019 г.: справа, строка 5; бланк «КР №»: слева, строка 5 «Место регистрации»</t>
         </is>
       </c>
     </row>
@@ -3530,22 +3534,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Адрес собственника</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>дата</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>на старом бланке — «место регистрации»</t>
+          <t>регистрация за текущим собственником</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 5; бланк «КР №»: слева, строка 5 «Место регистрации»</t>
+          <t>книжка с 2019 г.: справа, строка 7; бланк «КР №»: слева, строка 7</t>
         </is>
       </c>
     </row>
@@ -3557,51 +3561,43 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Дата регистрации</t>
+          <t>Серия и номер документа</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>регистрация за текущим собственником</t>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 7; бланк «КР №»: слева, строка 7</t>
+          <t>книжка с 2019 г.: слева внизу, «AB …»; бланк «КР №»: справа внизу, «КР № …»</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Серия и номер документа</t>
+          <t>Пробег</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>книжка с 2019 г.: слева внизу, «AB …»; бланк «КР №»: справа внизу, «КР № …»</t>
-        </is>
-      </c>
+          <t>км</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3611,15 +3607,19 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Пробег</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>км</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Колёсная формула</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
@@ -3653,19 +3653,15 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Колёсная формула</t>
+          <t>Число осей</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3676,7 +3672,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Число осей</t>
+          <t>Число управляемых осей</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3695,15 +3691,19 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Число управляемых осей</t>
+          <t>Тип КПП</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>механическая, автоматическая, роботизированная</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
@@ -3714,17 +3714,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Тип КПП</t>
+          <t>Коробка отбора мощности</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>да / нет</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>механическая, автоматическая, роботизированная</t>
+          <t>нужна модулям с гидравликой</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
@@ -3737,17 +3737,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Коробка отбора мощности</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>да / нет</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>нужна модулям с гидравликой</t>
+          <t>шкала осмотра</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
@@ -3760,65 +3760,42 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Пользователь</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
+          <t>таблица: название и значение</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Пользователь</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Дополнительные параметры</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>таблица: название и значение</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E35"/>
+  <autoFilter ref="A1:E34"/>
   <hyperlinks>
     <hyperlink ref="F1" location="'Оглавление'!A1" display="← Оглавление"/>
   </hyperlinks>
@@ -8668,7 +8645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9033,7 +9010,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ИНН (ПИН) собственника</t>
+          <t>Адрес собственника</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -9041,7 +9018,11 @@
           <t>текст</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>на старом бланке — «место регистрации»</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -9051,17 +9032,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Адрес собственника</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>дата</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>на старом бланке — «место регистрации»</t>
+          <t>регистрация за текущим собственником</t>
         </is>
       </c>
     </row>
@@ -9073,39 +9054,39 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Дата регистрации</t>
+          <t>Серия и номер документа</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>регистрация за текущим собственником</t>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Серия и номер документа</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>ч</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
+          <t>основной показатель наработки</t>
         </is>
       </c>
     </row>
@@ -9117,17 +9098,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>основной показатель наработки</t>
+          <t>шкала осмотра</t>
         </is>
       </c>
     </row>
@@ -9139,62 +9120,40 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Пользователь</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Пользователь</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Дополнительные параметры</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
           <t>таблица: название и значение</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля; что обычно вписывают по виду машины — колонка на листе «Самоходные машины»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:D24"/>
   <hyperlinks>
     <hyperlink ref="E1" location="'Оглавление'!A1" display="← Оглавление"/>
   </hyperlinks>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -24,12 +24,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Правила'!$A$1:$C$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Базы'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$E$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$E$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Модули'!$A$1:$D$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля модуля'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Самоходные машины'!$A$1:$E$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля самоходной машины'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля самоходной машины'!$A$1:$D$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Прицепные машины'!$A$1:$B$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Решения'!$A$1:$C$19</definedName>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -2932,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3484,18 +3484,22 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Собственник</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>регистрация за текущим собственником</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 3; бланк «КР №»: слева, строка 1</t>
+          <t>книжка с 2019 г.: справа, строка 7; бланк «КР №»: слева, строка 7</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3511,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Адрес собственника</t>
+          <t>Серия и номер документа</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3517,68 +3521,56 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>на старом бланке — «место регистрации»</t>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 5; бланк «КР №»: слева, строка 5 «Место регистрации»</t>
+          <t>книжка с 2019 г.: слева внизу, «AB …»; бланк «КР №»: справа внизу, «КР № …»</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Дата регистрации</t>
+          <t>Фактический адрес</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>регистрация за текущим собственником</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>книжка с 2019 г.: справа, строка 7; бланк «КР №»: слева, строка 7</t>
-        </is>
-      </c>
+          <t>где машина стоит на самом деле; не адрес из свидетельства</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Серия и номер документа</t>
+          <t>Пробег</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>книжка с 2019 г.: слева внизу, «AB …»; бланк «КР №»: справа внизу, «КР № …»</t>
-        </is>
-      </c>
+          <t>км</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3588,15 +3580,19 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Пробег</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>км</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
@@ -3607,17 +3603,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Колёсная формула</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr"/>
@@ -3630,19 +3626,15 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Колёсная формула</t>
+          <t>Число осей</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
@@ -3653,7 +3645,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Число осей</t>
+          <t>Число управляемых осей</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3672,15 +3664,19 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Число управляемых осей</t>
+          <t>Тип КПП</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>механическая, автоматическая, роботизированная</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
@@ -3691,17 +3687,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Тип КПП</t>
+          <t>Коробка отбора мощности</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>да / нет</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>механическая, автоматическая, роботизированная</t>
+          <t>нужна модулям с гидравликой</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr"/>
@@ -3714,17 +3710,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Коробка отбора мощности</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>да / нет</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>нужна модулям с гидравликой</t>
+          <t>шкала осмотра</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
@@ -3737,65 +3733,42 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Пользователь</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr"/>
+          <t>таблица: название и значение</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Пользователь</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Дополнительные параметры</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>таблица: название и значение</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E34"/>
+  <autoFilter ref="A1:E33"/>
   <hyperlinks>
     <hyperlink ref="F1" location="'Оглавление'!A1" display="← Оглавление"/>
   </hyperlinks>
@@ -8645,7 +8618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8992,15 +8965,19 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Собственник</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr"/>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>регистрация за текущим собственником</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -9010,7 +8987,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Адрес собственника</t>
+          <t>Серия и номер документа</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -9020,51 +8997,51 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>на старом бланке — «место регистрации»</t>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Дата регистрации</t>
+          <t>Фактический адрес</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>регистрация за текущим собственником</t>
+          <t>где машина стоит на самом деле; не адрес из свидетельства</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Серия и номер документа</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>ч</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
+          <t>основной показатель наработки</t>
         </is>
       </c>
     </row>
@@ -9076,17 +9053,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>основной показатель наработки</t>
+          <t>шкала осмотра</t>
         </is>
       </c>
     </row>
@@ -9098,62 +9075,40 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Пользователь</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Пользователь</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Дополнительные параметры</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
           <t>таблица: название и значение</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля; что обычно вписывают по виду машины — колонка на листе «Самоходные машины»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:D23"/>
   <hyperlinks>
     <hyperlink ref="E1" location="'Оглавление'!A1" display="← Оглавление"/>
   </hyperlinks>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -24,12 +24,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Правила'!$A$1:$C$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Базы'!$A$1:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$E$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Поля базы'!$A$1:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Особые поля баз'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Модули'!$A$1:$D$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Поля модуля'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Самоходные машины'!$A$1:$E$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля самоходной машины'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Поля самоходной машины'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Прицепные машины'!$A$1:$B$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Примеры отнесения'!$A$1:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Решения'!$A$1:$C$19</definedName>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Трактор (в том числе мини-трактор) и вездеход, гусеничный транспортёр заводятся только базой категории «Спецтехника», на листе самоходных машин их нет. Без навесного — база без модулей, с навесным или кунгом — база и модули. Машины, которые только называются тракторами, а оборудование у них встроено (трелёвочный трактор), — самоходные (правило 5).</t>
+          <t>Трактор (в том числе мини-трактор) и вездеход, гусеничный транспортёр заводятся только базой категории «Тракторы и специальные шасси», на листе самоходных машин их нет. Без навесного — база без модулей, с навесным или кунгом — база и модули. Машины, которые только называются тракторами, а оборудование у них встроено (трелёвочный трактор), — самоходные (правило 5).</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Рабочее орудие на своей транспортной оси (решение: со своими колёсами — прицеп).</t>
+          <t>Рабочее орудие на своей транспортной оси.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2810,7 +2810,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2832,7 +2832,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Работает сам по себе и несёт навесные модули — тогда он база.</t>
+          <t>Колёсный или гусеничный; работает с навесным и прицепным оборудованием.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2932,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Марка</t>
+          <t>Марка, модель</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>на старом бланке марка и модель одной строкой — «Модели»</t>
+          <t>как в документе, вместе с индексом модификации: ВАЗ-21074, ИМЗ-8.103-10</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 1 — вместе с моделью; бланк «КР №»: справа, строка 3 «Модели» — вместе с моделью</t>
+          <t>книжка с 2019 г.: слева, строка 1; бланк «КР №»: справа, строка 3 «Модели»; бланк УГАИ 2000-х: слева, строки 1–2 «Марка», «Модели» — часто одной записью в строке 1</t>
         </is>
       </c>
     </row>
@@ -3033,22 +3033,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Год выпуска</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>вместе с индексом модификации: ИМЗ-8.103-10, ВАЗ-21074</t>
+          <t>при замене кузова, рамы или двигателя не меняется</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 1 — вместе с маркой; бланк «КР №»: справа, строка 3 «Модели» — вместе с маркой</t>
+          <t>книжка с 2019 г.: слева, строка 2; бланк «КР №»: справа, строка 6; бланк УГАИ 2000-х: слева, строка 3</t>
         </is>
       </c>
     </row>
@@ -3060,22 +3060,18 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Год выпуска</t>
+          <t>Цвет</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>год</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>при замене кузова, рамы или двигателя не меняется</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 2; бланк «КР №»: справа, строка 6</t>
+          <t>книжка с 2019 г.: слева, строка 3; бланк «КР №»: справа, строка 7; бланк УГАИ 2000-х: слева, строка 4</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3083,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Цвет</t>
+          <t>Идентификационный номер (VIN)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3095,10 +3091,14 @@
           <t>текст</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>у японских машин и старой техники часто пусто; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 3; бланк «КР №»: справа, строка 7</t>
+          <t>книжка с 2019 г.: слева, строка 4; бланк «КР №»: справа, строка 2; бланк УГАИ 2000-х: нет графы</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Идентификационный номер (VIN)</t>
+          <t>№ кузова (коляски)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>у японских машин и старой техники часто пусто; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
+          <t>у японских машин здесь стоит идентификатор; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 4; бланк «КР №»: справа, строка 2</t>
+          <t>книжка с 2019 г.: слева, строка 5 — вместе с № шасси; бланк «КР №»: справа, строка 9; бланк УГАИ 2000-х: слева, строка 7</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>№ кузова (коляски)</t>
+          <t>№ шасси (рамы)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>у японских машин здесь стоит идентификатор; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
+          <t>из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 5 — вместе с № шасси; бланк «КР №»: справа, строка 9</t>
+          <t>книжка с 2019 г.: слева, строка 5 — вместе с № кузова; бланк «КР №»: справа, строка 8; бланк УГАИ 2000-х: слева, строка 6</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>№ шасси (рамы)</t>
+          <t>№ двигателя</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>из VIN, № кузова и № шасси заполняется хотя бы одно</t>
+          <t>необязательное: есть на свидетельствах прежнего образца, в советских техпаспортах и в документах на тракторы</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 5 — вместе с № кузова; бланк «КР №»: справа, строка 8</t>
+          <t>книжка с 2019 г.: нет графы; бланк «КР №»: справа, строка 10; бланк УГАИ 2000-х: слева, строка 5</t>
         </is>
       </c>
     </row>
@@ -3191,34 +3191,34 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>№ двигателя</t>
+          <t>Тип ТС, вид кузова</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>необязательное: есть на свидетельствах прежнего образца, в советских техпаспортах и в документах на тракторы</t>
+          <t>легковой, седан; мото, мотоцикл; грузовой, бортовой …</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: нет графы; бланк «КР №»: справа, строка 10</t>
+          <t>книжка с 2019 г.: слева, строка 6; бланк «КР №»: справа, строка 4; бланк УГАИ 2000-х: слева, строка 8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Техпаспорт или осмотр</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Тип ТС, вид кузова</t>
+          <t>Руль</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -3228,39 +3228,35 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>легковой, седан; мото, мотоцикл; грузовой, бортовой …</t>
+          <t>левый, правый; на бланках до 2019 года графы нет — по осмотру</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 6; бланк «КР №»: справа, строка 4</t>
+          <t>книжка с 2019 г.: слева, строка 7 — в строке категории; бланк «КР №»: нет графы; бланк УГАИ 2000-х: нет графы</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт или осмотр</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Руль</t>
+          <t>Количество мест</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>левый, правый; на бланках до 2019 года графы нет — по осмотру</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 7 — в строке категории; бланк «КР №»: нет графы</t>
+          <t>книжка с 2019 г.: слева, строка 7 — в строке категории; бланк «КР №»: справа, строка 5 — в строке категории; бланк УГАИ 2000-х: нет графы</t>
         </is>
       </c>
     </row>
@@ -3272,18 +3268,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Количество мест</t>
+          <t>Тип топлива</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>бензин, дизель, газ, газ-бензин, гибрид, электро; на старом бланке — рядом с объёмом («1588 Б»)</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 7 — в строке категории; бланк «КР №»: справа, строка 5 — в строке категории</t>
+          <t>книжка с 2019 г.: слева, строка 8; бланк «КР №»: справа, строка 12 — рядом с объёмом; бланк УГАИ 2000-х: нет графы</t>
         </is>
       </c>
     </row>
@@ -3295,22 +3295,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Тип топлива</t>
+          <t>Рабочий объём двигателя</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>см³</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>бензин, дизель, газ, газ-бензин, гибрид, электро; на старом бланке — рядом с объёмом («1588 Б»)</t>
+          <t>у электромобиля пусто</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 8; бланк «КР №»: справа, строка 12 — рядом с объёмом</t>
+          <t>книжка с 2019 г.: слева, строка 9; бланк «КР №»: справа, строка 12; бланк УГАИ 2000-х: нет графы; бывает вписан от руки у № двигателя</t>
         </is>
       </c>
     </row>
@@ -3322,22 +3322,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Рабочий объём двигателя</t>
+          <t>Мощность двигателя</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>см³</t>
+          <t>кВт или л.с.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>у электромобиля пусто</t>
+          <t>единица выбирается; в старых документах — в л.с.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 9; бланк «КР №»: справа, строка 12</t>
+          <t>книжка с 2019 г.: слева, строка 10; бланк «КР №»: справа, строка 11; бланк УГАИ 2000-х: нет графы</t>
         </is>
       </c>
     </row>
@@ -3349,22 +3349,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Масса без нагрузки</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>кВт или л.с.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>единица выбирается; у двигателя внутреннего сгорания на новом бланке пусто, «0.00» тоже считается пустым; в старых документах — в л.с.</t>
+          <t>у легковых часто не заполнена</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 10; бланк «КР №»: справа, строка 11</t>
+          <t>книжка с 2019 г.: слева, строка 11; бланк «КР №»: слева, строка 4; бланк УГАИ 2000-х: слева, строка 10</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Масса без нагрузки</t>
+          <t>Максимальная разрешённая масса</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 11; бланк «КР №»: слева, строка 4</t>
+          <t>книжка с 2019 г.: слева, строка 12; бланк «КР №»: слева, строка 3; бланк УГАИ 2000-х: слева, строка 9 «Полная масса»</t>
         </is>
       </c>
     </row>
@@ -3403,22 +3403,22 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Максимальная разрешённая масса</t>
+          <t>Регистрационный номер</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>у легковых часто не заполнена</t>
+          <t>01KG430BR</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: слева, строка 12; бланк «КР №»: слева, строка 3</t>
+          <t>книжка с 2019 г.: справа, строка 1; бланк «КР №»: справа, строка 1; бланк УГАИ 2000-х: вверху обеих страниц, у номера бланка</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Регистрационный номер</t>
+          <t>Уникальный идентификатор (VID)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>01KG430BR</t>
+          <t>на части старых бланков нет</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 1; бланк «КР №»: справа, строка 1</t>
+          <t>книжка с 2019 г.: справа, строка 2; бланк «КР №»: слева, под местом регистрации; бланк УГАИ 2000-х: нет графы</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Уникальный идентификатор (VID)</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>дата</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>на части старых бланков нет</t>
+          <t>регистрация за текущим собственником; на старых бланках две даты — берётся последняя, дата перерегистрации</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 2; бланк «КР №»: слева, под местом регистрации</t>
+          <t>книжка с 2019 г.: справа, строка 7; бланк «КР №»: слева, строка 7; бланк УГАИ 2000-х: справа внизу, «Перерегистрация»</t>
         </is>
       </c>
     </row>
@@ -3484,34 +3484,34 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Дата регистрации</t>
+          <t>Серия и номер документа</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>регистрация за текущим собственником</t>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>книжка с 2019 г.: справа, строка 7; бланк «КР №»: слева, строка 7</t>
+          <t>книжка с 2019 г.: слева внизу, «AB …»; бланк «КР №»: справа внизу, «КР № …»; бланк УГАИ 2000-х: вверху, «AB …»</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Серия и номер документа</t>
+          <t>Фактический адрес</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3521,14 +3521,10 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>книжка с 2019 г.: слева внизу, «AB …»; бланк «КР №»: справа внизу, «КР № …»</t>
-        </is>
-      </c>
+          <t>где машина стоит на самом деле; не адрес из свидетельства</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3538,19 +3534,15 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Фактический адрес</t>
+          <t>Пробег</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>где машина стоит на самом деле; не адрес из свидетельства</t>
-        </is>
-      </c>
+          <t>км</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3561,15 +3553,19 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Пробег</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>км</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr"/>
+          <t>ч</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
@@ -3580,17 +3576,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Колёсная формула</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ч</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>двигатель набирает моточасы без пробега, когда модуль работает от КОМ</t>
+          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
@@ -3603,19 +3599,15 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Колёсная формула</t>
+          <t>Число осей</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>4×2, 4×4, 6×4, 6×6, 8×4, 8×8; полный привод определяется по ней</t>
-        </is>
-      </c>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
       <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3626,7 +3618,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Число осей</t>
+          <t>Число управляемых осей</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3645,15 +3637,19 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Число управляемых осей</t>
+          <t>Тип КПП</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr"/>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>механическая, автоматическая, роботизированная</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3664,17 +3660,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Тип КПП</t>
+          <t>Коробка отбора мощности</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>да / нет</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>механическая, автоматическая, роботизированная</t>
+          <t>нужна модулям с гидравликой</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
@@ -3687,19 +3683,15 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Коробка отбора мощности</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>да / нет</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>нужна модулям с гидравликой</t>
-        </is>
-      </c>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
       <c r="E30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
@@ -3710,65 +3702,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Пользователь</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr"/>
+          <t>таблица: название и значение</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="inlineStr"/>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Пользователь</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Дополнительные параметры</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>таблица: название и значение</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E33"/>
+  <autoFilter ref="A1:E32"/>
   <hyperlinks>
     <hyperlink ref="F1" location="'Оглавление'!A1" display="← Оглавление"/>
   </hyperlinks>
@@ -3848,7 +3817,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3871,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3898,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
@@ -4002,7 +3971,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4025,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4106,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4263,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4317,7 +4286,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4340,7 +4309,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4360,14 +4329,14 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4394,7 +4363,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -4414,14 +4383,14 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -4448,7 +4417,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -4475,7 +4444,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -4502,7 +4471,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -4529,7 +4498,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4549,14 +4518,14 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>страна завода-сборщика; важна для лицензионной и китайской сборки</t>
+          <t>страна завода-сборщика</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -4583,7 +4552,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -4610,7 +4579,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -4633,7 +4602,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Спецтехника</t>
+          <t>Тракторы и специальные шасси</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7629,11 +7598,7 @@
           <t>список</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -8618,7 +8583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8663,7 +8628,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Марка</t>
+          <t>Марка, модель</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -8681,7 +8646,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Изготовитель</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -8699,7 +8664,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Изготовитель</t>
+          <t>Страна сборки</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -8717,15 +8682,19 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Страна сборки</t>
+          <t>Год выпуска</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>год</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>при замене рамы, двигателя, КПП или моста не меняется</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -8735,19 +8704,15 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Год выпуска</t>
+          <t>Цвет</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>год</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>при замене рамы, двигателя, КПП или моста не меняется</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -8757,7 +8722,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Цвет</t>
+          <t>Заводской № машины (рамы)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -8775,7 +8740,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Заводской № машины (рамы)</t>
+          <t>№ двигателя</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -8793,15 +8758,19 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>№ двигателя</t>
+          <t>Мощность двигателя</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>кВт или л.с.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>единица выбирается; в старых документах — в л.с.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -8811,17 +8780,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Тип топлива</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>кВт или л.с.</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>единица выбирается; у двигателя внутреннего сгорания на новом бланке пусто, «0.00» тоже считается пустым; в старых документах — в л.с.</t>
+          <t>дизель, бензин, газ, электро</t>
         </is>
       </c>
     </row>
@@ -8833,83 +8802,83 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Тип топлива</t>
+          <t>Конструкционная масса</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>дизель, бензин, газ, электро</t>
+          <t>так в техническом паспорте</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Техпаспорт или осмотр</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Конструкционная масса</t>
+          <t>Ходовая</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>несколько из списка</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>так в техническом паспорте</t>
+          <t>колёсная, гусеничная, полугусеничная, вальцовая, шнековая, шагающая, на полозьях; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт или осмотр</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Ходовая</t>
+          <t>Способ поворота</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>несколько из списка</t>
+          <t>список</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>колёсная, гусеничная, полугусеничная, вальцовая, шнековая, шагающая, на полозьях; отмечаются все, что есть у машины: экскаватор на гусеницах и колёсах — обе</t>
+          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Техпаспорт</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Способ поворота</t>
+          <t>Регистрационный номер</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>список</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>поворотные колёса; шарнирно-сочленённая (ломающаяся) рама; бортовой поворот</t>
+          <t>01KG430BR</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8890,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Регистрационный номер</t>
+          <t>Уникальный идентификатор (VID)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -8931,7 +8900,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>01KG430BR</t>
+          <t>на части старых бланков нет</t>
         </is>
       </c>
     </row>
@@ -8943,17 +8912,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Уникальный идентификатор (VID)</t>
+          <t>Дата регистрации</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>дата</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>на части старых бланков нет</t>
+          <t>регистрация за текущим собственником; на старых бланках две даты — берётся последняя, дата перерегистрации</t>
         </is>
       </c>
     </row>
@@ -8965,29 +8934,29 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Дата регистрации</t>
+          <t>Серия и номер документа</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>текст</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>регистрация за текущим собственником</t>
+          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Техпаспорт</t>
+          <t>Осмотр</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Серия и номер документа</t>
+          <t>Фактический адрес</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -8997,7 +8966,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>свидетельство: «КР № 0786414», «AB 1783965»; у самоходных — технический паспорт</t>
+          <t>где машина стоит на самом деле; не адрес из свидетельства</t>
         </is>
       </c>
     </row>
@@ -9009,17 +8978,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Фактический адрес</t>
+          <t>Моточасы</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
+          <t>ч</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>где машина стоит на самом деле; не адрес из свидетельства</t>
+          <t>основной показатель наработки</t>
         </is>
       </c>
     </row>
@@ -9031,19 +9000,15 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Моточасы</t>
+          <t>Техническое состояние</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>ч</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>основной показатель наработки</t>
-        </is>
-      </c>
+          <t>список</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -9053,62 +9018,40 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Техническое состояние</t>
+          <t>Комплектность</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>список</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>шкала осмотра</t>
-        </is>
-      </c>
+          <t>текст</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Осмотр</t>
+          <t>Пользователь</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Дополнительные параметры</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>текст</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Пользователь</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Дополнительные параметры</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
           <t>таблица: название и значение</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>пишет пользователь: особые отметки документа («взамен т/п АВ759281», сертификат соответствия) и всё, чему нет своего поля; что обычно вписывают по виду машины — колонка на листе «Самоходные машины»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D23"/>
+  <autoFilter ref="A1:D22"/>
   <hyperlinks>
     <hyperlink ref="E1" location="'Оглавление'!A1" display="← Оглавление"/>
   </hyperlinks>

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>До 8 пассажирских мест, максимальная разрешённая масса до 3,5 т. Пикап относится по полю «Тип ТС, вид кузова» в свидетельстве.</t>
+          <t>До 8 пассажирских мест, максимальная разрешённая масса до 3,5 т. Пикап — сюда, если в «Тип ТС, вид кузова» он записан легковым.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">

--- a/docs/kategorii-ts-baza-modul.xlsx
+++ b/docs/kategorii-ts-baza-modul.xlsx
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>у японских машин и старой техники часто пусто; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
+          <t>из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>у японских машин здесь стоит идентификатор; из VIN, № кузова и № шасси заполняется хотя бы одно</t>
+          <t>из VIN, № кузова и № шасси заполняется хотя бы одно</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3357,11 +3357,7 @@
           <t>кг</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>у легковых часто не заполнена</t>
-        </is>
-      </c>
+      <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>книжка с 2019 г.: слева, строка 11; бланк «КР №»: слева, строка 4; бланк УГАИ 2000-х: слева, строка 10</t>
@@ -3384,11 +3380,7 @@
           <t>кг</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>у легковых часто не заполнена</t>
-        </is>
-      </c>
+      <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>книжка с 2019 г.: слева, строка 12; бланк «КР №»: слева, строка 3; бланк УГАИ 2000-х: слева, строка 9 «Полная масса»</t>
